--- a/Carrera Laguna Seca.xlsx
+++ b/Carrera Laguna Seca.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\agustin.iraldi\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CA2C949D-2618-441A-8E14-3EBC81AB0034}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{ADC4414B-4509-4B18-9950-ADDEDEA587F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7605" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7605" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="75">
   <si>
     <t>POSICION C1</t>
   </si>
@@ -222,21 +222,6 @@
     <t>EZE</t>
   </si>
   <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>CALAFATE</t>
-  </si>
-  <si>
-    <t>TERMAS</t>
-  </si>
-  <si>
-    <t>ROSARIO</t>
-  </si>
-  <si>
-    <t>VILLICUM</t>
-  </si>
-  <si>
     <t>Total victorias</t>
   </si>
   <si>
@@ -261,34 +246,13 @@
     <t>VR Carrera 2</t>
   </si>
   <si>
-    <t>TERMAS TN</t>
-  </si>
-  <si>
     <t>Columna1</t>
-  </si>
-  <si>
-    <t>Termas TN</t>
   </si>
   <si>
     <t>Carrera</t>
   </si>
   <si>
     <t>ROSARIO C1</t>
-  </si>
-  <si>
-    <t>Pablo C2</t>
-  </si>
-  <si>
-    <t>Agus C2</t>
-  </si>
-  <si>
-    <t>Juandi C2</t>
-  </si>
-  <si>
-    <t>Eze C2</t>
-  </si>
-  <si>
-    <t>1</t>
   </si>
   <si>
     <t>Agus C1</t>
@@ -303,124 +267,10 @@
     <t>Adri C1</t>
   </si>
   <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
     <t>PROMEDIO</t>
   </si>
   <si>
     <t>Mejor tiempo</t>
-  </si>
-  <si>
-    <t>ROSARIO C2</t>
-  </si>
-  <si>
-    <t>Pablo C1</t>
-  </si>
-  <si>
-    <t>Juandi C1</t>
-  </si>
-  <si>
-    <t>Eze C1</t>
-  </si>
-  <si>
-    <t>=+K,ESIMO,MENOR(B38:B57;1)</t>
-  </si>
-  <si>
-    <t>=+K,ESIMO,MENOR(D38:D57;1)</t>
-  </si>
-  <si>
-    <t>=+K,ESIMO,MENOR(F38:F57;1)</t>
-  </si>
-  <si>
-    <t>=+K,ESIMO,MENOR(H38:H57;1)</t>
-  </si>
-  <si>
-    <t>=+K,ESIMO,MENOR(L38:L57;1)</t>
-  </si>
-  <si>
-    <t>=+K,ESIMO,MENOR(N38:N57;1)</t>
-  </si>
-  <si>
-    <t>=+K,ESIMO,MENOR(P38:P57;1)</t>
-  </si>
-  <si>
-    <t>=+K,ESIMO,MENOR(R38:R57;1)</t>
-  </si>
-  <si>
-    <t>VILLICUM C1</t>
-  </si>
-  <si>
-    <t>Toay</t>
-  </si>
-  <si>
-    <t>Exe</t>
-  </si>
-  <si>
-    <t>=+K,ESIMO,MENOR(D69:D84;1)</t>
-  </si>
-  <si>
-    <t>=+K,ESIMO,MENOR(H69:H84;1)</t>
-  </si>
-  <si>
-    <t>Promedio total</t>
-  </si>
-  <si>
-    <t>Dif promedio</t>
-  </si>
-  <si>
-    <t>Record</t>
-  </si>
-  <si>
-    <t>=+K,ESIMO,MENOR(N69:N93;1)</t>
-  </si>
-  <si>
-    <t>=+K,ESIMO,MENOR(R69:R93;1)</t>
-  </si>
-  <si>
-    <t>Dif, record</t>
-  </si>
-  <si>
-    <t>=+K,ESIMO,MENOR(R71:R95;1)</t>
   </si>
   <si>
     <t>Adrian Saldias</t>
@@ -447,10 +297,10 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="5">
     <numFmt numFmtId="164" formatCode="0&quot;Kg&quot;"/>
-    <numFmt numFmtId="166" formatCode="mm:ss.000"/>
-    <numFmt numFmtId="167" formatCode="\ &quot;+ &quot;s.000"/>
-    <numFmt numFmtId="168" formatCode="&quot;+&quot;s.000"/>
-    <numFmt numFmtId="169" formatCode="&quot;+ &quot;s.000"/>
+    <numFmt numFmtId="165" formatCode="mm:ss.000"/>
+    <numFmt numFmtId="166" formatCode="\ &quot;+ &quot;s.000"/>
+    <numFmt numFmtId="167" formatCode="&quot;+&quot;s.000"/>
+    <numFmt numFmtId="168" formatCode="&quot;+ &quot;s.000"/>
   </numFmts>
   <fonts count="12">
     <font>
@@ -1209,56 +1059,83 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="47" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="5" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="47" fontId="5" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="5" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="8" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="8" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1270,7 +1147,10 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1279,25 +1159,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1315,43 +1189,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment readingOrder="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="6">
     <dxf>
-      <numFmt numFmtId="167" formatCode="\ &quot;+ &quot;s.000"/>
+      <numFmt numFmtId="166" formatCode="\ &quot;+ &quot;s.000"/>
     </dxf>
     <dxf>
       <fill>
@@ -1361,10 +1211,10 @@
       </fill>
     </dxf>
     <dxf>
-      <numFmt numFmtId="168" formatCode="&quot;+&quot;s.000"/>
+      <numFmt numFmtId="167" formatCode="&quot;+&quot;s.000"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="169" formatCode="&quot;+ &quot;s.000"/>
+      <numFmt numFmtId="168" formatCode="&quot;+ &quot;s.000"/>
     </dxf>
     <dxf>
       <fill>
@@ -1374,7 +1224,7 @@
       </fill>
     </dxf>
     <dxf>
-      <numFmt numFmtId="168" formatCode="&quot;+&quot;s.000"/>
+      <numFmt numFmtId="167" formatCode="&quot;+&quot;s.000"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -3064,17 +2914,17 @@
       </c>
       <c r="D1" s="111"/>
       <c r="E1" s="1"/>
-      <c r="F1" s="105" t="s">
+      <c r="F1" s="118" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="105"/>
-      <c r="H1" s="105"/>
-      <c r="I1" s="105"/>
-      <c r="J1" s="105"/>
-      <c r="K1" s="105"/>
-      <c r="L1" s="105"/>
-      <c r="M1" s="105"/>
-      <c r="N1" s="105"/>
+      <c r="G1" s="118"/>
+      <c r="H1" s="118"/>
+      <c r="I1" s="118"/>
+      <c r="J1" s="118"/>
+      <c r="K1" s="118"/>
+      <c r="L1" s="118"/>
+      <c r="M1" s="118"/>
+      <c r="N1" s="118"/>
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
@@ -3089,13 +2939,13 @@
       <c r="Z1" s="1"/>
     </row>
     <row r="2" spans="1:26" ht="16.5" thickTop="1" thickBot="1">
-      <c r="A2" s="102">
+      <c r="A2" s="101">
         <v>1</v>
       </c>
-      <c r="B2" s="102">
+      <c r="B2" s="101">
         <v>25</v>
       </c>
-      <c r="C2" s="102">
+      <c r="C2" s="101">
         <v>1</v>
       </c>
       <c r="D2" s="1">
@@ -3135,26 +2985,26 @@
         <v>0</v>
       </c>
       <c r="Q2" s="1"/>
-      <c r="R2" s="105" t="s">
+      <c r="R2" s="118" t="s">
         <v>9</v>
       </c>
-      <c r="S2" s="105"/>
-      <c r="T2" s="105"/>
-      <c r="U2" s="105"/>
-      <c r="V2" s="105"/>
-      <c r="W2" s="105"/>
-      <c r="X2" s="105"/>
-      <c r="Y2" s="105"/>
-      <c r="Z2" s="105"/>
+      <c r="S2" s="118"/>
+      <c r="T2" s="118"/>
+      <c r="U2" s="118"/>
+      <c r="V2" s="118"/>
+      <c r="W2" s="118"/>
+      <c r="X2" s="118"/>
+      <c r="Y2" s="118"/>
+      <c r="Z2" s="118"/>
     </row>
     <row r="3" spans="1:26" ht="16.5" thickTop="1" thickBot="1">
-      <c r="A3" s="102">
+      <c r="A3" s="101">
         <v>2</v>
       </c>
-      <c r="B3" s="102">
+      <c r="B3" s="101">
         <v>18</v>
       </c>
-      <c r="C3" s="102">
+      <c r="C3" s="101">
         <v>2</v>
       </c>
       <c r="D3" s="1">
@@ -3223,13 +3073,13 @@
       <c r="Z3" s="1"/>
     </row>
     <row r="4" spans="1:26" ht="15.75" thickTop="1">
-      <c r="A4" s="102">
+      <c r="A4" s="101">
         <v>3</v>
       </c>
-      <c r="B4" s="102">
+      <c r="B4" s="101">
         <v>15</v>
       </c>
-      <c r="C4" s="102">
+      <c r="C4" s="101">
         <v>3</v>
       </c>
       <c r="D4" s="1">
@@ -3272,13 +3122,13 @@
       <c r="Z4" s="1"/>
     </row>
     <row r="5" spans="1:26">
-      <c r="A5" s="102">
+      <c r="A5" s="101">
         <v>4</v>
       </c>
-      <c r="B5" s="102">
+      <c r="B5" s="101">
         <v>12</v>
       </c>
-      <c r="C5" s="102">
+      <c r="C5" s="101">
         <v>4</v>
       </c>
       <c r="D5" s="1">
@@ -3332,17 +3182,17 @@
       <c r="O6" s="1"/>
       <c r="P6" s="1"/>
       <c r="Q6" s="1"/>
-      <c r="R6" s="105" t="s">
+      <c r="R6" s="118" t="s">
         <v>19</v>
       </c>
-      <c r="S6" s="105"/>
-      <c r="T6" s="105"/>
-      <c r="U6" s="105"/>
-      <c r="V6" s="105"/>
-      <c r="W6" s="105"/>
-      <c r="X6" s="105"/>
-      <c r="Y6" s="105"/>
-      <c r="Z6" s="105"/>
+      <c r="S6" s="118"/>
+      <c r="T6" s="118"/>
+      <c r="U6" s="118"/>
+      <c r="V6" s="118"/>
+      <c r="W6" s="118"/>
+      <c r="X6" s="118"/>
+      <c r="Y6" s="118"/>
+      <c r="Z6" s="118"/>
     </row>
     <row r="7" spans="1:26" ht="15.75" thickTop="1">
       <c r="A7" s="1"/>
@@ -3402,26 +3252,26 @@
       <c r="F8" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="G8" s="110">
+      <c r="G8" s="122">
         <f>+SUM(H3:H7)</f>
         <v>15</v>
       </c>
-      <c r="H8" s="109"/>
-      <c r="I8" s="110">
+      <c r="H8" s="120"/>
+      <c r="I8" s="122">
         <f>+SUM(J3:J7)</f>
         <v>25</v>
       </c>
-      <c r="J8" s="109"/>
-      <c r="K8" s="110">
+      <c r="J8" s="120"/>
+      <c r="K8" s="122">
         <f>+SUM(L3:L7)</f>
         <v>18</v>
       </c>
-      <c r="L8" s="109"/>
-      <c r="M8" s="110">
+      <c r="L8" s="120"/>
+      <c r="M8" s="122">
         <f>+SUM(N3:N7)</f>
         <v>13</v>
       </c>
-      <c r="N8" s="109"/>
+      <c r="N8" s="120"/>
       <c r="O8" s="1"/>
       <c r="P8" s="1"/>
       <c r="Q8" s="1"/>
@@ -3456,17 +3306,17 @@
       <c r="O9" s="1"/>
       <c r="P9" s="1"/>
       <c r="Q9" s="1"/>
-      <c r="R9" s="105" t="s">
+      <c r="R9" s="118" t="s">
         <v>22</v>
       </c>
-      <c r="S9" s="105"/>
-      <c r="T9" s="105"/>
-      <c r="U9" s="105"/>
-      <c r="V9" s="105"/>
-      <c r="W9" s="105"/>
-      <c r="X9" s="105"/>
-      <c r="Y9" s="105"/>
-      <c r="Z9" s="105"/>
+      <c r="S9" s="118"/>
+      <c r="T9" s="118"/>
+      <c r="U9" s="118"/>
+      <c r="V9" s="118"/>
+      <c r="W9" s="118"/>
+      <c r="X9" s="118"/>
+      <c r="Y9" s="118"/>
+      <c r="Z9" s="118"/>
     </row>
     <row r="10" spans="1:26" ht="15.75" thickTop="1">
       <c r="A10" s="1"/>
@@ -3477,26 +3327,26 @@
       <c r="F10" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="G10" s="112">
+      <c r="G10" s="121">
         <f>G8</f>
         <v>15</v>
       </c>
-      <c r="H10" s="112"/>
-      <c r="I10" s="112">
+      <c r="H10" s="121"/>
+      <c r="I10" s="121">
         <f>I8</f>
         <v>25</v>
       </c>
-      <c r="J10" s="112"/>
-      <c r="K10" s="112">
+      <c r="J10" s="121"/>
+      <c r="K10" s="121">
         <f>K8</f>
         <v>18</v>
       </c>
-      <c r="L10" s="112"/>
-      <c r="M10" s="112">
+      <c r="L10" s="121"/>
+      <c r="M10" s="121">
         <f>M8</f>
         <v>13</v>
       </c>
-      <c r="N10" s="112"/>
+      <c r="N10" s="121"/>
       <c r="O10" s="1"/>
       <c r="P10" s="1"/>
       <c r="Q10" s="1"/>
@@ -3529,26 +3379,26 @@
       <c r="F11" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="G11" s="103">
+      <c r="G11" s="112">
         <f>+IF($G3=1,40,IF($G3=2,20,IF($G3=3,10,IF($G3=4,0,""))))</f>
         <v>10</v>
       </c>
-      <c r="H11" s="104"/>
-      <c r="I11" s="103">
+      <c r="H11" s="113"/>
+      <c r="I11" s="112">
         <f>+IF($I3=1,40,IF($I3=2,20,IF($I3=3,10,IF($I3=4,0,""))))</f>
         <v>40</v>
       </c>
-      <c r="J11" s="104"/>
-      <c r="K11" s="103">
+      <c r="J11" s="113"/>
+      <c r="K11" s="112">
         <f>+IF($K3=1,40,IF($K3=2,20,IF($K3=3,10,IF($K3=4,0,""))))</f>
         <v>20</v>
       </c>
-      <c r="L11" s="104"/>
-      <c r="M11" s="103">
+      <c r="L11" s="113"/>
+      <c r="M11" s="112">
         <f>+IF($M3=1,40,IF($M3=2,20,IF($M3=3,10,IF($M3=4,0,""))))</f>
         <v>0</v>
       </c>
-      <c r="N11" s="104"/>
+      <c r="N11" s="113"/>
       <c r="O11" s="1"/>
       <c r="P11" s="1"/>
       <c r="Q11" s="1"/>
@@ -3571,40 +3421,40 @@
       <c r="F12" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="G12" s="103">
+      <c r="G12" s="112">
         <f>+IF($G3=1,40,IF($G3=2,20,IF($G3=3,10,IF($G3=4,0,""))))</f>
         <v>10</v>
       </c>
-      <c r="H12" s="104"/>
-      <c r="I12" s="103">
+      <c r="H12" s="113"/>
+      <c r="I12" s="112">
         <f>+IF($I3=1,40,IF($I3=2,20,IF($I3=3,10,IF($I3=4,0,""))))</f>
         <v>40</v>
       </c>
-      <c r="J12" s="104"/>
-      <c r="K12" s="103">
+      <c r="J12" s="113"/>
+      <c r="K12" s="112">
         <f>+IF($K3=1,40,IF($K3=2,20,IF($K3=3,10,IF($K3=4,0,""))))</f>
         <v>20</v>
       </c>
-      <c r="L12" s="104"/>
-      <c r="M12" s="103">
+      <c r="L12" s="113"/>
+      <c r="M12" s="112">
         <f>+IF($M3=1,40,IF($M3=2,20,IF($M3=3,10,IF($M3=4,0,""))))</f>
         <v>0</v>
       </c>
-      <c r="N12" s="104"/>
+      <c r="N12" s="113"/>
       <c r="O12" s="1"/>
       <c r="P12" s="1"/>
       <c r="Q12" s="1"/>
-      <c r="R12" s="105" t="s">
+      <c r="R12" s="118" t="s">
         <v>25</v>
       </c>
-      <c r="S12" s="105"/>
-      <c r="T12" s="105"/>
-      <c r="U12" s="105"/>
-      <c r="V12" s="105"/>
-      <c r="W12" s="105"/>
-      <c r="X12" s="105"/>
-      <c r="Y12" s="105"/>
-      <c r="Z12" s="105"/>
+      <c r="S12" s="118"/>
+      <c r="T12" s="118"/>
+      <c r="U12" s="118"/>
+      <c r="V12" s="118"/>
+      <c r="W12" s="118"/>
+      <c r="X12" s="118"/>
+      <c r="Y12" s="118"/>
+      <c r="Z12" s="118"/>
     </row>
     <row r="13" spans="1:26" ht="15.75" thickTop="1">
       <c r="A13" s="1"/>
@@ -3650,15 +3500,15 @@
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
-      <c r="F14" s="105"/>
-      <c r="G14" s="105"/>
-      <c r="H14" s="105"/>
-      <c r="I14" s="105"/>
-      <c r="J14" s="105"/>
-      <c r="K14" s="105"/>
-      <c r="L14" s="105"/>
-      <c r="M14" s="105"/>
-      <c r="N14" s="105"/>
+      <c r="F14" s="118"/>
+      <c r="G14" s="118"/>
+      <c r="H14" s="118"/>
+      <c r="I14" s="118"/>
+      <c r="J14" s="118"/>
+      <c r="K14" s="118"/>
+      <c r="L14" s="118"/>
+      <c r="M14" s="118"/>
+      <c r="N14" s="118"/>
       <c r="O14" s="1"/>
       <c r="P14" s="1"/>
       <c r="Q14" s="1"/>
@@ -3813,14 +3663,14 @@
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
       <c r="F21" s="12"/>
-      <c r="G21" s="110"/>
-      <c r="H21" s="109"/>
-      <c r="I21" s="108"/>
-      <c r="J21" s="109"/>
-      <c r="K21" s="108"/>
-      <c r="L21" s="109"/>
-      <c r="M21" s="108"/>
-      <c r="N21" s="109"/>
+      <c r="G21" s="122"/>
+      <c r="H21" s="120"/>
+      <c r="I21" s="119"/>
+      <c r="J21" s="120"/>
+      <c r="K21" s="119"/>
+      <c r="L21" s="120"/>
+      <c r="M21" s="119"/>
+      <c r="N21" s="120"/>
       <c r="O21" s="1"/>
       <c r="P21" s="1"/>
       <c r="Q21" s="1"/>
@@ -3851,14 +3701,14 @@
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
       <c r="F23" s="7"/>
-      <c r="G23" s="106"/>
-      <c r="H23" s="107"/>
-      <c r="I23" s="106"/>
-      <c r="J23" s="107"/>
-      <c r="K23" s="106"/>
-      <c r="L23" s="107"/>
-      <c r="M23" s="106"/>
-      <c r="N23" s="107"/>
+      <c r="G23" s="116"/>
+      <c r="H23" s="117"/>
+      <c r="I23" s="116"/>
+      <c r="J23" s="117"/>
+      <c r="K23" s="116"/>
+      <c r="L23" s="117"/>
+      <c r="M23" s="116"/>
+      <c r="N23" s="117"/>
       <c r="O23" s="1"/>
       <c r="P23" s="1"/>
       <c r="Q23" s="1"/>
@@ -3870,14 +3720,14 @@
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
       <c r="F24" s="7"/>
-      <c r="G24" s="103"/>
-      <c r="H24" s="104"/>
-      <c r="I24" s="103"/>
-      <c r="J24" s="104"/>
-      <c r="K24" s="103"/>
-      <c r="L24" s="104"/>
-      <c r="M24" s="103"/>
-      <c r="N24" s="104"/>
+      <c r="G24" s="112"/>
+      <c r="H24" s="113"/>
+      <c r="I24" s="112"/>
+      <c r="J24" s="113"/>
+      <c r="K24" s="112"/>
+      <c r="L24" s="113"/>
+      <c r="M24" s="112"/>
+      <c r="N24" s="113"/>
       <c r="O24" s="1"/>
       <c r="P24" s="1"/>
       <c r="Q24" s="1"/>
@@ -3889,14 +3739,14 @@
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>
       <c r="F25" s="15"/>
-      <c r="G25" s="103"/>
-      <c r="H25" s="104"/>
-      <c r="I25" s="103"/>
-      <c r="J25" s="104"/>
-      <c r="K25" s="103"/>
-      <c r="L25" s="104"/>
-      <c r="M25" s="103"/>
-      <c r="N25" s="104"/>
+      <c r="G25" s="112"/>
+      <c r="H25" s="113"/>
+      <c r="I25" s="112"/>
+      <c r="J25" s="113"/>
+      <c r="K25" s="112"/>
+      <c r="L25" s="113"/>
+      <c r="M25" s="112"/>
+      <c r="N25" s="113"/>
       <c r="O25" s="1"/>
       <c r="P25" s="1"/>
       <c r="Q25" s="1"/>
@@ -3926,15 +3776,15 @@
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
-      <c r="F27" s="105"/>
-      <c r="G27" s="105"/>
-      <c r="H27" s="105"/>
-      <c r="I27" s="105"/>
-      <c r="J27" s="105"/>
-      <c r="K27" s="105"/>
-      <c r="L27" s="105"/>
-      <c r="M27" s="105"/>
-      <c r="N27" s="105"/>
+      <c r="F27" s="118"/>
+      <c r="G27" s="118"/>
+      <c r="H27" s="118"/>
+      <c r="I27" s="118"/>
+      <c r="J27" s="118"/>
+      <c r="K27" s="118"/>
+      <c r="L27" s="118"/>
+      <c r="M27" s="118"/>
+      <c r="N27" s="118"/>
       <c r="O27" s="1"/>
       <c r="P27" s="1"/>
       <c r="Q27" s="1"/>
@@ -4058,14 +3908,14 @@
     </row>
     <row r="34" spans="6:23" ht="15.75" thickBot="1">
       <c r="F34" s="12"/>
-      <c r="G34" s="108"/>
-      <c r="H34" s="109"/>
-      <c r="I34" s="108"/>
-      <c r="J34" s="109"/>
-      <c r="K34" s="108"/>
-      <c r="L34" s="109"/>
-      <c r="M34" s="108"/>
-      <c r="N34" s="109"/>
+      <c r="G34" s="119"/>
+      <c r="H34" s="120"/>
+      <c r="I34" s="119"/>
+      <c r="J34" s="120"/>
+      <c r="K34" s="119"/>
+      <c r="L34" s="120"/>
+      <c r="M34" s="119"/>
+      <c r="N34" s="120"/>
       <c r="O34" s="1"/>
       <c r="P34" s="1"/>
       <c r="Q34" s="1"/>
@@ -4098,14 +3948,14 @@
     </row>
     <row r="36" spans="6:23">
       <c r="F36" s="7"/>
-      <c r="G36" s="106"/>
-      <c r="H36" s="107"/>
-      <c r="I36" s="106"/>
-      <c r="J36" s="107"/>
-      <c r="K36" s="106"/>
-      <c r="L36" s="107"/>
-      <c r="M36" s="106"/>
-      <c r="N36" s="107"/>
+      <c r="G36" s="116"/>
+      <c r="H36" s="117"/>
+      <c r="I36" s="116"/>
+      <c r="J36" s="117"/>
+      <c r="K36" s="116"/>
+      <c r="L36" s="117"/>
+      <c r="M36" s="116"/>
+      <c r="N36" s="117"/>
       <c r="O36" s="1"/>
       <c r="P36" s="1"/>
       <c r="Q36" s="1"/>
@@ -4118,14 +3968,14 @@
     </row>
     <row r="37" spans="6:23">
       <c r="F37" s="7"/>
-      <c r="G37" s="103"/>
-      <c r="H37" s="104"/>
-      <c r="I37" s="103"/>
-      <c r="J37" s="104"/>
-      <c r="K37" s="103"/>
-      <c r="L37" s="104"/>
-      <c r="M37" s="103"/>
-      <c r="N37" s="104"/>
+      <c r="G37" s="112"/>
+      <c r="H37" s="113"/>
+      <c r="I37" s="112"/>
+      <c r="J37" s="113"/>
+      <c r="K37" s="112"/>
+      <c r="L37" s="113"/>
+      <c r="M37" s="112"/>
+      <c r="N37" s="113"/>
       <c r="O37" s="1"/>
       <c r="P37" s="1"/>
       <c r="Q37" s="1"/>
@@ -4138,14 +3988,14 @@
     </row>
     <row r="38" spans="6:23">
       <c r="F38" s="15"/>
-      <c r="G38" s="103"/>
-      <c r="H38" s="104"/>
-      <c r="I38" s="103"/>
-      <c r="J38" s="104"/>
-      <c r="K38" s="103"/>
-      <c r="L38" s="104"/>
-      <c r="M38" s="103"/>
-      <c r="N38" s="104"/>
+      <c r="G38" s="112"/>
+      <c r="H38" s="113"/>
+      <c r="I38" s="112"/>
+      <c r="J38" s="113"/>
+      <c r="K38" s="112"/>
+      <c r="L38" s="113"/>
+      <c r="M38" s="112"/>
+      <c r="N38" s="113"/>
       <c r="O38" s="1"/>
       <c r="P38" s="1"/>
       <c r="Q38" s="1"/>
@@ -4177,15 +4027,15 @@
       <c r="W39" s="1"/>
     </row>
     <row r="40" spans="6:23" ht="15.75" thickBot="1">
-      <c r="F40" s="105"/>
-      <c r="G40" s="105"/>
-      <c r="H40" s="105"/>
-      <c r="I40" s="105"/>
-      <c r="J40" s="105"/>
-      <c r="K40" s="105"/>
-      <c r="L40" s="105"/>
-      <c r="M40" s="105"/>
-      <c r="N40" s="105"/>
+      <c r="F40" s="118"/>
+      <c r="G40" s="118"/>
+      <c r="H40" s="118"/>
+      <c r="I40" s="118"/>
+      <c r="J40" s="118"/>
+      <c r="K40" s="118"/>
+      <c r="L40" s="118"/>
+      <c r="M40" s="118"/>
+      <c r="N40" s="118"/>
       <c r="O40" s="1"/>
       <c r="P40" s="1"/>
       <c r="Q40" s="1"/>
@@ -4320,14 +4170,14 @@
     </row>
     <row r="47" spans="6:23" ht="15.75" thickBot="1">
       <c r="F47" s="12"/>
-      <c r="G47" s="108"/>
-      <c r="H47" s="109"/>
-      <c r="I47" s="108"/>
-      <c r="J47" s="109"/>
-      <c r="K47" s="108"/>
-      <c r="L47" s="109"/>
-      <c r="M47" s="108"/>
-      <c r="N47" s="109"/>
+      <c r="G47" s="119"/>
+      <c r="H47" s="120"/>
+      <c r="I47" s="119"/>
+      <c r="J47" s="120"/>
+      <c r="K47" s="119"/>
+      <c r="L47" s="120"/>
+      <c r="M47" s="119"/>
+      <c r="N47" s="120"/>
       <c r="O47" s="1"/>
       <c r="P47" s="1"/>
       <c r="Q47" s="1"/>
@@ -4360,40 +4210,40 @@
     </row>
     <row r="49" spans="6:16">
       <c r="F49" s="7"/>
-      <c r="G49" s="106"/>
-      <c r="H49" s="107"/>
-      <c r="I49" s="106"/>
-      <c r="J49" s="107"/>
-      <c r="K49" s="106"/>
-      <c r="L49" s="107"/>
-      <c r="M49" s="106"/>
-      <c r="N49" s="107"/>
+      <c r="G49" s="116"/>
+      <c r="H49" s="117"/>
+      <c r="I49" s="116"/>
+      <c r="J49" s="117"/>
+      <c r="K49" s="116"/>
+      <c r="L49" s="117"/>
+      <c r="M49" s="116"/>
+      <c r="N49" s="117"/>
       <c r="O49" s="1"/>
       <c r="P49" s="1"/>
     </row>
     <row r="50" spans="6:16">
       <c r="F50" s="7"/>
-      <c r="G50" s="103"/>
-      <c r="H50" s="104"/>
-      <c r="I50" s="103"/>
-      <c r="J50" s="104"/>
-      <c r="K50" s="103"/>
-      <c r="L50" s="104"/>
-      <c r="M50" s="103"/>
-      <c r="N50" s="104"/>
+      <c r="G50" s="112"/>
+      <c r="H50" s="113"/>
+      <c r="I50" s="112"/>
+      <c r="J50" s="113"/>
+      <c r="K50" s="112"/>
+      <c r="L50" s="113"/>
+      <c r="M50" s="112"/>
+      <c r="N50" s="113"/>
       <c r="O50" s="1"/>
       <c r="P50" s="1"/>
     </row>
     <row r="51" spans="6:16">
       <c r="F51" s="15"/>
-      <c r="G51" s="103"/>
-      <c r="H51" s="104"/>
-      <c r="I51" s="103"/>
-      <c r="J51" s="104"/>
-      <c r="K51" s="103"/>
-      <c r="L51" s="104"/>
-      <c r="M51" s="103"/>
-      <c r="N51" s="104"/>
+      <c r="G51" s="112"/>
+      <c r="H51" s="113"/>
+      <c r="I51" s="112"/>
+      <c r="J51" s="113"/>
+      <c r="K51" s="112"/>
+      <c r="L51" s="113"/>
+      <c r="M51" s="112"/>
+      <c r="N51" s="113"/>
       <c r="O51" s="1"/>
       <c r="P51" s="1"/>
     </row>
@@ -4411,15 +4261,15 @@
       <c r="P52" s="1"/>
     </row>
     <row r="53" spans="6:16" ht="15.75" thickBot="1">
-      <c r="F53" s="105"/>
-      <c r="G53" s="105"/>
-      <c r="H53" s="105"/>
-      <c r="I53" s="105"/>
-      <c r="J53" s="105"/>
-      <c r="K53" s="105"/>
-      <c r="L53" s="105"/>
-      <c r="M53" s="105"/>
-      <c r="N53" s="105"/>
+      <c r="F53" s="118"/>
+      <c r="G53" s="118"/>
+      <c r="H53" s="118"/>
+      <c r="I53" s="118"/>
+      <c r="J53" s="118"/>
+      <c r="K53" s="118"/>
+      <c r="L53" s="118"/>
+      <c r="M53" s="118"/>
+      <c r="N53" s="118"/>
       <c r="O53" s="1"/>
       <c r="P53" s="1"/>
     </row>
@@ -4505,14 +4355,14 @@
     </row>
     <row r="60" spans="6:16" ht="15.75" thickBot="1">
       <c r="F60" s="12"/>
-      <c r="G60" s="108"/>
-      <c r="H60" s="109"/>
-      <c r="I60" s="108"/>
-      <c r="J60" s="109"/>
-      <c r="K60" s="108"/>
-      <c r="L60" s="109"/>
-      <c r="M60" s="108"/>
-      <c r="N60" s="109"/>
+      <c r="G60" s="119"/>
+      <c r="H60" s="120"/>
+      <c r="I60" s="119"/>
+      <c r="J60" s="120"/>
+      <c r="K60" s="119"/>
+      <c r="L60" s="120"/>
+      <c r="M60" s="119"/>
+      <c r="N60" s="120"/>
       <c r="O60" s="1"/>
       <c r="P60" s="1"/>
     </row>
@@ -4531,53 +4381,53 @@
     </row>
     <row r="62" spans="6:16">
       <c r="F62" s="7"/>
-      <c r="G62" s="106"/>
-      <c r="H62" s="107"/>
-      <c r="I62" s="106"/>
-      <c r="J62" s="107"/>
-      <c r="K62" s="106"/>
-      <c r="L62" s="107"/>
-      <c r="M62" s="106"/>
-      <c r="N62" s="107"/>
+      <c r="G62" s="116"/>
+      <c r="H62" s="117"/>
+      <c r="I62" s="116"/>
+      <c r="J62" s="117"/>
+      <c r="K62" s="116"/>
+      <c r="L62" s="117"/>
+      <c r="M62" s="116"/>
+      <c r="N62" s="117"/>
       <c r="O62" s="1"/>
       <c r="P62" s="1"/>
     </row>
     <row r="63" spans="6:16">
       <c r="F63" s="7"/>
-      <c r="G63" s="103"/>
-      <c r="H63" s="104"/>
-      <c r="I63" s="103"/>
-      <c r="J63" s="104"/>
-      <c r="K63" s="103"/>
-      <c r="L63" s="104"/>
-      <c r="M63" s="103"/>
-      <c r="N63" s="104"/>
+      <c r="G63" s="112"/>
+      <c r="H63" s="113"/>
+      <c r="I63" s="112"/>
+      <c r="J63" s="113"/>
+      <c r="K63" s="112"/>
+      <c r="L63" s="113"/>
+      <c r="M63" s="112"/>
+      <c r="N63" s="113"/>
       <c r="O63" s="1"/>
       <c r="P63" s="1"/>
     </row>
     <row r="64" spans="6:16">
       <c r="F64" s="15"/>
-      <c r="G64" s="103"/>
-      <c r="H64" s="104"/>
-      <c r="I64" s="103"/>
-      <c r="J64" s="104"/>
-      <c r="K64" s="103"/>
-      <c r="L64" s="104"/>
-      <c r="M64" s="103"/>
-      <c r="N64" s="104"/>
+      <c r="G64" s="112"/>
+      <c r="H64" s="113"/>
+      <c r="I64" s="112"/>
+      <c r="J64" s="113"/>
+      <c r="K64" s="112"/>
+      <c r="L64" s="113"/>
+      <c r="M64" s="112"/>
+      <c r="N64" s="113"/>
       <c r="O64" s="1"/>
       <c r="P64" s="1"/>
     </row>
     <row r="66" spans="6:16" ht="15.75" thickBot="1">
-      <c r="F66" s="105"/>
-      <c r="G66" s="105"/>
-      <c r="H66" s="105"/>
-      <c r="I66" s="105"/>
-      <c r="J66" s="105"/>
-      <c r="K66" s="105"/>
-      <c r="L66" s="105"/>
-      <c r="M66" s="105"/>
-      <c r="N66" s="105"/>
+      <c r="F66" s="118"/>
+      <c r="G66" s="118"/>
+      <c r="H66" s="118"/>
+      <c r="I66" s="118"/>
+      <c r="J66" s="118"/>
+      <c r="K66" s="118"/>
+      <c r="L66" s="118"/>
+      <c r="M66" s="118"/>
+      <c r="N66" s="118"/>
       <c r="O66" s="1"/>
       <c r="P66" s="1"/>
     </row>
@@ -4663,14 +4513,14 @@
     </row>
     <row r="73" spans="6:16" ht="15.75" thickBot="1">
       <c r="F73" s="12"/>
-      <c r="G73" s="108"/>
-      <c r="H73" s="109"/>
-      <c r="I73" s="108"/>
-      <c r="J73" s="109"/>
-      <c r="K73" s="108"/>
-      <c r="L73" s="109"/>
-      <c r="M73" s="108"/>
-      <c r="N73" s="109"/>
+      <c r="G73" s="119"/>
+      <c r="H73" s="120"/>
+      <c r="I73" s="119"/>
+      <c r="J73" s="120"/>
+      <c r="K73" s="119"/>
+      <c r="L73" s="120"/>
+      <c r="M73" s="119"/>
+      <c r="N73" s="120"/>
       <c r="O73" s="1"/>
       <c r="P73" s="1"/>
     </row>
@@ -4689,53 +4539,53 @@
     </row>
     <row r="75" spans="6:16">
       <c r="F75" s="7"/>
-      <c r="G75" s="106"/>
-      <c r="H75" s="107"/>
-      <c r="I75" s="106"/>
-      <c r="J75" s="107"/>
-      <c r="K75" s="106"/>
-      <c r="L75" s="107"/>
-      <c r="M75" s="106"/>
-      <c r="N75" s="107"/>
+      <c r="G75" s="116"/>
+      <c r="H75" s="117"/>
+      <c r="I75" s="116"/>
+      <c r="J75" s="117"/>
+      <c r="K75" s="116"/>
+      <c r="L75" s="117"/>
+      <c r="M75" s="116"/>
+      <c r="N75" s="117"/>
       <c r="O75" s="1"/>
       <c r="P75" s="1"/>
     </row>
     <row r="76" spans="6:16">
       <c r="F76" s="7"/>
-      <c r="G76" s="103"/>
-      <c r="H76" s="104"/>
-      <c r="I76" s="103"/>
-      <c r="J76" s="104"/>
-      <c r="K76" s="103"/>
-      <c r="L76" s="104"/>
-      <c r="M76" s="103"/>
-      <c r="N76" s="104"/>
+      <c r="G76" s="112"/>
+      <c r="H76" s="113"/>
+      <c r="I76" s="112"/>
+      <c r="J76" s="113"/>
+      <c r="K76" s="112"/>
+      <c r="L76" s="113"/>
+      <c r="M76" s="112"/>
+      <c r="N76" s="113"/>
       <c r="O76" s="1"/>
       <c r="P76" s="1"/>
     </row>
     <row r="77" spans="6:16">
       <c r="F77" s="15"/>
-      <c r="G77" s="103"/>
-      <c r="H77" s="104"/>
-      <c r="I77" s="103"/>
-      <c r="J77" s="104"/>
-      <c r="K77" s="103"/>
-      <c r="L77" s="104"/>
-      <c r="M77" s="103"/>
-      <c r="N77" s="104"/>
+      <c r="G77" s="112"/>
+      <c r="H77" s="113"/>
+      <c r="I77" s="112"/>
+      <c r="J77" s="113"/>
+      <c r="K77" s="112"/>
+      <c r="L77" s="113"/>
+      <c r="M77" s="112"/>
+      <c r="N77" s="113"/>
       <c r="O77" s="1"/>
       <c r="P77" s="1"/>
     </row>
     <row r="79" spans="6:16" ht="15.75" thickBot="1">
-      <c r="F79" s="105"/>
-      <c r="G79" s="105"/>
-      <c r="H79" s="105"/>
-      <c r="I79" s="105"/>
-      <c r="J79" s="105"/>
-      <c r="K79" s="105"/>
-      <c r="L79" s="105"/>
-      <c r="M79" s="105"/>
-      <c r="N79" s="105"/>
+      <c r="F79" s="118"/>
+      <c r="G79" s="118"/>
+      <c r="H79" s="118"/>
+      <c r="I79" s="118"/>
+      <c r="J79" s="118"/>
+      <c r="K79" s="118"/>
+      <c r="L79" s="118"/>
+      <c r="M79" s="118"/>
+      <c r="N79" s="118"/>
       <c r="O79" s="1"/>
       <c r="P79" s="1"/>
     </row>
@@ -4871,14 +4721,14 @@
     </row>
     <row r="86" spans="6:26" ht="15.75" thickBot="1">
       <c r="F86" s="12"/>
-      <c r="G86" s="108"/>
-      <c r="H86" s="109"/>
-      <c r="I86" s="108"/>
-      <c r="J86" s="109"/>
-      <c r="K86" s="108"/>
-      <c r="L86" s="109"/>
-      <c r="M86" s="108"/>
-      <c r="N86" s="109"/>
+      <c r="G86" s="119"/>
+      <c r="H86" s="120"/>
+      <c r="I86" s="119"/>
+      <c r="J86" s="120"/>
+      <c r="K86" s="119"/>
+      <c r="L86" s="120"/>
+      <c r="M86" s="119"/>
+      <c r="N86" s="120"/>
       <c r="O86" s="1"/>
       <c r="P86" s="1"/>
       <c r="Q86" s="1"/>
@@ -4917,14 +4767,14 @@
     </row>
     <row r="88" spans="6:26">
       <c r="F88" s="7"/>
-      <c r="G88" s="106"/>
-      <c r="H88" s="107"/>
-      <c r="I88" s="106"/>
-      <c r="J88" s="107"/>
-      <c r="K88" s="106"/>
-      <c r="L88" s="107"/>
-      <c r="M88" s="106"/>
-      <c r="N88" s="107"/>
+      <c r="G88" s="116"/>
+      <c r="H88" s="117"/>
+      <c r="I88" s="116"/>
+      <c r="J88" s="117"/>
+      <c r="K88" s="116"/>
+      <c r="L88" s="117"/>
+      <c r="M88" s="116"/>
+      <c r="N88" s="117"/>
       <c r="O88" s="1"/>
       <c r="P88" s="1"/>
       <c r="Q88" s="1"/>
@@ -4940,14 +4790,14 @@
     </row>
     <row r="89" spans="6:26">
       <c r="F89" s="7"/>
-      <c r="G89" s="103"/>
-      <c r="H89" s="104"/>
-      <c r="I89" s="103"/>
-      <c r="J89" s="104"/>
-      <c r="K89" s="103"/>
-      <c r="L89" s="104"/>
-      <c r="M89" s="103"/>
-      <c r="N89" s="104"/>
+      <c r="G89" s="112"/>
+      <c r="H89" s="113"/>
+      <c r="I89" s="112"/>
+      <c r="J89" s="113"/>
+      <c r="K89" s="112"/>
+      <c r="L89" s="113"/>
+      <c r="M89" s="112"/>
+      <c r="N89" s="113"/>
       <c r="O89" s="1"/>
       <c r="P89" s="1"/>
       <c r="Q89" s="1"/>
@@ -4963,14 +4813,14 @@
     </row>
     <row r="90" spans="6:26">
       <c r="F90" s="15"/>
-      <c r="G90" s="103"/>
-      <c r="H90" s="104"/>
-      <c r="I90" s="103"/>
-      <c r="J90" s="104"/>
-      <c r="K90" s="103"/>
-      <c r="L90" s="104"/>
-      <c r="M90" s="103"/>
-      <c r="N90" s="104"/>
+      <c r="G90" s="112"/>
+      <c r="H90" s="113"/>
+      <c r="I90" s="112"/>
+      <c r="J90" s="113"/>
+      <c r="K90" s="112"/>
+      <c r="L90" s="113"/>
+      <c r="M90" s="112"/>
+      <c r="N90" s="113"/>
       <c r="O90" s="1"/>
       <c r="P90" s="1"/>
       <c r="Q90" s="1"/>
@@ -5008,15 +4858,15 @@
       <c r="Z91" s="1"/>
     </row>
     <row r="92" spans="6:26">
-      <c r="F92" s="105"/>
-      <c r="G92" s="105"/>
-      <c r="H92" s="105"/>
-      <c r="I92" s="105"/>
-      <c r="J92" s="105"/>
-      <c r="K92" s="105"/>
-      <c r="L92" s="105"/>
-      <c r="M92" s="105"/>
-      <c r="N92" s="105"/>
+      <c r="F92" s="118"/>
+      <c r="G92" s="118"/>
+      <c r="H92" s="118"/>
+      <c r="I92" s="118"/>
+      <c r="J92" s="118"/>
+      <c r="K92" s="118"/>
+      <c r="L92" s="118"/>
+      <c r="M92" s="118"/>
+      <c r="N92" s="118"/>
       <c r="O92" s="1"/>
       <c r="P92" s="1"/>
       <c r="Q92" s="1"/>
@@ -5166,14 +5016,14 @@
     </row>
     <row r="99" spans="6:23" ht="15.75" customHeight="1">
       <c r="F99" s="12"/>
-      <c r="G99" s="108"/>
-      <c r="H99" s="109"/>
-      <c r="I99" s="108"/>
-      <c r="J99" s="109"/>
-      <c r="K99" s="108"/>
-      <c r="L99" s="109"/>
-      <c r="M99" s="108"/>
-      <c r="N99" s="109"/>
+      <c r="G99" s="119"/>
+      <c r="H99" s="120"/>
+      <c r="I99" s="119"/>
+      <c r="J99" s="120"/>
+      <c r="K99" s="119"/>
+      <c r="L99" s="120"/>
+      <c r="M99" s="119"/>
+      <c r="N99" s="120"/>
       <c r="O99" s="1"/>
       <c r="P99" s="1"/>
       <c r="Q99" s="1"/>
@@ -5206,14 +5056,14 @@
     </row>
     <row r="101" spans="6:23">
       <c r="F101" s="7"/>
-      <c r="G101" s="106"/>
-      <c r="H101" s="107"/>
-      <c r="I101" s="106"/>
-      <c r="J101" s="107"/>
-      <c r="K101" s="106"/>
-      <c r="L101" s="107"/>
-      <c r="M101" s="106"/>
-      <c r="N101" s="107"/>
+      <c r="G101" s="116"/>
+      <c r="H101" s="117"/>
+      <c r="I101" s="116"/>
+      <c r="J101" s="117"/>
+      <c r="K101" s="116"/>
+      <c r="L101" s="117"/>
+      <c r="M101" s="116"/>
+      <c r="N101" s="117"/>
       <c r="O101" s="1"/>
       <c r="P101" s="1"/>
       <c r="Q101" s="1"/>
@@ -5226,14 +5076,14 @@
     </row>
     <row r="102" spans="6:23">
       <c r="F102" s="7"/>
-      <c r="G102" s="103"/>
-      <c r="H102" s="104"/>
-      <c r="I102" s="103"/>
-      <c r="J102" s="104"/>
-      <c r="K102" s="103"/>
-      <c r="L102" s="104"/>
-      <c r="M102" s="103"/>
-      <c r="N102" s="104"/>
+      <c r="G102" s="112"/>
+      <c r="H102" s="113"/>
+      <c r="I102" s="112"/>
+      <c r="J102" s="113"/>
+      <c r="K102" s="112"/>
+      <c r="L102" s="113"/>
+      <c r="M102" s="112"/>
+      <c r="N102" s="113"/>
       <c r="O102" s="1"/>
       <c r="P102" s="1"/>
       <c r="Q102" s="1"/>
@@ -5246,14 +5096,14 @@
     </row>
     <row r="103" spans="6:23">
       <c r="F103" s="15"/>
-      <c r="G103" s="103"/>
-      <c r="H103" s="104"/>
-      <c r="I103" s="103"/>
-      <c r="J103" s="104"/>
-      <c r="K103" s="103"/>
-      <c r="L103" s="104"/>
-      <c r="M103" s="103"/>
-      <c r="N103" s="104"/>
+      <c r="G103" s="112"/>
+      <c r="H103" s="113"/>
+      <c r="I103" s="112"/>
+      <c r="J103" s="113"/>
+      <c r="K103" s="112"/>
+      <c r="L103" s="113"/>
+      <c r="M103" s="112"/>
+      <c r="N103" s="113"/>
       <c r="O103" s="1"/>
       <c r="P103" s="1"/>
       <c r="Q103" s="1"/>
@@ -5265,15 +5115,15 @@
       <c r="W103" s="97"/>
     </row>
     <row r="105" spans="6:23">
-      <c r="F105" s="105"/>
-      <c r="G105" s="105"/>
-      <c r="H105" s="105"/>
-      <c r="I105" s="105"/>
-      <c r="J105" s="105"/>
-      <c r="K105" s="105"/>
-      <c r="L105" s="105"/>
-      <c r="M105" s="105"/>
-      <c r="N105" s="105"/>
+      <c r="F105" s="118"/>
+      <c r="G105" s="118"/>
+      <c r="H105" s="118"/>
+      <c r="I105" s="118"/>
+      <c r="J105" s="118"/>
+      <c r="K105" s="118"/>
+      <c r="L105" s="118"/>
+      <c r="M105" s="118"/>
+      <c r="N105" s="118"/>
       <c r="O105" s="1"/>
       <c r="P105" s="1"/>
       <c r="Q105" s="1"/>
@@ -5408,14 +5258,14 @@
     </row>
     <row r="112" spans="6:23" ht="15.75" customHeight="1">
       <c r="F112" s="12"/>
-      <c r="G112" s="108"/>
-      <c r="H112" s="109"/>
-      <c r="I112" s="108"/>
-      <c r="J112" s="109"/>
-      <c r="K112" s="108"/>
-      <c r="L112" s="109"/>
-      <c r="M112" s="108"/>
-      <c r="N112" s="109"/>
+      <c r="G112" s="119"/>
+      <c r="H112" s="120"/>
+      <c r="I112" s="119"/>
+      <c r="J112" s="120"/>
+      <c r="K112" s="119"/>
+      <c r="L112" s="120"/>
+      <c r="M112" s="119"/>
+      <c r="N112" s="120"/>
       <c r="O112" s="1"/>
       <c r="P112" s="1"/>
       <c r="Q112" s="1"/>
@@ -5448,14 +5298,14 @@
     </row>
     <row r="114" spans="6:23">
       <c r="F114" s="7"/>
-      <c r="G114" s="106"/>
-      <c r="H114" s="107"/>
-      <c r="I114" s="106"/>
-      <c r="J114" s="107"/>
-      <c r="K114" s="106"/>
-      <c r="L114" s="107"/>
-      <c r="M114" s="106"/>
-      <c r="N114" s="107"/>
+      <c r="G114" s="116"/>
+      <c r="H114" s="117"/>
+      <c r="I114" s="116"/>
+      <c r="J114" s="117"/>
+      <c r="K114" s="116"/>
+      <c r="L114" s="117"/>
+      <c r="M114" s="116"/>
+      <c r="N114" s="117"/>
       <c r="O114" s="1"/>
       <c r="P114" s="1"/>
       <c r="Q114" s="1"/>
@@ -5476,14 +5326,14 @@
     </row>
     <row r="115" spans="6:23">
       <c r="F115" s="7"/>
-      <c r="G115" s="103"/>
-      <c r="H115" s="104"/>
-      <c r="I115" s="103"/>
-      <c r="J115" s="104"/>
-      <c r="K115" s="103"/>
-      <c r="L115" s="104"/>
-      <c r="M115" s="103"/>
-      <c r="N115" s="104"/>
+      <c r="G115" s="112"/>
+      <c r="H115" s="113"/>
+      <c r="I115" s="112"/>
+      <c r="J115" s="113"/>
+      <c r="K115" s="112"/>
+      <c r="L115" s="113"/>
+      <c r="M115" s="112"/>
+      <c r="N115" s="113"/>
       <c r="O115" s="1"/>
       <c r="P115" s="1"/>
       <c r="Q115" s="1"/>
@@ -5496,14 +5346,14 @@
     </row>
     <row r="116" spans="6:23">
       <c r="F116" s="15"/>
-      <c r="G116" s="103"/>
-      <c r="H116" s="104"/>
-      <c r="I116" s="103"/>
-      <c r="J116" s="104"/>
-      <c r="K116" s="103"/>
-      <c r="L116" s="104"/>
-      <c r="M116" s="103"/>
-      <c r="N116" s="104"/>
+      <c r="G116" s="112"/>
+      <c r="H116" s="113"/>
+      <c r="I116" s="112"/>
+      <c r="J116" s="113"/>
+      <c r="K116" s="112"/>
+      <c r="L116" s="113"/>
+      <c r="M116" s="112"/>
+      <c r="N116" s="113"/>
       <c r="O116" s="1"/>
       <c r="P116" s="1"/>
       <c r="Q116" s="1"/>
@@ -5515,15 +5365,15 @@
       <c r="W116" s="1"/>
     </row>
     <row r="118" spans="6:23">
-      <c r="F118" s="105"/>
-      <c r="G118" s="105"/>
-      <c r="H118" s="105"/>
-      <c r="I118" s="105"/>
-      <c r="J118" s="105"/>
-      <c r="K118" s="105"/>
-      <c r="L118" s="105"/>
-      <c r="M118" s="105"/>
-      <c r="N118" s="105"/>
+      <c r="F118" s="118"/>
+      <c r="G118" s="118"/>
+      <c r="H118" s="118"/>
+      <c r="I118" s="118"/>
+      <c r="J118" s="118"/>
+      <c r="K118" s="118"/>
+      <c r="L118" s="118"/>
+      <c r="M118" s="118"/>
+      <c r="N118" s="118"/>
       <c r="O118" s="1"/>
       <c r="P118" s="1"/>
       <c r="Q118" s="1"/>
@@ -5658,14 +5508,14 @@
     </row>
     <row r="125" spans="6:23" ht="15.75" customHeight="1">
       <c r="F125" s="12"/>
-      <c r="G125" s="108"/>
-      <c r="H125" s="109"/>
-      <c r="I125" s="108"/>
-      <c r="J125" s="109"/>
-      <c r="K125" s="108"/>
-      <c r="L125" s="109"/>
-      <c r="M125" s="108"/>
-      <c r="N125" s="109"/>
+      <c r="G125" s="119"/>
+      <c r="H125" s="120"/>
+      <c r="I125" s="119"/>
+      <c r="J125" s="120"/>
+      <c r="K125" s="119"/>
+      <c r="L125" s="120"/>
+      <c r="M125" s="119"/>
+      <c r="N125" s="120"/>
       <c r="O125" s="1"/>
       <c r="P125" s="1"/>
       <c r="Q125" s="1"/>
@@ -5698,14 +5548,14 @@
     </row>
     <row r="127" spans="6:23">
       <c r="F127" s="7"/>
-      <c r="G127" s="106"/>
-      <c r="H127" s="107"/>
-      <c r="I127" s="106"/>
-      <c r="J127" s="107"/>
-      <c r="K127" s="106"/>
-      <c r="L127" s="107"/>
-      <c r="M127" s="106"/>
-      <c r="N127" s="107"/>
+      <c r="G127" s="116"/>
+      <c r="H127" s="117"/>
+      <c r="I127" s="116"/>
+      <c r="J127" s="117"/>
+      <c r="K127" s="116"/>
+      <c r="L127" s="117"/>
+      <c r="M127" s="116"/>
+      <c r="N127" s="117"/>
       <c r="O127" s="1"/>
       <c r="P127" s="1" t="s">
         <v>10</v>
@@ -5724,14 +5574,14 @@
     </row>
     <row r="128" spans="6:23">
       <c r="F128" s="7"/>
-      <c r="G128" s="103"/>
-      <c r="H128" s="104"/>
-      <c r="I128" s="113"/>
-      <c r="J128" s="114"/>
-      <c r="K128" s="106"/>
-      <c r="L128" s="107"/>
-      <c r="M128" s="106"/>
-      <c r="N128" s="107"/>
+      <c r="G128" s="112"/>
+      <c r="H128" s="113"/>
+      <c r="I128" s="114"/>
+      <c r="J128" s="115"/>
+      <c r="K128" s="116"/>
+      <c r="L128" s="117"/>
+      <c r="M128" s="116"/>
+      <c r="N128" s="117"/>
       <c r="O128" s="1"/>
       <c r="P128" s="1">
         <v>37.5</v>
@@ -5753,14 +5603,14 @@
     </row>
     <row r="129" spans="6:23">
       <c r="F129" s="15"/>
-      <c r="G129" s="103"/>
-      <c r="H129" s="104"/>
-      <c r="I129" s="103"/>
-      <c r="J129" s="104"/>
-      <c r="K129" s="103"/>
-      <c r="L129" s="104"/>
-      <c r="M129" s="103"/>
-      <c r="N129" s="104"/>
+      <c r="G129" s="112"/>
+      <c r="H129" s="113"/>
+      <c r="I129" s="112"/>
+      <c r="J129" s="113"/>
+      <c r="K129" s="112"/>
+      <c r="L129" s="113"/>
+      <c r="M129" s="112"/>
+      <c r="N129" s="113"/>
       <c r="O129" s="1"/>
       <c r="P129" s="1">
         <v>28.125</v>
@@ -5782,110 +5632,54 @@
     </row>
   </sheetData>
   <mergeCells count="176">
-    <mergeCell ref="G128:H128"/>
-    <mergeCell ref="I128:J128"/>
-    <mergeCell ref="K128:L128"/>
-    <mergeCell ref="M128:N128"/>
-    <mergeCell ref="G129:H129"/>
-    <mergeCell ref="I129:J129"/>
-    <mergeCell ref="K129:L129"/>
-    <mergeCell ref="M129:N129"/>
-    <mergeCell ref="F118:N118"/>
-    <mergeCell ref="G125:H125"/>
-    <mergeCell ref="I125:J125"/>
-    <mergeCell ref="K125:L125"/>
-    <mergeCell ref="M125:N125"/>
-    <mergeCell ref="G127:H127"/>
-    <mergeCell ref="I127:J127"/>
-    <mergeCell ref="K127:L127"/>
-    <mergeCell ref="M127:N127"/>
-    <mergeCell ref="G114:H114"/>
-    <mergeCell ref="I114:J114"/>
-    <mergeCell ref="K114:L114"/>
-    <mergeCell ref="M114:N114"/>
-    <mergeCell ref="G115:H115"/>
-    <mergeCell ref="I115:J115"/>
-    <mergeCell ref="K115:L115"/>
-    <mergeCell ref="M115:N115"/>
-    <mergeCell ref="G116:H116"/>
-    <mergeCell ref="I116:J116"/>
-    <mergeCell ref="K116:L116"/>
-    <mergeCell ref="M116:N116"/>
-    <mergeCell ref="G103:H103"/>
-    <mergeCell ref="I103:J103"/>
-    <mergeCell ref="K103:L103"/>
-    <mergeCell ref="M103:N103"/>
-    <mergeCell ref="F105:N105"/>
-    <mergeCell ref="G112:H112"/>
-    <mergeCell ref="I112:J112"/>
-    <mergeCell ref="K112:L112"/>
-    <mergeCell ref="M112:N112"/>
-    <mergeCell ref="G99:H99"/>
-    <mergeCell ref="I99:J99"/>
-    <mergeCell ref="K99:L99"/>
-    <mergeCell ref="M99:N99"/>
-    <mergeCell ref="G101:H101"/>
-    <mergeCell ref="I101:J101"/>
-    <mergeCell ref="K101:L101"/>
-    <mergeCell ref="M101:N101"/>
-    <mergeCell ref="G102:H102"/>
-    <mergeCell ref="I102:J102"/>
-    <mergeCell ref="K102:L102"/>
-    <mergeCell ref="M102:N102"/>
-    <mergeCell ref="G89:H89"/>
-    <mergeCell ref="I89:J89"/>
-    <mergeCell ref="K89:L89"/>
-    <mergeCell ref="M89:N89"/>
-    <mergeCell ref="G90:H90"/>
-    <mergeCell ref="I90:J90"/>
-    <mergeCell ref="K90:L90"/>
-    <mergeCell ref="M90:N90"/>
-    <mergeCell ref="F92:N92"/>
-    <mergeCell ref="F79:N79"/>
-    <mergeCell ref="G86:H86"/>
-    <mergeCell ref="I86:J86"/>
-    <mergeCell ref="K86:L86"/>
-    <mergeCell ref="M86:N86"/>
-    <mergeCell ref="G88:H88"/>
-    <mergeCell ref="I88:J88"/>
-    <mergeCell ref="K88:L88"/>
-    <mergeCell ref="M88:N88"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="M10:N10"/>
-    <mergeCell ref="K10:L10"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="M8:N8"/>
-    <mergeCell ref="K8:L8"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="F1:N1"/>
-    <mergeCell ref="M36:N36"/>
-    <mergeCell ref="G47:H47"/>
-    <mergeCell ref="I47:J47"/>
-    <mergeCell ref="K47:L47"/>
-    <mergeCell ref="M47:N47"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="K12:L12"/>
-    <mergeCell ref="M12:N12"/>
-    <mergeCell ref="G64:H64"/>
-    <mergeCell ref="I64:J64"/>
-    <mergeCell ref="K64:L64"/>
-    <mergeCell ref="M64:N64"/>
-    <mergeCell ref="G51:H51"/>
-    <mergeCell ref="I51:J51"/>
-    <mergeCell ref="K51:L51"/>
-    <mergeCell ref="M51:N51"/>
-    <mergeCell ref="G60:H60"/>
-    <mergeCell ref="I60:J60"/>
-    <mergeCell ref="K60:L60"/>
-    <mergeCell ref="M60:N60"/>
-    <mergeCell ref="G62:H62"/>
-    <mergeCell ref="I62:J62"/>
-    <mergeCell ref="K62:L62"/>
-    <mergeCell ref="M62:N62"/>
+    <mergeCell ref="G77:H77"/>
+    <mergeCell ref="I77:J77"/>
+    <mergeCell ref="K77:L77"/>
+    <mergeCell ref="M77:N77"/>
+    <mergeCell ref="R2:Z2"/>
+    <mergeCell ref="R6:Z6"/>
+    <mergeCell ref="R9:Z9"/>
+    <mergeCell ref="R12:Z12"/>
+    <mergeCell ref="G75:H75"/>
+    <mergeCell ref="I75:J75"/>
+    <mergeCell ref="K75:L75"/>
+    <mergeCell ref="M75:N75"/>
+    <mergeCell ref="G76:H76"/>
+    <mergeCell ref="I76:J76"/>
+    <mergeCell ref="K76:L76"/>
+    <mergeCell ref="M76:N76"/>
+    <mergeCell ref="F66:N66"/>
+    <mergeCell ref="G73:H73"/>
+    <mergeCell ref="I73:J73"/>
+    <mergeCell ref="K73:L73"/>
+    <mergeCell ref="M73:N73"/>
+    <mergeCell ref="G50:H50"/>
+    <mergeCell ref="I50:J50"/>
+    <mergeCell ref="K50:L50"/>
+    <mergeCell ref="M50:N50"/>
+    <mergeCell ref="G63:H63"/>
+    <mergeCell ref="I63:J63"/>
+    <mergeCell ref="K63:L63"/>
+    <mergeCell ref="M63:N63"/>
+    <mergeCell ref="F14:N14"/>
+    <mergeCell ref="F27:N27"/>
+    <mergeCell ref="F40:N40"/>
+    <mergeCell ref="F53:N53"/>
+    <mergeCell ref="G38:H38"/>
+    <mergeCell ref="I38:J38"/>
+    <mergeCell ref="K38:L38"/>
+    <mergeCell ref="M38:N38"/>
+    <mergeCell ref="G49:H49"/>
+    <mergeCell ref="I49:J49"/>
+    <mergeCell ref="K49:L49"/>
+    <mergeCell ref="M49:N49"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="K23:L23"/>
+    <mergeCell ref="M23:N23"/>
+    <mergeCell ref="G36:H36"/>
+    <mergeCell ref="I36:J36"/>
+    <mergeCell ref="K36:L36"/>
     <mergeCell ref="M11:N11"/>
     <mergeCell ref="K11:L11"/>
     <mergeCell ref="I11:J11"/>
@@ -5910,54 +5704,110 @@
     <mergeCell ref="I25:J25"/>
     <mergeCell ref="K25:L25"/>
     <mergeCell ref="M25:N25"/>
-    <mergeCell ref="M50:N50"/>
-    <mergeCell ref="G63:H63"/>
-    <mergeCell ref="I63:J63"/>
-    <mergeCell ref="K63:L63"/>
-    <mergeCell ref="M63:N63"/>
-    <mergeCell ref="F14:N14"/>
-    <mergeCell ref="F27:N27"/>
-    <mergeCell ref="F40:N40"/>
-    <mergeCell ref="F53:N53"/>
-    <mergeCell ref="G38:H38"/>
-    <mergeCell ref="I38:J38"/>
-    <mergeCell ref="K38:L38"/>
-    <mergeCell ref="M38:N38"/>
-    <mergeCell ref="G49:H49"/>
-    <mergeCell ref="I49:J49"/>
-    <mergeCell ref="K49:L49"/>
-    <mergeCell ref="M49:N49"/>
-    <mergeCell ref="G23:H23"/>
-    <mergeCell ref="I23:J23"/>
-    <mergeCell ref="K23:L23"/>
-    <mergeCell ref="M23:N23"/>
-    <mergeCell ref="G36:H36"/>
-    <mergeCell ref="I36:J36"/>
-    <mergeCell ref="K36:L36"/>
-    <mergeCell ref="G77:H77"/>
-    <mergeCell ref="I77:J77"/>
-    <mergeCell ref="K77:L77"/>
-    <mergeCell ref="M77:N77"/>
-    <mergeCell ref="R2:Z2"/>
-    <mergeCell ref="R6:Z6"/>
-    <mergeCell ref="R9:Z9"/>
-    <mergeCell ref="R12:Z12"/>
-    <mergeCell ref="G75:H75"/>
-    <mergeCell ref="I75:J75"/>
-    <mergeCell ref="K75:L75"/>
-    <mergeCell ref="M75:N75"/>
-    <mergeCell ref="G76:H76"/>
-    <mergeCell ref="I76:J76"/>
-    <mergeCell ref="K76:L76"/>
-    <mergeCell ref="M76:N76"/>
-    <mergeCell ref="F66:N66"/>
-    <mergeCell ref="G73:H73"/>
-    <mergeCell ref="I73:J73"/>
-    <mergeCell ref="K73:L73"/>
-    <mergeCell ref="M73:N73"/>
-    <mergeCell ref="G50:H50"/>
-    <mergeCell ref="I50:J50"/>
-    <mergeCell ref="K50:L50"/>
+    <mergeCell ref="G64:H64"/>
+    <mergeCell ref="I64:J64"/>
+    <mergeCell ref="K64:L64"/>
+    <mergeCell ref="M64:N64"/>
+    <mergeCell ref="G51:H51"/>
+    <mergeCell ref="I51:J51"/>
+    <mergeCell ref="K51:L51"/>
+    <mergeCell ref="M51:N51"/>
+    <mergeCell ref="G60:H60"/>
+    <mergeCell ref="I60:J60"/>
+    <mergeCell ref="K60:L60"/>
+    <mergeCell ref="M60:N60"/>
+    <mergeCell ref="G62:H62"/>
+    <mergeCell ref="I62:J62"/>
+    <mergeCell ref="K62:L62"/>
+    <mergeCell ref="M62:N62"/>
+    <mergeCell ref="M36:N36"/>
+    <mergeCell ref="G47:H47"/>
+    <mergeCell ref="I47:J47"/>
+    <mergeCell ref="K47:L47"/>
+    <mergeCell ref="M47:N47"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="K12:L12"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="M10:N10"/>
+    <mergeCell ref="K10:L10"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="M8:N8"/>
+    <mergeCell ref="K8:L8"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="F1:N1"/>
+    <mergeCell ref="F79:N79"/>
+    <mergeCell ref="G86:H86"/>
+    <mergeCell ref="I86:J86"/>
+    <mergeCell ref="K86:L86"/>
+    <mergeCell ref="M86:N86"/>
+    <mergeCell ref="G88:H88"/>
+    <mergeCell ref="I88:J88"/>
+    <mergeCell ref="K88:L88"/>
+    <mergeCell ref="M88:N88"/>
+    <mergeCell ref="G89:H89"/>
+    <mergeCell ref="I89:J89"/>
+    <mergeCell ref="K89:L89"/>
+    <mergeCell ref="M89:N89"/>
+    <mergeCell ref="G90:H90"/>
+    <mergeCell ref="I90:J90"/>
+    <mergeCell ref="K90:L90"/>
+    <mergeCell ref="M90:N90"/>
+    <mergeCell ref="F92:N92"/>
+    <mergeCell ref="G99:H99"/>
+    <mergeCell ref="I99:J99"/>
+    <mergeCell ref="K99:L99"/>
+    <mergeCell ref="M99:N99"/>
+    <mergeCell ref="G101:H101"/>
+    <mergeCell ref="I101:J101"/>
+    <mergeCell ref="K101:L101"/>
+    <mergeCell ref="M101:N101"/>
+    <mergeCell ref="G102:H102"/>
+    <mergeCell ref="I102:J102"/>
+    <mergeCell ref="K102:L102"/>
+    <mergeCell ref="M102:N102"/>
+    <mergeCell ref="G103:H103"/>
+    <mergeCell ref="I103:J103"/>
+    <mergeCell ref="K103:L103"/>
+    <mergeCell ref="M103:N103"/>
+    <mergeCell ref="F105:N105"/>
+    <mergeCell ref="G112:H112"/>
+    <mergeCell ref="I112:J112"/>
+    <mergeCell ref="K112:L112"/>
+    <mergeCell ref="M112:N112"/>
+    <mergeCell ref="G114:H114"/>
+    <mergeCell ref="I114:J114"/>
+    <mergeCell ref="K114:L114"/>
+    <mergeCell ref="M114:N114"/>
+    <mergeCell ref="G115:H115"/>
+    <mergeCell ref="I115:J115"/>
+    <mergeCell ref="K115:L115"/>
+    <mergeCell ref="M115:N115"/>
+    <mergeCell ref="G116:H116"/>
+    <mergeCell ref="I116:J116"/>
+    <mergeCell ref="K116:L116"/>
+    <mergeCell ref="M116:N116"/>
+    <mergeCell ref="G128:H128"/>
+    <mergeCell ref="I128:J128"/>
+    <mergeCell ref="K128:L128"/>
+    <mergeCell ref="M128:N128"/>
+    <mergeCell ref="G129:H129"/>
+    <mergeCell ref="I129:J129"/>
+    <mergeCell ref="K129:L129"/>
+    <mergeCell ref="M129:N129"/>
+    <mergeCell ref="F118:N118"/>
+    <mergeCell ref="G125:H125"/>
+    <mergeCell ref="I125:J125"/>
+    <mergeCell ref="K125:L125"/>
+    <mergeCell ref="M125:N125"/>
+    <mergeCell ref="G127:H127"/>
+    <mergeCell ref="I127:J127"/>
+    <mergeCell ref="K127:L127"/>
+    <mergeCell ref="M127:N127"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -6931,19 +6781,19 @@
       <c r="F1" s="2"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
-      <c r="I1" s="116" t="s">
+      <c r="I1" s="124" t="s">
         <v>34</v>
       </c>
-      <c r="J1" s="116"/>
-      <c r="K1" s="116"/>
-      <c r="L1" s="116"/>
-      <c r="M1" s="116"/>
-      <c r="N1" s="116"/>
-      <c r="O1" s="116"/>
-      <c r="P1" s="116"/>
-      <c r="Q1" s="116"/>
-      <c r="R1" s="116"/>
-      <c r="S1" s="116"/>
+      <c r="J1" s="124"/>
+      <c r="K1" s="124"/>
+      <c r="L1" s="124"/>
+      <c r="M1" s="124"/>
+      <c r="N1" s="124"/>
+      <c r="O1" s="124"/>
+      <c r="P1" s="124"/>
+      <c r="Q1" s="124"/>
+      <c r="R1" s="124"/>
+      <c r="S1" s="124"/>
     </row>
     <row r="2" spans="1:19">
       <c r="A2" s="111" t="s">
@@ -6964,20 +6814,20 @@
       </c>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
-      <c r="I2" s="116"/>
-      <c r="J2" s="116"/>
-      <c r="K2" s="116"/>
-      <c r="L2" s="116"/>
-      <c r="M2" s="116"/>
-      <c r="N2" s="116"/>
-      <c r="O2" s="116"/>
-      <c r="P2" s="116"/>
-      <c r="Q2" s="116"/>
-      <c r="R2" s="116"/>
-      <c r="S2" s="116"/>
+      <c r="I2" s="124"/>
+      <c r="J2" s="124"/>
+      <c r="K2" s="124"/>
+      <c r="L2" s="124"/>
+      <c r="M2" s="124"/>
+      <c r="N2" s="124"/>
+      <c r="O2" s="124"/>
+      <c r="P2" s="124"/>
+      <c r="Q2" s="124"/>
+      <c r="R2" s="124"/>
+      <c r="S2" s="124"/>
     </row>
     <row r="3" spans="1:19">
-      <c r="A3" s="115" t="s">
+      <c r="A3" s="123" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -7034,7 +6884,7 @@
       </c>
     </row>
     <row r="4" spans="1:19">
-      <c r="A4" s="115"/>
+      <c r="A4" s="123"/>
       <c r="B4" s="1" t="s">
         <v>47</v>
       </c>
@@ -7101,9 +6951,7 @@
       </c>
     </row>
     <row r="5" spans="1:19">
-      <c r="A5" s="115" t="s">
-        <v>19</v>
-      </c>
+      <c r="A5" s="123"/>
       <c r="B5" s="1" t="s">
         <v>36</v>
       </c>
@@ -7170,7 +7018,7 @@
       </c>
     </row>
     <row r="6" spans="1:19">
-      <c r="A6" s="115"/>
+      <c r="A6" s="123"/>
       <c r="B6" s="1" t="s">
         <v>47</v>
       </c>
@@ -7237,9 +7085,7 @@
       </c>
     </row>
     <row r="7" spans="1:19">
-      <c r="A7" s="115" t="s">
-        <v>22</v>
-      </c>
+      <c r="A7" s="123"/>
       <c r="B7" s="1" t="s">
         <v>36</v>
       </c>
@@ -7306,7 +7152,7 @@
       </c>
     </row>
     <row r="8" spans="1:19">
-      <c r="A8" s="115"/>
+      <c r="A8" s="123"/>
       <c r="B8" s="1" t="s">
         <v>47</v>
       </c>
@@ -7341,9 +7187,7 @@
       <c r="S8" s="1"/>
     </row>
     <row r="9" spans="1:19">
-      <c r="A9" s="115" t="s">
-        <v>25</v>
-      </c>
+      <c r="A9" s="123"/>
       <c r="B9" s="1" t="s">
         <v>36</v>
       </c>
@@ -7378,7 +7222,7 @@
       <c r="S9" s="1"/>
     </row>
     <row r="10" spans="1:19">
-      <c r="A10" s="115"/>
+      <c r="A10" s="123"/>
       <c r="B10" s="1" t="s">
         <v>47</v>
       </c>
@@ -7413,9 +7257,7 @@
       <c r="S10" s="1"/>
     </row>
     <row r="11" spans="1:19">
-      <c r="A11" s="115" t="s">
-        <v>52</v>
-      </c>
+      <c r="A11" s="123"/>
       <c r="B11" s="1" t="s">
         <v>36</v>
       </c>
@@ -7450,7 +7292,7 @@
       <c r="S11" s="1"/>
     </row>
     <row r="12" spans="1:19">
-      <c r="A12" s="115"/>
+      <c r="A12" s="123"/>
       <c r="B12" s="1" t="s">
         <v>47</v>
       </c>
@@ -7485,9 +7327,7 @@
       <c r="S12" s="1"/>
     </row>
     <row r="13" spans="1:19">
-      <c r="A13" s="115" t="s">
-        <v>53</v>
-      </c>
+      <c r="A13" s="123"/>
       <c r="B13" s="1" t="s">
         <v>36</v>
       </c>
@@ -7522,7 +7362,7 @@
       <c r="S13" s="1"/>
     </row>
     <row r="14" spans="1:19">
-      <c r="A14" s="115"/>
+      <c r="A14" s="123"/>
       <c r="B14" s="1" t="s">
         <v>47</v>
       </c>
@@ -7557,9 +7397,7 @@
       <c r="S14" s="1"/>
     </row>
     <row r="15" spans="1:19">
-      <c r="A15" s="115" t="s">
-        <v>54</v>
-      </c>
+      <c r="A15" s="123"/>
       <c r="B15" s="1" t="s">
         <v>36</v>
       </c>
@@ -7594,7 +7432,7 @@
       <c r="S15" s="1"/>
     </row>
     <row r="16" spans="1:19">
-      <c r="A16" s="115"/>
+      <c r="A16" s="123"/>
       <c r="B16" s="1" t="s">
         <v>47</v>
       </c>
@@ -7629,9 +7467,7 @@
       <c r="S16" s="1"/>
     </row>
     <row r="17" spans="1:7">
-      <c r="A17" s="115" t="s">
-        <v>55</v>
-      </c>
+      <c r="A17" s="123"/>
       <c r="B17" s="1" t="s">
         <v>36</v>
       </c>
@@ -7654,7 +7490,7 @@
       <c r="G17" s="1"/>
     </row>
     <row r="18" spans="1:7">
-      <c r="A18" s="115"/>
+      <c r="A18" s="123"/>
       <c r="B18" s="1" t="s">
         <v>47</v>
       </c>
@@ -7677,9 +7513,7 @@
       <c r="G18" s="1"/>
     </row>
     <row r="19" spans="1:7">
-      <c r="A19" s="115" t="s">
-        <v>56</v>
-      </c>
+      <c r="A19" s="123"/>
       <c r="B19" s="1" t="s">
         <v>36</v>
       </c>
@@ -7702,7 +7536,7 @@
       <c r="G19" s="1"/>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" s="115"/>
+      <c r="A20" s="123"/>
       <c r="B20" s="1" t="s">
         <v>47</v>
       </c>
@@ -7725,7 +7559,7 @@
       <c r="G20" s="1"/>
     </row>
     <row r="21" spans="1:7">
-      <c r="A21" s="115"/>
+      <c r="A21" s="123"/>
       <c r="B21" s="1" t="s">
         <v>36</v>
       </c>
@@ -7748,7 +7582,7 @@
       <c r="G21" s="1"/>
     </row>
     <row r="22" spans="1:7">
-      <c r="A22" s="115"/>
+      <c r="A22" s="123"/>
       <c r="B22" s="1" t="s">
         <v>47</v>
       </c>
@@ -7772,7 +7606,7 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="1" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="B24" s="1"/>
       <c r="C24" s="1">
@@ -7809,26 +7643,26 @@
         <v>35</v>
       </c>
       <c r="B26" s="111"/>
-      <c r="C26" s="101" t="s">
+      <c r="C26" s="102" t="s">
         <v>48</v>
       </c>
-      <c r="D26" s="101" t="s">
+      <c r="D26" s="102" t="s">
         <v>49</v>
       </c>
-      <c r="E26" s="101" t="s">
+      <c r="E26" s="102" t="s">
         <v>50</v>
       </c>
-      <c r="F26" s="101" t="s">
+      <c r="F26" s="102" t="s">
         <v>51</v>
       </c>
       <c r="G26" s="1"/>
     </row>
     <row r="27" spans="1:7">
-      <c r="A27" s="115" t="s">
+      <c r="A27" s="123" t="s">
         <v>2</v>
       </c>
-      <c r="B27" s="115" t="s">
-        <v>58</v>
+      <c r="B27" s="123" t="s">
+        <v>53</v>
       </c>
       <c r="C27" s="111">
         <f>Hoja1!H5</f>
@@ -7849,8 +7683,8 @@
       <c r="G27" s="111"/>
     </row>
     <row r="28" spans="1:7">
-      <c r="A28" s="115"/>
-      <c r="B28" s="115"/>
+      <c r="A28" s="123"/>
+      <c r="B28" s="123"/>
       <c r="C28" s="111"/>
       <c r="D28" s="111"/>
       <c r="E28" s="111"/>
@@ -7858,8 +7692,8 @@
       <c r="G28" s="111"/>
     </row>
     <row r="29" spans="1:7">
-      <c r="A29" s="115"/>
-      <c r="B29" s="115"/>
+      <c r="A29" s="123"/>
+      <c r="B29" s="123"/>
       <c r="C29" s="111"/>
       <c r="D29" s="111"/>
       <c r="E29" s="111"/>
@@ -7867,8 +7701,8 @@
       <c r="G29" s="111"/>
     </row>
     <row r="30" spans="1:7">
-      <c r="A30" s="115"/>
-      <c r="B30" s="115"/>
+      <c r="A30" s="123"/>
+      <c r="B30" s="123"/>
       <c r="C30" s="111"/>
       <c r="D30" s="111"/>
       <c r="E30" s="111"/>
@@ -7876,8 +7710,8 @@
       <c r="G30" s="111"/>
     </row>
     <row r="31" spans="1:7">
-      <c r="A31" s="115"/>
-      <c r="B31" s="115"/>
+      <c r="A31" s="123"/>
+      <c r="B31" s="123"/>
       <c r="C31" s="111"/>
       <c r="D31" s="111"/>
       <c r="E31" s="111"/>
@@ -7885,8 +7719,8 @@
       <c r="G31" s="111"/>
     </row>
     <row r="32" spans="1:7">
-      <c r="A32" s="115"/>
-      <c r="B32" s="115"/>
+      <c r="A32" s="123"/>
+      <c r="B32" s="123"/>
       <c r="C32" s="111"/>
       <c r="D32" s="111"/>
       <c r="E32" s="111"/>
@@ -7894,8 +7728,8 @@
       <c r="G32" s="111"/>
     </row>
     <row r="33" spans="1:7">
-      <c r="A33" s="115"/>
-      <c r="B33" s="115"/>
+      <c r="A33" s="123"/>
+      <c r="B33" s="123"/>
       <c r="C33" s="111"/>
       <c r="D33" s="111"/>
       <c r="E33" s="111"/>
@@ -7903,8 +7737,8 @@
       <c r="G33" s="111"/>
     </row>
     <row r="34" spans="1:7">
-      <c r="A34" s="115"/>
-      <c r="B34" s="115"/>
+      <c r="A34" s="123"/>
+      <c r="B34" s="123"/>
       <c r="C34" s="111"/>
       <c r="D34" s="111"/>
       <c r="E34" s="111"/>
@@ -7912,8 +7746,8 @@
       <c r="G34" s="111"/>
     </row>
     <row r="35" spans="1:7">
-      <c r="A35" s="115"/>
-      <c r="B35" s="115"/>
+      <c r="A35" s="123"/>
+      <c r="B35" s="123"/>
       <c r="C35" s="111"/>
       <c r="D35" s="111"/>
       <c r="E35" s="111"/>
@@ -7921,8 +7755,8 @@
       <c r="G35" s="111"/>
     </row>
     <row r="36" spans="1:7">
-      <c r="A36" s="115"/>
-      <c r="B36" s="115"/>
+      <c r="A36" s="123"/>
+      <c r="B36" s="123"/>
       <c r="C36" s="111"/>
       <c r="D36" s="111"/>
       <c r="E36" s="111"/>
@@ -7930,8 +7764,8 @@
       <c r="G36" s="111"/>
     </row>
     <row r="37" spans="1:7">
-      <c r="A37" s="115"/>
-      <c r="B37" s="115"/>
+      <c r="A37" s="123"/>
+      <c r="B37" s="123"/>
       <c r="C37" s="111"/>
       <c r="D37" s="111"/>
       <c r="E37" s="111"/>
@@ -7939,8 +7773,8 @@
       <c r="G37" s="111"/>
     </row>
     <row r="38" spans="1:7">
-      <c r="A38" s="115"/>
-      <c r="B38" s="115"/>
+      <c r="A38" s="123"/>
+      <c r="B38" s="123"/>
       <c r="C38" s="111"/>
       <c r="D38" s="111"/>
       <c r="E38" s="111"/>
@@ -7948,8 +7782,8 @@
       <c r="G38" s="111"/>
     </row>
     <row r="39" spans="1:7">
-      <c r="A39" s="115"/>
-      <c r="B39" s="115"/>
+      <c r="A39" s="123"/>
+      <c r="B39" s="123"/>
       <c r="C39" s="111"/>
       <c r="D39" s="111"/>
       <c r="E39" s="111"/>
@@ -7957,8 +7791,8 @@
       <c r="G39" s="111"/>
     </row>
     <row r="40" spans="1:7">
-      <c r="A40" s="115"/>
-      <c r="B40" s="115"/>
+      <c r="A40" s="123"/>
+      <c r="B40" s="123"/>
       <c r="C40" s="111"/>
       <c r="D40" s="111"/>
       <c r="E40" s="111"/>
@@ -7966,8 +7800,8 @@
       <c r="G40" s="111"/>
     </row>
     <row r="41" spans="1:7">
-      <c r="A41" s="115"/>
-      <c r="B41" s="115"/>
+      <c r="A41" s="123"/>
+      <c r="B41" s="123"/>
       <c r="C41" s="111"/>
       <c r="D41" s="111"/>
       <c r="E41" s="111"/>
@@ -7975,8 +7809,8 @@
       <c r="G41" s="111"/>
     </row>
     <row r="42" spans="1:7">
-      <c r="A42" s="115"/>
-      <c r="B42" s="115"/>
+      <c r="A42" s="123"/>
+      <c r="B42" s="123"/>
       <c r="C42" s="111"/>
       <c r="D42" s="111"/>
       <c r="E42" s="111"/>
@@ -7984,8 +7818,8 @@
       <c r="G42" s="111"/>
     </row>
     <row r="43" spans="1:7">
-      <c r="A43" s="115"/>
-      <c r="B43" s="115"/>
+      <c r="A43" s="123"/>
+      <c r="B43" s="123"/>
       <c r="C43" s="111"/>
       <c r="D43" s="111"/>
       <c r="E43" s="111"/>
@@ -7993,8 +7827,8 @@
       <c r="G43" s="111"/>
     </row>
     <row r="44" spans="1:7">
-      <c r="A44" s="115"/>
-      <c r="B44" s="115"/>
+      <c r="A44" s="123"/>
+      <c r="B44" s="123"/>
       <c r="C44" s="111"/>
       <c r="D44" s="111"/>
       <c r="E44" s="111"/>
@@ -8002,8 +7836,8 @@
       <c r="G44" s="111"/>
     </row>
     <row r="45" spans="1:7">
-      <c r="A45" s="115"/>
-      <c r="B45" s="115"/>
+      <c r="A45" s="123"/>
+      <c r="B45" s="123"/>
       <c r="C45" s="111"/>
       <c r="D45" s="111"/>
       <c r="E45" s="111"/>
@@ -8011,8 +7845,8 @@
       <c r="G45" s="111"/>
     </row>
     <row r="46" spans="1:7">
-      <c r="A46" s="115"/>
-      <c r="B46" s="115"/>
+      <c r="A46" s="123"/>
+      <c r="B46" s="123"/>
       <c r="C46" s="111"/>
       <c r="D46" s="111"/>
       <c r="E46" s="111"/>
@@ -8044,12 +7878,68 @@
     </row>
   </sheetData>
   <mergeCells count="84">
-    <mergeCell ref="A21:A22"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="G35:G36"/>
+    <mergeCell ref="G33:G34"/>
+    <mergeCell ref="G27:G28"/>
+    <mergeCell ref="G29:G30"/>
+    <mergeCell ref="G31:G32"/>
+    <mergeCell ref="G45:G46"/>
+    <mergeCell ref="G43:G44"/>
+    <mergeCell ref="G41:G42"/>
+    <mergeCell ref="G39:G40"/>
+    <mergeCell ref="G37:G38"/>
+    <mergeCell ref="C45:C46"/>
+    <mergeCell ref="D45:D46"/>
+    <mergeCell ref="E45:E46"/>
+    <mergeCell ref="F45:F46"/>
+    <mergeCell ref="C41:C42"/>
+    <mergeCell ref="D41:D42"/>
+    <mergeCell ref="E41:E42"/>
+    <mergeCell ref="F41:F42"/>
+    <mergeCell ref="C43:C44"/>
+    <mergeCell ref="D43:D44"/>
+    <mergeCell ref="E43:E44"/>
+    <mergeCell ref="F43:F44"/>
+    <mergeCell ref="C37:C38"/>
+    <mergeCell ref="D37:D38"/>
+    <mergeCell ref="E37:E38"/>
+    <mergeCell ref="F37:F38"/>
+    <mergeCell ref="C39:C40"/>
+    <mergeCell ref="D39:D40"/>
+    <mergeCell ref="E39:E40"/>
+    <mergeCell ref="F39:F40"/>
+    <mergeCell ref="C33:C34"/>
+    <mergeCell ref="D33:D34"/>
+    <mergeCell ref="E33:E34"/>
+    <mergeCell ref="F33:F34"/>
+    <mergeCell ref="C35:C36"/>
+    <mergeCell ref="D35:D36"/>
+    <mergeCell ref="E35:E36"/>
+    <mergeCell ref="F35:F36"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="E29:E30"/>
+    <mergeCell ref="F29:F30"/>
+    <mergeCell ref="C31:C32"/>
+    <mergeCell ref="D31:D32"/>
+    <mergeCell ref="E31:E32"/>
+    <mergeCell ref="F31:F32"/>
+    <mergeCell ref="A39:A40"/>
+    <mergeCell ref="A41:A42"/>
+    <mergeCell ref="A43:A44"/>
+    <mergeCell ref="A45:A46"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="B33:B34"/>
+    <mergeCell ref="B35:B36"/>
+    <mergeCell ref="B37:B38"/>
+    <mergeCell ref="B39:B40"/>
+    <mergeCell ref="B41:B42"/>
+    <mergeCell ref="B43:B44"/>
+    <mergeCell ref="B45:B46"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="A31:A32"/>
     <mergeCell ref="A33:A34"/>
     <mergeCell ref="A35:A36"/>
     <mergeCell ref="A37:A38"/>
@@ -8066,68 +7956,12 @@
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="A7:A8"/>
-    <mergeCell ref="A39:A40"/>
-    <mergeCell ref="A41:A42"/>
-    <mergeCell ref="A43:A44"/>
-    <mergeCell ref="A45:A46"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="B31:B32"/>
-    <mergeCell ref="B33:B34"/>
-    <mergeCell ref="B35:B36"/>
-    <mergeCell ref="B37:B38"/>
-    <mergeCell ref="B39:B40"/>
-    <mergeCell ref="B41:B42"/>
-    <mergeCell ref="B43:B44"/>
-    <mergeCell ref="B45:B46"/>
-    <mergeCell ref="A29:A30"/>
-    <mergeCell ref="A31:A32"/>
-    <mergeCell ref="C29:C30"/>
-    <mergeCell ref="D29:D30"/>
-    <mergeCell ref="E29:E30"/>
-    <mergeCell ref="F29:F30"/>
-    <mergeCell ref="C31:C32"/>
-    <mergeCell ref="D31:D32"/>
-    <mergeCell ref="E31:E32"/>
-    <mergeCell ref="F31:F32"/>
-    <mergeCell ref="C33:C34"/>
-    <mergeCell ref="D33:D34"/>
-    <mergeCell ref="E33:E34"/>
-    <mergeCell ref="F33:F34"/>
-    <mergeCell ref="C35:C36"/>
-    <mergeCell ref="D35:D36"/>
-    <mergeCell ref="E35:E36"/>
-    <mergeCell ref="F35:F36"/>
-    <mergeCell ref="C37:C38"/>
-    <mergeCell ref="D37:D38"/>
-    <mergeCell ref="E37:E38"/>
-    <mergeCell ref="F37:F38"/>
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="D39:D40"/>
-    <mergeCell ref="E39:E40"/>
-    <mergeCell ref="F39:F40"/>
-    <mergeCell ref="C45:C46"/>
-    <mergeCell ref="D45:D46"/>
-    <mergeCell ref="E45:E46"/>
-    <mergeCell ref="F45:F46"/>
-    <mergeCell ref="C41:C42"/>
-    <mergeCell ref="D41:D42"/>
-    <mergeCell ref="E41:E42"/>
-    <mergeCell ref="F41:F42"/>
-    <mergeCell ref="C43:C44"/>
-    <mergeCell ref="D43:D44"/>
-    <mergeCell ref="E43:E44"/>
-    <mergeCell ref="F43:F44"/>
-    <mergeCell ref="G45:G46"/>
-    <mergeCell ref="G43:G44"/>
-    <mergeCell ref="G41:G42"/>
-    <mergeCell ref="G39:G40"/>
-    <mergeCell ref="G37:G38"/>
-    <mergeCell ref="G35:G36"/>
-    <mergeCell ref="G33:G34"/>
-    <mergeCell ref="G27:G28"/>
-    <mergeCell ref="G29:G30"/>
-    <mergeCell ref="G31:G32"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="A19:A20"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -8150,19 +7984,19 @@
         <v>27</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>20</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="H1" s="1"/>
     </row>
@@ -8283,12 +8117,8 @@
       <c r="H5" s="1"/>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="53" t="s">
-        <v>19</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>4</v>
-      </c>
+      <c r="A6" s="53"/>
+      <c r="B6" s="1"/>
       <c r="C6" s="1">
         <f>INDEX(Hoja1!$A$1:$N$250, INT((ROW(A5)-1)/4)*13 + 5, CHOOSE(MOD(ROW(A5)-1,4)+1, 8, 10, 12, 14))</f>
         <v>0</v>
@@ -8312,12 +8142,8 @@
       <c r="H6" s="1"/>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="53" t="s">
-        <v>19</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>12</v>
-      </c>
+      <c r="A7" s="53"/>
+      <c r="B7" s="1"/>
       <c r="C7" s="1">
         <f>INDEX(Hoja1!$A$1:$N$250, INT((ROW(A6)-1)/4)*13 + 5, CHOOSE(MOD(ROW(A6)-1,4)+1, 8, 10, 12, 14))</f>
         <v>0</v>
@@ -8341,12 +8167,8 @@
       <c r="H7" s="1"/>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="53" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>13</v>
-      </c>
+      <c r="A8" s="53"/>
+      <c r="B8" s="1"/>
       <c r="C8" s="1">
         <f>INDEX(Hoja1!$A$1:$N$250, INT((ROW(A7)-1)/4)*13 + 5, CHOOSE(MOD(ROW(A7)-1,4)+1, 8, 10, 12, 14))</f>
         <v>0</v>
@@ -8370,12 +8192,8 @@
       <c r="H8" s="1"/>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="53" t="s">
-        <v>19</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>14</v>
-      </c>
+      <c r="A9" s="53"/>
+      <c r="B9" s="1"/>
       <c r="C9" s="1">
         <f>INDEX(Hoja1!$A$1:$N$250, INT((ROW(A8)-1)/4)*13 + 5, CHOOSE(MOD(ROW(A8)-1,4)+1, 8, 10, 12, 14))</f>
         <v>0</v>
@@ -8399,12 +8217,8 @@
       <c r="H9" s="1"/>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="53" t="s">
-        <v>22</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>4</v>
-      </c>
+      <c r="A10" s="53"/>
+      <c r="B10" s="1"/>
       <c r="C10" s="1">
         <f>INDEX(Hoja1!$A$1:$N$250, INT((ROW(A9)-1)/4)*13 + 5, CHOOSE(MOD(ROW(A9)-1,4)+1, 8, 10, 12, 14))</f>
         <v>0</v>
@@ -8428,12 +8242,8 @@
       <c r="H10" s="1"/>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="53" t="s">
-        <v>22</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>12</v>
-      </c>
+      <c r="A11" s="53"/>
+      <c r="B11" s="1"/>
       <c r="C11" s="1">
         <f>INDEX(Hoja1!$A$1:$N$250, INT((ROW(A10)-1)/4)*13 + 5, CHOOSE(MOD(ROW(A10)-1,4)+1, 8, 10, 12, 14))</f>
         <v>0</v>
@@ -8457,12 +8267,8 @@
       <c r="H11" s="1"/>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="53" t="s">
-        <v>22</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>13</v>
-      </c>
+      <c r="A12" s="53"/>
+      <c r="B12" s="1"/>
       <c r="C12" s="1">
         <f>INDEX(Hoja1!$A$1:$N$250, INT((ROW(A11)-1)/4)*13 + 5, CHOOSE(MOD(ROW(A11)-1,4)+1, 8, 10, 12, 14))</f>
         <v>0</v>
@@ -8486,12 +8292,8 @@
       <c r="H12" s="1"/>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="53" t="s">
-        <v>22</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>14</v>
-      </c>
+      <c r="A13" s="53"/>
+      <c r="B13" s="1"/>
       <c r="C13" s="1">
         <f>INDEX(Hoja1!$A$1:$N$250, INT((ROW(A12)-1)/4)*13 + 5, CHOOSE(MOD(ROW(A12)-1,4)+1, 8, 10, 12, 14))</f>
         <v>0</v>
@@ -8515,12 +8317,8 @@
       <c r="H13" s="1"/>
     </row>
     <row r="14" spans="1:8">
-      <c r="A14" s="53" t="s">
-        <v>25</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>4</v>
-      </c>
+      <c r="A14" s="53"/>
+      <c r="B14" s="1"/>
       <c r="C14" s="1">
         <f>INDEX(Hoja1!$A$1:$N$250, INT((ROW(A13)-1)/4)*13 + 5, CHOOSE(MOD(ROW(A13)-1,4)+1, 8, 10, 12, 14))</f>
         <v>0</v>
@@ -8544,12 +8342,8 @@
       <c r="H14" s="1"/>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="53" t="s">
-        <v>25</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>12</v>
-      </c>
+      <c r="A15" s="53"/>
+      <c r="B15" s="1"/>
       <c r="C15" s="1">
         <f>INDEX(Hoja1!$A$1:$N$250, INT((ROW(A14)-1)/4)*13 + 5, CHOOSE(MOD(ROW(A14)-1,4)+1, 8, 10, 12, 14))</f>
         <v>0</v>
@@ -8573,12 +8367,8 @@
       <c r="H15" s="1"/>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="53" t="s">
-        <v>25</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>13</v>
-      </c>
+      <c r="A16" s="53"/>
+      <c r="B16" s="1"/>
       <c r="C16" s="1">
         <f>INDEX(Hoja1!$A$1:$N$250, INT((ROW(A15)-1)/4)*13 + 5, CHOOSE(MOD(ROW(A15)-1,4)+1, 8, 10, 12, 14))</f>
         <v>0</v>
@@ -8602,12 +8392,8 @@
       <c r="H16" s="1"/>
     </row>
     <row r="17" spans="1:7">
-      <c r="A17" s="53" t="s">
-        <v>25</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>14</v>
-      </c>
+      <c r="A17" s="53"/>
+      <c r="B17" s="1"/>
       <c r="C17" s="1">
         <f>INDEX(Hoja1!$A$1:$N$250, INT((ROW(A16)-1)/4)*13 + 5, CHOOSE(MOD(ROW(A16)-1,4)+1, 8, 10, 12, 14))</f>
         <v>0</v>
@@ -8630,12 +8416,8 @@
       </c>
     </row>
     <row r="18" spans="1:7">
-      <c r="A18" s="53" t="s">
-        <v>52</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>4</v>
-      </c>
+      <c r="A18" s="53"/>
+      <c r="B18" s="1"/>
       <c r="C18" s="1">
         <f>INDEX(Hoja1!$A$1:$N$250, INT((ROW(A17)-1)/4)*13 + 5, CHOOSE(MOD(ROW(A17)-1,4)+1, 8, 10, 12, 14))</f>
         <v>0</v>
@@ -8658,12 +8440,8 @@
       </c>
     </row>
     <row r="19" spans="1:7">
-      <c r="A19" s="53" t="s">
-        <v>52</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>12</v>
-      </c>
+      <c r="A19" s="53"/>
+      <c r="B19" s="1"/>
       <c r="C19" s="1">
         <f>INDEX(Hoja1!$A$1:$N$250, INT((ROW(A18)-1)/4)*13 + 5, CHOOSE(MOD(ROW(A18)-1,4)+1, 8, 10, 12, 14))</f>
         <v>0</v>
@@ -8686,12 +8464,8 @@
       </c>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" s="53" t="s">
-        <v>52</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>13</v>
-      </c>
+      <c r="A20" s="53"/>
+      <c r="B20" s="1"/>
       <c r="C20" s="1">
         <f>INDEX(Hoja1!$A$1:$N$250, INT((ROW(A19)-1)/4)*13 + 5, CHOOSE(MOD(ROW(A19)-1,4)+1, 8, 10, 12, 14))</f>
         <v>0</v>
@@ -8714,12 +8488,8 @@
       </c>
     </row>
     <row r="21" spans="1:7">
-      <c r="A21" s="53" t="s">
-        <v>52</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>14</v>
-      </c>
+      <c r="A21" s="53"/>
+      <c r="B21" s="1"/>
       <c r="C21" s="1">
         <f>INDEX(Hoja1!$A$1:$N$250, INT((ROW(A20)-1)/4)*13 + 5, CHOOSE(MOD(ROW(A20)-1,4)+1, 8, 10, 12, 14))</f>
         <v>0</v>
@@ -8742,12 +8512,8 @@
       </c>
     </row>
     <row r="22" spans="1:7">
-      <c r="A22" s="53" t="s">
-        <v>53</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>4</v>
-      </c>
+      <c r="A22" s="53"/>
+      <c r="B22" s="1"/>
       <c r="C22" s="1">
         <f>INDEX(Hoja1!$A$1:$N$250, INT((ROW(A21)-1)/4)*13 + 5, CHOOSE(MOD(ROW(A21)-1,4)+1, 8, 10, 12, 14))</f>
         <v>0</v>
@@ -8770,12 +8536,8 @@
       </c>
     </row>
     <row r="23" spans="1:7">
-      <c r="A23" s="53" t="s">
-        <v>53</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>12</v>
-      </c>
+      <c r="A23" s="53"/>
+      <c r="B23" s="1"/>
       <c r="C23" s="1">
         <f>INDEX(Hoja1!$A$1:$N$250, INT((ROW(A22)-1)/4)*13 + 5, CHOOSE(MOD(ROW(A22)-1,4)+1, 8, 10, 12, 14))</f>
         <v>0</v>
@@ -8798,12 +8560,8 @@
       </c>
     </row>
     <row r="24" spans="1:7">
-      <c r="A24" s="53" t="s">
-        <v>53</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>13</v>
-      </c>
+      <c r="A24" s="53"/>
+      <c r="B24" s="1"/>
       <c r="C24" s="1">
         <f>INDEX(Hoja1!$A$1:$N$250, INT((ROW(A23)-1)/4)*13 + 5, CHOOSE(MOD(ROW(A23)-1,4)+1, 8, 10, 12, 14))</f>
         <v>0</v>
@@ -8826,12 +8584,8 @@
       </c>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" s="53" t="s">
-        <v>53</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>14</v>
-      </c>
+      <c r="A25" s="53"/>
+      <c r="B25" s="1"/>
       <c r="C25" s="1">
         <f>INDEX(Hoja1!$A$1:$N$250, INT((ROW(A24)-1)/4)*13 + 5, CHOOSE(MOD(ROW(A24)-1,4)+1, 8, 10, 12, 14))</f>
         <v>0</v>
@@ -8854,12 +8608,8 @@
       </c>
     </row>
     <row r="26" spans="1:7">
-      <c r="A26" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>4</v>
-      </c>
+      <c r="A26" s="2"/>
+      <c r="B26" s="1"/>
       <c r="C26" s="1">
         <f>INDEX(Hoja1!$A$1:$N$250, INT((ROW(A25)-1)/4)*13 + 5, CHOOSE(MOD(ROW(A25)-1,4)+1, 8, 10, 12, 14))</f>
         <v>0</v>
@@ -8882,12 +8632,8 @@
       </c>
     </row>
     <row r="27" spans="1:7">
-      <c r="A27" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>12</v>
-      </c>
+      <c r="A27" s="2"/>
+      <c r="B27" s="1"/>
       <c r="C27" s="1">
         <f>INDEX(Hoja1!$A$1:$N$250, INT((ROW(A26)-1)/4)*13 + 5, CHOOSE(MOD(ROW(A26)-1,4)+1, 8, 10, 12, 14))</f>
         <v>0</v>
@@ -8910,12 +8656,8 @@
       </c>
     </row>
     <row r="28" spans="1:7">
-      <c r="A28" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>13</v>
-      </c>
+      <c r="A28" s="2"/>
+      <c r="B28" s="1"/>
       <c r="C28" s="1">
         <f>INDEX(Hoja1!$A$1:$N$250, INT((ROW(A27)-1)/4)*13 + 5, CHOOSE(MOD(ROW(A27)-1,4)+1, 8, 10, 12, 14))</f>
         <v>0</v>
@@ -8938,12 +8680,8 @@
       </c>
     </row>
     <row r="29" spans="1:7">
-      <c r="A29" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>14</v>
-      </c>
+      <c r="A29" s="2"/>
+      <c r="B29" s="1"/>
       <c r="C29" s="1">
         <f>INDEX(Hoja1!$A$1:$N$250, INT((ROW(A28)-1)/4)*13 + 5, CHOOSE(MOD(ROW(A28)-1,4)+1, 8, 10, 12, 14))</f>
         <v>0</v>
@@ -8966,12 +8704,8 @@
       </c>
     </row>
     <row r="30" spans="1:7">
-      <c r="A30" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>4</v>
-      </c>
+      <c r="A30" s="2"/>
+      <c r="B30" s="1"/>
       <c r="C30" s="1">
         <f>INDEX(Hoja1!$A$1:$N$250, INT((ROW(A29)-1)/4)*13 + 5, CHOOSE(MOD(ROW(A29)-1,4)+1, 8, 10, 12, 14))</f>
         <v>0</v>
@@ -8994,12 +8728,8 @@
       </c>
     </row>
     <row r="31" spans="1:7">
-      <c r="A31" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>12</v>
-      </c>
+      <c r="A31" s="2"/>
+      <c r="B31" s="1"/>
       <c r="C31" s="1">
         <f>INDEX(Hoja1!$A$1:$N$250, INT((ROW(A30)-1)/4)*13 + 5, CHOOSE(MOD(ROW(A30)-1,4)+1, 8, 10, 12, 14))</f>
         <v>0</v>
@@ -9022,12 +8752,8 @@
       </c>
     </row>
     <row r="32" spans="1:7">
-      <c r="A32" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>13</v>
-      </c>
+      <c r="A32" s="2"/>
+      <c r="B32" s="1"/>
       <c r="C32" s="1">
         <f>INDEX(Hoja1!$A$1:$N$250, INT((ROW(A31)-1)/4)*13 + 5, CHOOSE(MOD(ROW(A31)-1,4)+1, 8, 10, 12, 14))</f>
         <v>0</v>
@@ -9050,12 +8776,8 @@
       </c>
     </row>
     <row r="33" spans="1:7">
-      <c r="A33" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>14</v>
-      </c>
+      <c r="A33" s="2"/>
+      <c r="B33" s="1"/>
       <c r="C33" s="1">
         <f>INDEX(Hoja1!$A$1:$N$250, INT((ROW(A32)-1)/4)*13 + 5, CHOOSE(MOD(ROW(A32)-1,4)+1, 8, 10, 12, 14))</f>
         <v>0</v>
@@ -9078,12 +8800,8 @@
       </c>
     </row>
     <row r="34" spans="1:7">
-      <c r="A34" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>4</v>
-      </c>
+      <c r="A34" s="2"/>
+      <c r="B34" s="1"/>
       <c r="C34" s="1">
         <f>INDEX(Hoja1!$A$1:$N$250, INT((ROW(A33)-1)/4)*13 + 5, CHOOSE(MOD(ROW(A33)-1,4)+1, 8, 10, 12, 14))</f>
         <v>0</v>
@@ -9106,12 +8824,8 @@
       </c>
     </row>
     <row r="35" spans="1:7">
-      <c r="A35" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>12</v>
-      </c>
+      <c r="A35" s="2"/>
+      <c r="B35" s="1"/>
       <c r="C35" s="1">
         <f>INDEX(Hoja1!$A$1:$N$250, INT((ROW(A34)-1)/4)*13 + 5, CHOOSE(MOD(ROW(A34)-1,4)+1, 8, 10, 12, 14))</f>
         <v>0</v>
@@ -9134,12 +8848,8 @@
       </c>
     </row>
     <row r="36" spans="1:7">
-      <c r="A36" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>13</v>
-      </c>
+      <c r="A36" s="2"/>
+      <c r="B36" s="1"/>
       <c r="C36" s="1">
         <f>INDEX(Hoja1!$A$1:$N$250, INT((ROW(A35)-1)/4)*13 + 5, CHOOSE(MOD(ROW(A35)-1,4)+1, 8, 10, 12, 14))</f>
         <v>0</v>
@@ -9162,12 +8872,8 @@
       </c>
     </row>
     <row r="37" spans="1:7">
-      <c r="A37" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>14</v>
-      </c>
+      <c r="A37" s="2"/>
+      <c r="B37" s="1"/>
       <c r="C37" s="1">
         <f>INDEX(Hoja1!$A$1:$N$250, INT((ROW(A36)-1)/4)*13 + 5, CHOOSE(MOD(ROW(A36)-1,4)+1, 8, 10, 12, 14))</f>
         <v>0</v>
@@ -9191,9 +8897,7 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38" s="111"/>
-      <c r="B38" s="1" t="s">
-        <v>4</v>
-      </c>
+      <c r="B38" s="1"/>
       <c r="C38" s="1">
         <f>INDEX(Hoja1!$A$1:$N$250, INT((ROW(A37)-1)/4)*13 + 5, CHOOSE(MOD(ROW(A37)-1,4)+1, 8, 10, 12, 14))</f>
         <v>0</v>
@@ -9217,9 +8921,7 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39" s="111"/>
-      <c r="B39" s="1" t="s">
-        <v>12</v>
-      </c>
+      <c r="B39" s="1"/>
       <c r="C39" s="1">
         <f>INDEX(Hoja1!$A$1:$N$250, INT((ROW(A38)-1)/4)*13 + 5, CHOOSE(MOD(ROW(A38)-1,4)+1, 8, 10, 12, 14))</f>
         <v>0</v>
@@ -9243,9 +8945,7 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40" s="111"/>
-      <c r="B40" s="1" t="s">
-        <v>13</v>
-      </c>
+      <c r="B40" s="1"/>
       <c r="C40" s="1">
         <f>INDEX(Hoja1!$A$1:$N$250, INT((ROW(A39)-1)/4)*13 + 5, CHOOSE(MOD(ROW(A39)-1,4)+1, 8, 10, 12, 14))</f>
         <v>0</v>
@@ -9269,9 +8969,7 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41" s="111"/>
-      <c r="B41" s="1" t="s">
-        <v>14</v>
-      </c>
+      <c r="B41" s="1"/>
       <c r="C41" s="1">
         <f>INDEX(Hoja1!$A$1:$N$250, INT((ROW(A40)-1)/4)*13 + 5, CHOOSE(MOD(ROW(A40)-1,4)+1, 8, 10, 12, 14))</f>
         <v>0</v>
@@ -9326,11 +9024,11 @@
       </c>
     </row>
     <row r="2" spans="1:16">
-      <c r="A2" s="115" t="s">
+      <c r="A2" s="123" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C2" s="54">
         <v>1.0411342592592594E-3</v>
@@ -9356,9 +9054,9 @@
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="1:16">
-      <c r="A3" s="115"/>
+      <c r="A3" s="123"/>
       <c r="B3" s="1" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C3" s="54">
         <v>1.0291782407407407E-3</v>
@@ -9384,9 +9082,9 @@
       <c r="P3" s="1"/>
     </row>
     <row r="4" spans="1:16">
-      <c r="A4" s="115"/>
+      <c r="A4" s="123"/>
       <c r="B4" s="1" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C4" s="54"/>
       <c r="D4" s="54"/>
@@ -9404,11 +9102,9 @@
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="1:16">
-      <c r="A5" s="115" t="s">
-        <v>19</v>
-      </c>
+      <c r="A5" s="123"/>
       <c r="B5" s="1" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C5" s="54"/>
       <c r="D5" s="54"/>
@@ -9426,9 +9122,9 @@
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="1:16">
-      <c r="A6" s="115"/>
+      <c r="A6" s="123"/>
       <c r="B6" s="1" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C6" s="54"/>
       <c r="D6" s="54"/>
@@ -9446,9 +9142,9 @@
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="1:16">
-      <c r="A7" s="115"/>
+      <c r="A7" s="123"/>
       <c r="B7" s="1" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C7" s="54"/>
       <c r="D7" s="54"/>
@@ -9466,11 +9162,9 @@
       <c r="P7" s="1"/>
     </row>
     <row r="8" spans="1:16">
-      <c r="A8" s="115" t="s">
-        <v>22</v>
-      </c>
+      <c r="A8" s="123"/>
       <c r="B8" s="1" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C8" s="54"/>
       <c r="D8" s="54"/>
@@ -9488,9 +9182,9 @@
       <c r="P8" s="1"/>
     </row>
     <row r="9" spans="1:16">
-      <c r="A9" s="115"/>
+      <c r="A9" s="123"/>
       <c r="B9" s="1" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C9" s="54"/>
       <c r="D9" s="54"/>
@@ -9508,9 +9202,9 @@
       <c r="P9" s="1"/>
     </row>
     <row r="10" spans="1:16">
-      <c r="A10" s="115"/>
+      <c r="A10" s="123"/>
       <c r="B10" s="1" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C10" s="54"/>
       <c r="D10" s="54"/>
@@ -9528,11 +9222,9 @@
       <c r="P10" s="1"/>
     </row>
     <row r="11" spans="1:16">
-      <c r="A11" s="115" t="s">
-        <v>25</v>
-      </c>
+      <c r="A11" s="123"/>
       <c r="B11" s="1" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C11" s="54"/>
       <c r="D11" s="54"/>
@@ -9550,9 +9242,9 @@
       <c r="P11" s="1"/>
     </row>
     <row r="12" spans="1:16">
-      <c r="A12" s="115"/>
+      <c r="A12" s="123"/>
       <c r="B12" s="1" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C12" s="54"/>
       <c r="D12" s="54"/>
@@ -9570,9 +9262,9 @@
       <c r="P12" s="1"/>
     </row>
     <row r="13" spans="1:16">
-      <c r="A13" s="115"/>
+      <c r="A13" s="123"/>
       <c r="B13" s="1" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C13" s="54"/>
       <c r="D13" s="54"/>
@@ -9593,11 +9285,9 @@
       </c>
     </row>
     <row r="14" spans="1:16">
-      <c r="A14" s="115" t="s">
-        <v>52</v>
-      </c>
+      <c r="A14" s="123"/>
       <c r="B14" s="1" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C14" s="54"/>
       <c r="D14" s="54"/>
@@ -9630,9 +9320,9 @@
       </c>
     </row>
     <row r="15" spans="1:16">
-      <c r="A15" s="115"/>
+      <c r="A15" s="123"/>
       <c r="B15" s="1" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C15" s="54"/>
       <c r="D15" s="54"/>
@@ -9662,9 +9352,9 @@
       <c r="P15" s="1"/>
     </row>
     <row r="16" spans="1:16">
-      <c r="A16" s="115"/>
+      <c r="A16" s="123"/>
       <c r="B16" s="1" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C16" s="54"/>
       <c r="D16" s="54"/>
@@ -9694,11 +9384,9 @@
       <c r="P16" s="1"/>
     </row>
     <row r="17" spans="1:18">
-      <c r="A17" s="115" t="s">
-        <v>53</v>
-      </c>
+      <c r="A17" s="123"/>
       <c r="B17" s="1" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C17" s="54"/>
       <c r="D17" s="54"/>
@@ -9718,9 +9406,9 @@
       <c r="R17" s="1"/>
     </row>
     <row r="18" spans="1:18">
-      <c r="A18" s="115"/>
+      <c r="A18" s="123"/>
       <c r="B18" s="1" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C18" s="54"/>
       <c r="D18" s="54"/>
@@ -9743,9 +9431,9 @@
       </c>
     </row>
     <row r="19" spans="1:18">
-      <c r="A19" s="115"/>
+      <c r="A19" s="123"/>
       <c r="B19" s="1" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C19" s="54"/>
       <c r="D19" s="54"/>
@@ -9765,11 +9453,9 @@
       <c r="R19" s="1"/>
     </row>
     <row r="20" spans="1:18">
-      <c r="A20" s="115" t="s">
-        <v>54</v>
-      </c>
+      <c r="A20" s="123"/>
       <c r="B20" s="1" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C20" s="54"/>
       <c r="D20" s="54"/>
@@ -9789,9 +9475,9 @@
       <c r="R20" s="1"/>
     </row>
     <row r="21" spans="1:18">
-      <c r="A21" s="115"/>
+      <c r="A21" s="123"/>
       <c r="B21" s="1" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C21" s="54"/>
       <c r="D21" s="54"/>
@@ -9811,9 +9497,9 @@
       <c r="R21" s="1"/>
     </row>
     <row r="22" spans="1:18">
-      <c r="A22" s="115"/>
+      <c r="A22" s="123"/>
       <c r="B22" s="1" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C22" s="54"/>
       <c r="D22" s="54"/>
@@ -9833,11 +9519,9 @@
       <c r="R22" s="1"/>
     </row>
     <row r="23" spans="1:18">
-      <c r="A23" s="115" t="s">
-        <v>55</v>
-      </c>
+      <c r="A23" s="123"/>
       <c r="B23" s="1" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C23" s="54"/>
       <c r="D23" s="54"/>
@@ -9857,9 +9541,9 @@
       <c r="R23" s="1"/>
     </row>
     <row r="24" spans="1:18">
-      <c r="A24" s="115"/>
+      <c r="A24" s="123"/>
       <c r="B24" s="1" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C24" s="128"/>
       <c r="D24" s="128"/>
@@ -9879,9 +9563,9 @@
       <c r="R24" s="1"/>
     </row>
     <row r="25" spans="1:18">
-      <c r="A25" s="115"/>
+      <c r="A25" s="123"/>
       <c r="B25" s="1" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C25" s="54"/>
       <c r="D25" s="54"/>
@@ -9901,11 +9585,9 @@
       <c r="R25" s="1"/>
     </row>
     <row r="26" spans="1:18">
-      <c r="A26" s="115" t="s">
-        <v>56</v>
-      </c>
+      <c r="A26" s="123"/>
       <c r="B26" s="1" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C26" s="54"/>
       <c r="D26" s="54"/>
@@ -9925,9 +9607,9 @@
       <c r="R26" s="1"/>
     </row>
     <row r="27" spans="1:18">
-      <c r="A27" s="115"/>
+      <c r="A27" s="123"/>
       <c r="B27" s="1" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C27" s="54"/>
       <c r="D27" s="54"/>
@@ -9947,9 +9629,9 @@
       <c r="R27" s="1"/>
     </row>
     <row r="28" spans="1:18">
-      <c r="A28" s="115"/>
+      <c r="A28" s="123"/>
       <c r="B28" s="1" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C28" s="54"/>
       <c r="D28" s="54"/>
@@ -9969,11 +9651,9 @@
       <c r="R28" s="1"/>
     </row>
     <row r="29" spans="1:18">
-      <c r="A29" s="115" t="s">
-        <v>25</v>
-      </c>
+      <c r="A29" s="123"/>
       <c r="B29" s="1" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C29" s="54"/>
       <c r="D29" s="54"/>
@@ -9993,9 +9673,9 @@
       <c r="R29" s="1"/>
     </row>
     <row r="30" spans="1:18">
-      <c r="A30" s="115"/>
+      <c r="A30" s="123"/>
       <c r="B30" s="1" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C30" s="54"/>
       <c r="D30" s="54"/>
@@ -10015,9 +9695,9 @@
       <c r="R30" s="1"/>
     </row>
     <row r="31" spans="1:18">
-      <c r="A31" s="115"/>
+      <c r="A31" s="123"/>
       <c r="B31" s="1" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
@@ -10037,11 +9717,9 @@
       <c r="R31" s="1"/>
     </row>
     <row r="32" spans="1:18">
-      <c r="A32" s="115" t="s">
-        <v>65</v>
-      </c>
+      <c r="A32" s="123"/>
       <c r="B32" s="1" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C32" s="54"/>
       <c r="D32" s="54"/>
@@ -10061,15 +9739,15 @@
       <c r="R32" s="1"/>
     </row>
     <row r="33" spans="1:2">
-      <c r="A33" s="115"/>
+      <c r="A33" s="123"/>
       <c r="B33" s="1" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
     </row>
     <row r="34" spans="1:2">
-      <c r="A34" s="115"/>
+      <c r="A34" s="123"/>
       <c r="B34" s="1" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -10117,7 +9795,7 @@
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>4</v>
@@ -10134,11 +9812,11 @@
       <c r="P1" s="1"/>
     </row>
     <row r="2" spans="1:16">
-      <c r="A2" s="117" t="s">
+      <c r="A2" s="125" t="s">
         <v>9</v>
       </c>
       <c r="B2" s="60" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C2" s="65">
         <f>+IF('Carga Tiempos'!C2=MIN('Carga Tiempos'!$C2:$F2),'Carga Tiempos'!C2,'Carga Tiempos'!C2-MIN('Carga Tiempos'!$C2:$F2))</f>
@@ -10179,9 +9857,9 @@
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="1:16">
-      <c r="A3" s="118"/>
+      <c r="A3" s="126"/>
       <c r="B3" s="58" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C3" s="65">
         <f>+IF('Carga Tiempos'!C3=MIN('Carga Tiempos'!$C3:$F3),'Carga Tiempos'!C3,'Carga Tiempos'!C3-MIN('Carga Tiempos'!$C3:$F3))</f>
@@ -10222,9 +9900,9 @@
       <c r="P3" s="1"/>
     </row>
     <row r="4" spans="1:16">
-      <c r="A4" s="118"/>
+      <c r="A4" s="126"/>
       <c r="B4" s="58" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C4" s="65">
         <f>+IF('Carga Tiempos'!C4=MIN('Carga Tiempos'!$C4:$F4),'Carga Tiempos'!C4,'Carga Tiempos'!C4-MIN('Carga Tiempos'!$C4:$F4))</f>
@@ -10265,11 +9943,9 @@
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="1:16">
-      <c r="A5" s="117" t="s">
-        <v>19</v>
-      </c>
+      <c r="A5" s="125"/>
       <c r="B5" s="60" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C5" s="66"/>
       <c r="D5" s="56"/>
@@ -10287,9 +9963,9 @@
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="1:16">
-      <c r="A6" s="118"/>
+      <c r="A6" s="126"/>
       <c r="B6" s="58" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C6" s="65"/>
       <c r="D6" s="64"/>
@@ -10307,9 +9983,9 @@
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="1:16">
-      <c r="A7" s="119"/>
+      <c r="A7" s="127"/>
       <c r="B7" s="62" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C7" s="67"/>
       <c r="D7" s="57"/>
@@ -10327,11 +10003,9 @@
       <c r="P7" s="1"/>
     </row>
     <row r="8" spans="1:16">
-      <c r="A8" s="118" t="s">
-        <v>22</v>
-      </c>
+      <c r="A8" s="126"/>
       <c r="B8" s="60" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C8" s="65"/>
       <c r="D8" s="64"/>
@@ -10349,9 +10023,9 @@
       <c r="P8" s="1"/>
     </row>
     <row r="9" spans="1:16">
-      <c r="A9" s="118"/>
+      <c r="A9" s="126"/>
       <c r="B9" s="58" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C9" s="65"/>
       <c r="D9" s="64"/>
@@ -10369,9 +10043,9 @@
       <c r="P9" s="1"/>
     </row>
     <row r="10" spans="1:16">
-      <c r="A10" s="119"/>
+      <c r="A10" s="127"/>
       <c r="B10" s="62" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C10" s="67">
         <f>+IF('Carga Tiempos'!C10=MIN('Carga Tiempos'!$C10:$F10),'Carga Tiempos'!C10,'Carga Tiempos'!C10-MIN('Carga Tiempos'!$C10:$F10))</f>
@@ -10401,11 +10075,9 @@
       <c r="P10" s="1"/>
     </row>
     <row r="11" spans="1:16">
-      <c r="A11" s="118" t="s">
-        <v>25</v>
-      </c>
+      <c r="A11" s="126"/>
       <c r="B11" s="60" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C11" s="65">
         <f>+IF('Carga Tiempos'!C11=MIN('Carga Tiempos'!$C11:$F11),'Carga Tiempos'!C11,'Carga Tiempos'!C11-MIN('Carga Tiempos'!$C11:$F11))</f>
@@ -10435,9 +10107,9 @@
       <c r="P11" s="1"/>
     </row>
     <row r="12" spans="1:16">
-      <c r="A12" s="118"/>
+      <c r="A12" s="126"/>
       <c r="B12" s="58" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C12" s="65"/>
       <c r="D12" s="64"/>
@@ -10455,9 +10127,9 @@
       <c r="P12" s="1"/>
     </row>
     <row r="13" spans="1:16">
-      <c r="A13" s="118"/>
+      <c r="A13" s="126"/>
       <c r="B13" s="58" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C13" s="65"/>
       <c r="D13" s="64"/>
@@ -10475,11 +10147,9 @@
       <c r="P13" s="1"/>
     </row>
     <row r="14" spans="1:16">
-      <c r="A14" s="117" t="s">
-        <v>52</v>
-      </c>
+      <c r="A14" s="125"/>
       <c r="B14" s="60" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C14" s="66">
         <f>+IF('Carga Tiempos'!C14=MIN('Carga Tiempos'!$C14:$F14),'Carga Tiempos'!C14,'Carga Tiempos'!C14-MIN('Carga Tiempos'!$C14:$F14))</f>
@@ -10509,9 +10179,9 @@
       <c r="P14" s="1"/>
     </row>
     <row r="15" spans="1:16">
-      <c r="A15" s="118"/>
+      <c r="A15" s="126"/>
       <c r="B15" s="58" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C15" s="65">
         <f>+IF('Carga Tiempos'!C15=MIN('Carga Tiempos'!$C15:$F15),'Carga Tiempos'!C15,'Carga Tiempos'!C15-MIN('Carga Tiempos'!$C15:$F15))</f>
@@ -10541,9 +10211,9 @@
       <c r="P15" s="1"/>
     </row>
     <row r="16" spans="1:16">
-      <c r="A16" s="119"/>
+      <c r="A16" s="127"/>
       <c r="B16" s="62" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C16" s="67">
         <f>+IF('Carga Tiempos'!C16=MIN('Carga Tiempos'!$C16:$F16),'Carga Tiempos'!C16,'Carga Tiempos'!C16-MIN('Carga Tiempos'!$C16:$F16))</f>
@@ -10573,11 +10243,9 @@
       <c r="P16" s="1"/>
     </row>
     <row r="17" spans="1:16">
-      <c r="A17" s="118" t="s">
-        <v>53</v>
-      </c>
+      <c r="A17" s="126"/>
       <c r="B17" s="58" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C17" s="65">
         <f>+IF('Carga Tiempos'!C17=MIN('Carga Tiempos'!$C17:$F17),'Carga Tiempos'!C17,'Carga Tiempos'!C17-MIN('Carga Tiempos'!$C17:$F17))</f>
@@ -10607,9 +10275,9 @@
       <c r="P17" s="1"/>
     </row>
     <row r="18" spans="1:16">
-      <c r="A18" s="118"/>
+      <c r="A18" s="126"/>
       <c r="B18" s="58" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C18" s="65">
         <f>+IF('Carga Tiempos'!C18=MIN('Carga Tiempos'!$C18:$F18),'Carga Tiempos'!C18,'Carga Tiempos'!C18-MIN('Carga Tiempos'!$C18:$F18))</f>
@@ -10639,9 +10307,9 @@
       <c r="P18" s="1"/>
     </row>
     <row r="19" spans="1:16">
-      <c r="A19" s="118"/>
+      <c r="A19" s="126"/>
       <c r="B19" s="58" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C19" s="65">
         <f>+IF('Carga Tiempos'!C19=MIN('Carga Tiempos'!$C19:$F19),'Carga Tiempos'!C19,'Carga Tiempos'!C19-MIN('Carga Tiempos'!$C19:$F19))</f>
@@ -10671,11 +10339,9 @@
       <c r="P19" s="1"/>
     </row>
     <row r="20" spans="1:16">
-      <c r="A20" s="117" t="s">
-        <v>54</v>
-      </c>
+      <c r="A20" s="125"/>
       <c r="B20" s="60" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C20" s="66">
         <f>+IF('Carga Tiempos'!C20=MIN('Carga Tiempos'!$C20:$F20),'Carga Tiempos'!C20,'Carga Tiempos'!C20-MIN('Carga Tiempos'!$C20:$F20))</f>
@@ -10705,9 +10371,9 @@
       <c r="P20" s="1"/>
     </row>
     <row r="21" spans="1:16">
-      <c r="A21" s="118"/>
+      <c r="A21" s="126"/>
       <c r="B21" s="58" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C21" s="65">
         <f>+IF('Carga Tiempos'!C21=MIN('Carga Tiempos'!$C21:$F21),'Carga Tiempos'!C21,'Carga Tiempos'!C21-MIN('Carga Tiempos'!$C21:$F21))</f>
@@ -10737,9 +10403,9 @@
       <c r="P21" s="1"/>
     </row>
     <row r="22" spans="1:16">
-      <c r="A22" s="118"/>
+      <c r="A22" s="126"/>
       <c r="B22" s="58" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C22" s="65">
         <f>+IF('Carga Tiempos'!C22=MIN('Carga Tiempos'!$C22:$F22),'Carga Tiempos'!C22,'Carga Tiempos'!C22-MIN('Carga Tiempos'!$C22:$F22))</f>
@@ -10769,11 +10435,9 @@
       <c r="P22" s="1"/>
     </row>
     <row r="23" spans="1:16">
-      <c r="A23" s="117" t="s">
-        <v>55</v>
-      </c>
+      <c r="A23" s="125"/>
       <c r="B23" s="60" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C23" s="66">
         <f>+IF('Carga Tiempos'!C23=MIN('Carga Tiempos'!$C23:$F23),'Carga Tiempos'!C23,'Carga Tiempos'!C23-MIN('Carga Tiempos'!$C23:$F23))</f>
@@ -10803,9 +10467,9 @@
       <c r="P23" s="1"/>
     </row>
     <row r="24" spans="1:16">
-      <c r="A24" s="118"/>
+      <c r="A24" s="126"/>
       <c r="B24" s="58" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C24" s="65">
         <f>+IF('Carga Tiempos'!C24=MIN('Carga Tiempos'!$C24:$F24),'Carga Tiempos'!C24,'Carga Tiempos'!C24-MIN('Carga Tiempos'!$C24:$F24))</f>
@@ -10835,9 +10499,9 @@
       <c r="P24" s="1"/>
     </row>
     <row r="25" spans="1:16">
-      <c r="A25" s="119"/>
+      <c r="A25" s="127"/>
       <c r="B25" s="62" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C25" s="67">
         <f>+IF('Carga Tiempos'!C25=MIN('Carga Tiempos'!$C25:$F25),'Carga Tiempos'!C25,'Carga Tiempos'!C25-MIN('Carga Tiempos'!$C25:$F25))</f>
@@ -10867,11 +10531,9 @@
       <c r="P25" s="1"/>
     </row>
     <row r="26" spans="1:16">
-      <c r="A26" s="118" t="s">
-        <v>56</v>
-      </c>
+      <c r="A26" s="126"/>
       <c r="B26" s="58" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C26" s="65">
         <f>+IF('Carga Tiempos'!C26=MIN('Carga Tiempos'!$C26:$F26),'Carga Tiempos'!C26,'Carga Tiempos'!C26-MIN('Carga Tiempos'!$C26:$F26))</f>
@@ -10901,9 +10563,9 @@
       <c r="P26" s="1"/>
     </row>
     <row r="27" spans="1:16">
-      <c r="A27" s="118"/>
+      <c r="A27" s="126"/>
       <c r="B27" s="58" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C27" s="65">
         <f>+IF('Carga Tiempos'!C27=MIN('Carga Tiempos'!$C27:$F27),'Carga Tiempos'!C27,'Carga Tiempos'!C27-MIN('Carga Tiempos'!$C27:$F27))</f>
@@ -10933,9 +10595,9 @@
       <c r="P27" s="1"/>
     </row>
     <row r="28" spans="1:16">
-      <c r="A28" s="118"/>
+      <c r="A28" s="126"/>
       <c r="B28" s="58" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C28" s="65">
         <f>+IF('Carga Tiempos'!C28=MIN('Carga Tiempos'!$C28:$F28),'Carga Tiempos'!C28,'Carga Tiempos'!C28-MIN('Carga Tiempos'!$C28:$F28))</f>
@@ -10965,11 +10627,9 @@
       <c r="P28" s="1"/>
     </row>
     <row r="29" spans="1:16">
-      <c r="A29" s="117" t="s">
-        <v>67</v>
-      </c>
+      <c r="A29" s="125"/>
       <c r="B29" s="60" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C29" s="66">
         <f>+IF('Carga Tiempos'!C29=MIN('Carga Tiempos'!$C29:$F29),'Carga Tiempos'!C29,'Carga Tiempos'!C29-MIN('Carga Tiempos'!$C29:$F29))</f>
@@ -10999,9 +10659,9 @@
       <c r="P29" s="1"/>
     </row>
     <row r="30" spans="1:16">
-      <c r="A30" s="118"/>
+      <c r="A30" s="126"/>
       <c r="B30" s="58" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C30" s="65">
         <f>+IF('Carga Tiempos'!C30=MIN('Carga Tiempos'!$C30:$F30),'Carga Tiempos'!C30,'Carga Tiempos'!C30-MIN('Carga Tiempos'!$C30:$F30))</f>
@@ -11031,9 +10691,9 @@
       <c r="P30" s="1"/>
     </row>
     <row r="31" spans="1:16">
-      <c r="A31" s="119"/>
+      <c r="A31" s="127"/>
       <c r="B31" s="62" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C31" s="67">
         <f>+IF('Carga Tiempos'!C31=MIN('Carga Tiempos'!$C31:$F31),'Carga Tiempos'!C31,'Carga Tiempos'!C31-MIN('Carga Tiempos'!$C31:$F31))</f>
@@ -11159,148 +10819,106 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" s="1" customFormat="1" ht="34.5">
-      <c r="A1" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="K1" s="120" t="s">
-        <v>54</v>
-      </c>
-      <c r="L1" s="120"/>
-      <c r="M1" s="120"/>
-      <c r="N1" s="120"/>
-      <c r="O1" s="120"/>
-      <c r="P1" s="120"/>
-      <c r="Q1" s="120"/>
-      <c r="R1" s="120"/>
+      <c r="A1" s="97" t="s">
+        <v>61</v>
+      </c>
+      <c r="K1" s="108"/>
+      <c r="L1" s="108"/>
+      <c r="M1" s="108"/>
+      <c r="N1" s="108"/>
+      <c r="O1" s="108"/>
+      <c r="P1" s="108"/>
+      <c r="Q1" s="108"/>
+      <c r="R1" s="108"/>
     </row>
     <row r="2" spans="1:22" ht="34.5">
-      <c r="A2" s="120" t="s">
-        <v>69</v>
-      </c>
-      <c r="B2" s="120"/>
-      <c r="C2" s="120"/>
-      <c r="D2" s="120"/>
-      <c r="E2" s="120"/>
-      <c r="F2" s="120"/>
-      <c r="G2" s="120"/>
-      <c r="H2" s="120"/>
+      <c r="A2" s="108" t="s">
+        <v>62</v>
+      </c>
+      <c r="B2" s="108"/>
+      <c r="C2" s="108"/>
+      <c r="D2" s="108"/>
+      <c r="E2" s="108"/>
+      <c r="F2" s="108"/>
+      <c r="G2" s="108"/>
+      <c r="H2" s="108"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
-      <c r="K2" s="121" t="s">
-        <v>70</v>
-      </c>
-      <c r="L2" s="122"/>
-      <c r="M2" s="121" t="s">
-        <v>71</v>
-      </c>
-      <c r="N2" s="122"/>
-      <c r="O2" s="121" t="s">
-        <v>72</v>
-      </c>
-      <c r="P2" s="122"/>
-      <c r="Q2" s="121" t="s">
-        <v>73</v>
-      </c>
-      <c r="R2" s="122"/>
+      <c r="K2" s="104"/>
+      <c r="L2" s="105"/>
+      <c r="M2" s="104"/>
+      <c r="N2" s="105"/>
+      <c r="O2" s="104"/>
+      <c r="P2" s="105"/>
+      <c r="Q2" s="104"/>
+      <c r="R2" s="105"/>
       <c r="S2" s="1"/>
       <c r="T2" s="1"/>
       <c r="U2" s="1"/>
       <c r="V2" s="1"/>
     </row>
     <row r="3" spans="1:22">
-      <c r="A3" s="125" t="s">
+      <c r="A3" s="109" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="126"/>
-      <c r="C3" s="125" t="s">
+      <c r="B3" s="110"/>
+      <c r="C3" s="109" t="s">
         <v>27</v>
       </c>
-      <c r="D3" s="126"/>
-      <c r="E3" s="125" t="s">
+      <c r="D3" s="110"/>
+      <c r="E3" s="109" t="s">
         <v>27</v>
       </c>
-      <c r="F3" s="126"/>
-      <c r="G3" s="125" t="s">
+      <c r="F3" s="110"/>
+      <c r="G3" s="109" t="s">
         <v>27</v>
       </c>
-      <c r="H3" s="126"/>
+      <c r="H3" s="110"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
-      <c r="K3" s="72">
-        <v>1</v>
-      </c>
-      <c r="L3" s="77">
-        <v>1.2731481481481483E-3</v>
-      </c>
-      <c r="M3" s="82" t="s">
-        <v>74</v>
-      </c>
-      <c r="N3" s="73">
-        <v>1.2796759259259259E-3</v>
-      </c>
-      <c r="O3" s="82" t="s">
-        <v>74</v>
-      </c>
-      <c r="P3" s="80">
-        <v>1.4428356481481482E-3</v>
-      </c>
-      <c r="Q3" s="79" t="s">
-        <v>74</v>
-      </c>
-      <c r="R3" s="80">
-        <v>1.4428356481481482E-3</v>
-      </c>
+      <c r="K3" s="72"/>
+      <c r="L3" s="77"/>
+      <c r="M3" s="82"/>
+      <c r="N3" s="73"/>
+      <c r="O3" s="82"/>
+      <c r="P3" s="80"/>
+      <c r="Q3" s="79"/>
+      <c r="R3" s="80"/>
       <c r="S3" s="1"/>
       <c r="T3" s="1"/>
-      <c r="U3" s="127"/>
+      <c r="U3" s="103"/>
       <c r="V3" s="1"/>
     </row>
     <row r="4" spans="1:22">
-      <c r="A4" s="121" t="s">
-        <v>75</v>
-      </c>
-      <c r="B4" s="122"/>
-      <c r="C4" s="121" t="s">
-        <v>76</v>
-      </c>
-      <c r="D4" s="122"/>
-      <c r="E4" s="123" t="s">
-        <v>77</v>
-      </c>
-      <c r="F4" s="124"/>
-      <c r="G4" s="121" t="s">
-        <v>78</v>
-      </c>
-      <c r="H4" s="122"/>
+      <c r="A4" s="104" t="s">
+        <v>63</v>
+      </c>
+      <c r="B4" s="105"/>
+      <c r="C4" s="104" t="s">
+        <v>64</v>
+      </c>
+      <c r="D4" s="105"/>
+      <c r="E4" s="106" t="s">
+        <v>65</v>
+      </c>
+      <c r="F4" s="107"/>
+      <c r="G4" s="104" t="s">
+        <v>66</v>
+      </c>
+      <c r="H4" s="105"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
-      <c r="K4" s="74">
-        <v>2</v>
-      </c>
-      <c r="L4" s="77">
-        <v>1.2580092592592593E-3</v>
-      </c>
-      <c r="M4" s="79" t="s">
-        <v>79</v>
-      </c>
-      <c r="N4" s="73">
-        <v>1.2429976851851853E-3</v>
-      </c>
-      <c r="O4" s="79" t="s">
-        <v>79</v>
-      </c>
-      <c r="P4" s="77">
-        <v>1.2858101851851852E-3</v>
-      </c>
-      <c r="Q4" s="79" t="s">
-        <v>79</v>
-      </c>
-      <c r="R4" s="77">
-        <v>1.2858101851851852E-3</v>
-      </c>
+      <c r="K4" s="74"/>
+      <c r="L4" s="77"/>
+      <c r="M4" s="79"/>
+      <c r="N4" s="73"/>
+      <c r="O4" s="79"/>
+      <c r="P4" s="77"/>
+      <c r="Q4" s="79"/>
+      <c r="R4" s="77"/>
       <c r="S4" s="1"/>
       <c r="T4" s="1"/>
-      <c r="U4" s="127"/>
+      <c r="U4" s="103"/>
       <c r="V4" s="1"/>
     </row>
     <row r="5" spans="1:22">
@@ -11330,33 +10948,17 @@
       </c>
       <c r="I5" s="54"/>
       <c r="J5" s="1"/>
-      <c r="K5" s="74">
-        <v>3</v>
-      </c>
-      <c r="L5" s="77">
-        <v>1.2545601851851852E-3</v>
-      </c>
-      <c r="M5" s="83" t="s">
-        <v>80</v>
-      </c>
-      <c r="N5" s="73">
-        <v>1.2377777777777777E-3</v>
-      </c>
-      <c r="O5" s="83" t="s">
-        <v>80</v>
-      </c>
-      <c r="P5" s="77">
-        <v>1.2647453703703703E-3</v>
-      </c>
-      <c r="Q5" s="79" t="s">
-        <v>80</v>
-      </c>
-      <c r="R5" s="77">
-        <v>1.2647453703703703E-3</v>
-      </c>
+      <c r="K5" s="74"/>
+      <c r="L5" s="77"/>
+      <c r="M5" s="83"/>
+      <c r="N5" s="73"/>
+      <c r="O5" s="83"/>
+      <c r="P5" s="77"/>
+      <c r="Q5" s="79"/>
+      <c r="R5" s="77"/>
       <c r="S5" s="1"/>
       <c r="T5" s="1"/>
-      <c r="U5" s="127"/>
+      <c r="U5" s="103"/>
       <c r="V5" s="1"/>
     </row>
     <row r="6" spans="1:22">
@@ -11386,33 +10988,17 @@
       </c>
       <c r="I6" s="54"/>
       <c r="J6" s="1"/>
-      <c r="K6" s="74">
-        <v>4</v>
-      </c>
-      <c r="L6" s="77">
-        <v>1.2705902777777778E-3</v>
-      </c>
-      <c r="M6" s="79" t="s">
-        <v>81</v>
-      </c>
-      <c r="N6" s="73">
-        <v>1.3249884259259259E-3</v>
-      </c>
-      <c r="O6" s="79" t="s">
-        <v>81</v>
-      </c>
-      <c r="P6" s="77">
-        <v>1.2908564814814816E-3</v>
-      </c>
-      <c r="Q6" s="79" t="s">
-        <v>81</v>
-      </c>
-      <c r="R6" s="77">
-        <v>1.2908564814814816E-3</v>
-      </c>
+      <c r="K6" s="74"/>
+      <c r="L6" s="77"/>
+      <c r="M6" s="79"/>
+      <c r="N6" s="73"/>
+      <c r="O6" s="79"/>
+      <c r="P6" s="77"/>
+      <c r="Q6" s="79"/>
+      <c r="R6" s="77"/>
       <c r="S6" s="1"/>
       <c r="T6" s="1"/>
-      <c r="U6" s="127"/>
+      <c r="U6" s="103"/>
       <c r="V6" s="1"/>
     </row>
     <row r="7" spans="1:22">
@@ -11442,33 +11028,17 @@
       </c>
       <c r="I7" s="54"/>
       <c r="J7" s="1"/>
-      <c r="K7" s="74">
-        <v>5</v>
-      </c>
-      <c r="L7" s="77">
-        <v>1.260300925925926E-3</v>
-      </c>
-      <c r="M7" s="83" t="s">
-        <v>82</v>
-      </c>
-      <c r="N7" s="73">
-        <v>1.2426273148148149E-3</v>
-      </c>
-      <c r="O7" s="83" t="s">
-        <v>82</v>
-      </c>
-      <c r="P7" s="77">
-        <v>1.2742476851851851E-3</v>
-      </c>
-      <c r="Q7" s="79" t="s">
-        <v>82</v>
-      </c>
-      <c r="R7" s="77">
-        <v>1.2742476851851851E-3</v>
-      </c>
+      <c r="K7" s="74"/>
+      <c r="L7" s="77"/>
+      <c r="M7" s="83"/>
+      <c r="N7" s="73"/>
+      <c r="O7" s="83"/>
+      <c r="P7" s="77"/>
+      <c r="Q7" s="79"/>
+      <c r="R7" s="77"/>
       <c r="S7" s="1"/>
       <c r="T7" s="1"/>
-      <c r="U7" s="127"/>
+      <c r="U7" s="103"/>
       <c r="V7" s="1"/>
     </row>
     <row r="8" spans="1:22">
@@ -11498,33 +11068,17 @@
       </c>
       <c r="I8" s="54"/>
       <c r="J8" s="1"/>
-      <c r="K8" s="74">
-        <v>6</v>
-      </c>
-      <c r="L8" s="77">
-        <v>1.2778935185185185E-3</v>
-      </c>
-      <c r="M8" s="79" t="s">
-        <v>83</v>
-      </c>
-      <c r="N8" s="73">
-        <v>1.2478472222222222E-3</v>
-      </c>
-      <c r="O8" s="79" t="s">
-        <v>83</v>
-      </c>
-      <c r="P8" s="77">
-        <v>1.2452199074074073E-3</v>
-      </c>
-      <c r="Q8" s="79" t="s">
-        <v>83</v>
-      </c>
-      <c r="R8" s="77">
-        <v>1.2452199074074073E-3</v>
-      </c>
+      <c r="K8" s="74"/>
+      <c r="L8" s="77"/>
+      <c r="M8" s="79"/>
+      <c r="N8" s="73"/>
+      <c r="O8" s="79"/>
+      <c r="P8" s="77"/>
+      <c r="Q8" s="79"/>
+      <c r="R8" s="77"/>
       <c r="S8" s="1"/>
       <c r="T8" s="1"/>
-      <c r="U8" s="127"/>
+      <c r="U8" s="103"/>
       <c r="V8" s="1"/>
     </row>
     <row r="9" spans="1:22">
@@ -11554,33 +11108,17 @@
       </c>
       <c r="I9" s="54"/>
       <c r="J9" s="1"/>
-      <c r="K9" s="74">
-        <v>7</v>
-      </c>
-      <c r="L9" s="77">
-        <v>1.2427199074074074E-3</v>
-      </c>
-      <c r="M9" s="79" t="s">
-        <v>84</v>
-      </c>
-      <c r="N9" s="73">
-        <v>1.248275462962963E-3</v>
-      </c>
-      <c r="O9" s="79" t="s">
-        <v>84</v>
-      </c>
-      <c r="P9" s="77">
-        <v>1.2555324074074075E-3</v>
-      </c>
-      <c r="Q9" s="79" t="s">
-        <v>84</v>
-      </c>
-      <c r="R9" s="77">
-        <v>1.2555324074074075E-3</v>
-      </c>
+      <c r="K9" s="74"/>
+      <c r="L9" s="77"/>
+      <c r="M9" s="79"/>
+      <c r="N9" s="73"/>
+      <c r="O9" s="79"/>
+      <c r="P9" s="77"/>
+      <c r="Q9" s="79"/>
+      <c r="R9" s="77"/>
       <c r="S9" s="1"/>
       <c r="T9" s="1"/>
-      <c r="U9" s="127"/>
+      <c r="U9" s="103"/>
       <c r="V9" s="1"/>
     </row>
     <row r="10" spans="1:22">
@@ -11610,33 +11148,17 @@
       </c>
       <c r="I10" s="54"/>
       <c r="J10" s="1"/>
-      <c r="K10" s="72">
-        <v>8</v>
-      </c>
-      <c r="L10" s="77">
-        <v>1.2430787037037037E-3</v>
-      </c>
-      <c r="M10" s="83" t="s">
-        <v>85</v>
-      </c>
-      <c r="N10" s="73">
-        <v>1.2653240740740741E-3</v>
-      </c>
-      <c r="O10" s="83" t="s">
-        <v>85</v>
-      </c>
-      <c r="P10" s="77">
-        <v>1.2631365740740741E-3</v>
-      </c>
-      <c r="Q10" s="79" t="s">
-        <v>85</v>
-      </c>
-      <c r="R10" s="77">
-        <v>1.2631365740740741E-3</v>
-      </c>
+      <c r="K10" s="72"/>
+      <c r="L10" s="77"/>
+      <c r="M10" s="83"/>
+      <c r="N10" s="73"/>
+      <c r="O10" s="83"/>
+      <c r="P10" s="77"/>
+      <c r="Q10" s="79"/>
+      <c r="R10" s="77"/>
       <c r="S10" s="1"/>
       <c r="T10" s="1"/>
-      <c r="U10" s="127"/>
+      <c r="U10" s="103"/>
       <c r="V10" s="1"/>
     </row>
     <row r="11" spans="1:22">
@@ -11666,33 +11188,17 @@
       </c>
       <c r="I11" s="54"/>
       <c r="J11" s="1"/>
-      <c r="K11" s="72">
-        <v>9</v>
-      </c>
-      <c r="L11" s="77">
-        <v>1.6843518518518518E-3</v>
-      </c>
-      <c r="M11" s="79" t="s">
-        <v>86</v>
-      </c>
-      <c r="N11" s="73">
-        <v>1.6837615740740741E-3</v>
-      </c>
-      <c r="O11" s="79" t="s">
-        <v>86</v>
-      </c>
-      <c r="P11" s="77">
-        <v>1.4671412037037036E-3</v>
-      </c>
-      <c r="Q11" s="79" t="s">
-        <v>86</v>
-      </c>
-      <c r="R11" s="77">
-        <v>1.4671412037037036E-3</v>
-      </c>
+      <c r="K11" s="72"/>
+      <c r="L11" s="77"/>
+      <c r="M11" s="79"/>
+      <c r="N11" s="73"/>
+      <c r="O11" s="79"/>
+      <c r="P11" s="77"/>
+      <c r="Q11" s="79"/>
+      <c r="R11" s="77"/>
       <c r="S11" s="1"/>
       <c r="T11" s="1"/>
-      <c r="U11" s="127"/>
+      <c r="U11" s="103"/>
       <c r="V11" s="1"/>
     </row>
     <row r="12" spans="1:22">
@@ -11722,33 +11228,17 @@
       </c>
       <c r="I12" s="54"/>
       <c r="J12" s="1"/>
-      <c r="K12" s="72">
-        <v>10</v>
-      </c>
-      <c r="L12" s="77">
-        <v>1.5963078703703703E-3</v>
-      </c>
-      <c r="M12" s="79" t="s">
-        <v>87</v>
-      </c>
-      <c r="N12" s="73">
-        <v>1.543287037037037E-3</v>
-      </c>
-      <c r="O12" s="79" t="s">
-        <v>87</v>
-      </c>
-      <c r="P12" s="77">
-        <v>1.5160185185185185E-3</v>
-      </c>
-      <c r="Q12" s="79" t="s">
-        <v>87</v>
-      </c>
-      <c r="R12" s="77">
-        <v>1.5160185185185185E-3</v>
-      </c>
+      <c r="K12" s="72"/>
+      <c r="L12" s="77"/>
+      <c r="M12" s="79"/>
+      <c r="N12" s="73"/>
+      <c r="O12" s="79"/>
+      <c r="P12" s="77"/>
+      <c r="Q12" s="79"/>
+      <c r="R12" s="77"/>
       <c r="S12" s="1"/>
       <c r="T12" s="1"/>
-      <c r="U12" s="127"/>
+      <c r="U12" s="103"/>
       <c r="V12" s="1"/>
     </row>
     <row r="13" spans="1:22">
@@ -11778,33 +11268,17 @@
       </c>
       <c r="I13" s="54"/>
       <c r="J13" s="1"/>
-      <c r="K13" s="72">
-        <v>11</v>
-      </c>
-      <c r="L13" s="77">
-        <v>1.8983680555555557E-3</v>
-      </c>
-      <c r="M13" s="79" t="s">
-        <v>88</v>
-      </c>
-      <c r="N13" s="73">
-        <v>1.9202893518518521E-3</v>
-      </c>
-      <c r="O13" s="79" t="s">
-        <v>88</v>
-      </c>
-      <c r="P13" s="77">
-        <v>1.9527199074074074E-3</v>
-      </c>
-      <c r="Q13" s="79" t="s">
-        <v>88</v>
-      </c>
-      <c r="R13" s="77">
-        <v>1.9527199074074074E-3</v>
-      </c>
+      <c r="K13" s="72"/>
+      <c r="L13" s="77"/>
+      <c r="M13" s="79"/>
+      <c r="N13" s="73"/>
+      <c r="O13" s="79"/>
+      <c r="P13" s="77"/>
+      <c r="Q13" s="79"/>
+      <c r="R13" s="77"/>
       <c r="S13" s="1"/>
       <c r="T13" s="54"/>
-      <c r="U13" s="127"/>
+      <c r="U13" s="103"/>
       <c r="V13" s="1"/>
     </row>
     <row r="14" spans="1:22">
@@ -11834,33 +11308,17 @@
       </c>
       <c r="I14" s="54"/>
       <c r="J14" s="1"/>
-      <c r="K14" s="72">
-        <v>12</v>
-      </c>
-      <c r="L14" s="77">
-        <v>1.2470833333333331E-3</v>
-      </c>
-      <c r="M14" s="79" t="s">
-        <v>89</v>
-      </c>
-      <c r="N14" s="73">
-        <v>1.2480787037037037E-3</v>
-      </c>
-      <c r="O14" s="79" t="s">
-        <v>89</v>
-      </c>
-      <c r="P14" s="77">
-        <v>1.2462037037037036E-3</v>
-      </c>
-      <c r="Q14" s="79" t="s">
-        <v>89</v>
-      </c>
-      <c r="R14" s="77">
-        <v>1.2462037037037036E-3</v>
-      </c>
+      <c r="K14" s="72"/>
+      <c r="L14" s="77"/>
+      <c r="M14" s="79"/>
+      <c r="N14" s="73"/>
+      <c r="O14" s="79"/>
+      <c r="P14" s="77"/>
+      <c r="Q14" s="79"/>
+      <c r="R14" s="77"/>
       <c r="S14" s="1"/>
       <c r="T14" s="1"/>
-      <c r="U14" s="127"/>
+      <c r="U14" s="103"/>
       <c r="V14" s="1"/>
     </row>
     <row r="15" spans="1:22">
@@ -11890,33 +11348,17 @@
       </c>
       <c r="I15" s="54"/>
       <c r="J15" s="1"/>
-      <c r="K15" s="72">
-        <v>13</v>
-      </c>
-      <c r="L15" s="77">
-        <v>1.236238425925926E-3</v>
-      </c>
-      <c r="M15" s="83" t="s">
-        <v>90</v>
-      </c>
-      <c r="N15" s="73">
-        <v>1.241701388888889E-3</v>
-      </c>
-      <c r="O15" s="83" t="s">
-        <v>90</v>
-      </c>
-      <c r="P15" s="77">
-        <v>1.2494560185185185E-3</v>
-      </c>
-      <c r="Q15" s="79" t="s">
-        <v>90</v>
-      </c>
-      <c r="R15" s="77">
-        <v>1.2494560185185185E-3</v>
-      </c>
+      <c r="K15" s="72"/>
+      <c r="L15" s="77"/>
+      <c r="M15" s="83"/>
+      <c r="N15" s="73"/>
+      <c r="O15" s="83"/>
+      <c r="P15" s="77"/>
+      <c r="Q15" s="79"/>
+      <c r="R15" s="77"/>
       <c r="S15" s="1"/>
       <c r="T15" s="1"/>
-      <c r="U15" s="127"/>
+      <c r="U15" s="103"/>
       <c r="V15" s="1"/>
     </row>
     <row r="16" spans="1:22">
@@ -11946,33 +11388,17 @@
       </c>
       <c r="I16" s="54"/>
       <c r="J16" s="1"/>
-      <c r="K16" s="72">
-        <v>14</v>
-      </c>
-      <c r="L16" s="77">
-        <v>1.2310648148148148E-3</v>
-      </c>
-      <c r="M16" s="84" t="s">
-        <v>91</v>
-      </c>
-      <c r="N16" s="73">
-        <v>1.2480208333333334E-3</v>
-      </c>
-      <c r="O16" s="84" t="s">
-        <v>91</v>
-      </c>
-      <c r="P16" s="77">
-        <v>1.2403703703703704E-3</v>
-      </c>
-      <c r="Q16" s="79" t="s">
-        <v>91</v>
-      </c>
-      <c r="R16" s="77">
-        <v>1.2403703703703704E-3</v>
-      </c>
+      <c r="K16" s="72"/>
+      <c r="L16" s="77"/>
+      <c r="M16" s="84"/>
+      <c r="N16" s="73"/>
+      <c r="O16" s="84"/>
+      <c r="P16" s="77"/>
+      <c r="Q16" s="79"/>
+      <c r="R16" s="77"/>
       <c r="S16" s="1"/>
       <c r="T16" s="1"/>
-      <c r="U16" s="127"/>
+      <c r="U16" s="103"/>
       <c r="V16" s="1"/>
     </row>
     <row r="17" spans="1:24">
@@ -12002,33 +11428,17 @@
       </c>
       <c r="I17" s="54"/>
       <c r="J17" s="1"/>
-      <c r="K17" s="75">
-        <v>15</v>
-      </c>
-      <c r="L17" s="78">
-        <v>1.2800810185185185E-3</v>
-      </c>
-      <c r="M17" s="81" t="s">
-        <v>92</v>
-      </c>
-      <c r="N17" s="76">
-        <v>1.2779629629629629E-3</v>
-      </c>
-      <c r="O17" s="81" t="s">
-        <v>92</v>
-      </c>
-      <c r="P17" s="78">
-        <v>1.2507638888888889E-3</v>
-      </c>
-      <c r="Q17" s="81" t="s">
-        <v>92</v>
-      </c>
-      <c r="R17" s="78">
-        <v>1.2507638888888889E-3</v>
-      </c>
+      <c r="K17" s="75"/>
+      <c r="L17" s="78"/>
+      <c r="M17" s="81"/>
+      <c r="N17" s="76"/>
+      <c r="O17" s="81"/>
+      <c r="P17" s="78"/>
+      <c r="Q17" s="81"/>
+      <c r="R17" s="78"/>
       <c r="S17" s="1"/>
       <c r="T17" s="1"/>
-      <c r="U17" s="127"/>
+      <c r="U17" s="103"/>
       <c r="V17" s="1"/>
       <c r="W17" s="1"/>
       <c r="X17" s="1"/>
@@ -12070,7 +11480,7 @@
       <c r="R18" s="1"/>
       <c r="S18" s="1"/>
       <c r="T18" s="1"/>
-      <c r="U18" s="127"/>
+      <c r="U18" s="103"/>
       <c r="V18" s="1"/>
       <c r="W18" s="1"/>
       <c r="X18" s="1"/>
@@ -12101,7 +11511,7 @@
         <v>1.0273495370370371E-3</v>
       </c>
       <c r="I19" s="54"/>
-      <c r="U19" s="127"/>
+      <c r="U19" s="103"/>
     </row>
     <row r="20" spans="1:24" s="1" customFormat="1">
       <c r="A20" s="129">
@@ -12129,25 +11539,25 @@
         <v>1.0275810185185186E-3</v>
       </c>
       <c r="I20" s="54"/>
-      <c r="L20" s="54">
+      <c r="L20" s="54" t="e">
         <f>+AVERAGE(L3:L10,L14:L17)</f>
-        <v>1.2562307098765433E-3</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="M20" s="71"/>
-      <c r="N20" s="54">
+      <c r="N20" s="54" t="e">
         <f>+AVERAGE(N3:N10,N14:N17)</f>
-        <v>1.2587731481481482E-3</v>
-      </c>
-      <c r="P20" s="54">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="P20" s="54" t="e">
         <f>+AVERAGE(P3:P10,P14:P17)</f>
-        <v>1.2757648533950618E-3</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="Q20" s="71"/>
-      <c r="R20" s="54">
+      <c r="R20" s="54" t="e">
         <f>+AVERAGE(R3:R10,R14:R17)</f>
-        <v>1.2757648533950618E-3</v>
-      </c>
-      <c r="U20" s="127"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U20" s="103"/>
     </row>
     <row r="21" spans="1:24" s="1" customFormat="1">
       <c r="A21" s="129">
@@ -12176,7 +11586,7 @@
       </c>
       <c r="I21" s="54"/>
       <c r="L21" s="54"/>
-      <c r="U21" s="127"/>
+      <c r="U21" s="103"/>
     </row>
     <row r="22" spans="1:24" s="1" customFormat="1">
       <c r="A22" s="129">
@@ -12204,25 +11614,25 @@
         <v>1.0513657407407407E-3</v>
       </c>
       <c r="I22" s="54"/>
-      <c r="L22" s="85">
+      <c r="L22" s="85" t="e">
         <f>+AVERAGE(L20:L21)</f>
-        <v>1.2562307098765433E-3</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="M22" s="86"/>
-      <c r="N22" s="87">
+      <c r="N22" s="87" t="e">
         <f>+SUM(N20-L20)</f>
-        <v>2.5424382716048976E-6</v>
-      </c>
-      <c r="P22" s="87">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="P22" s="87" t="e">
         <f>+SUM(P20-L20)</f>
-        <v>1.9534143518518555E-5</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="Q22" s="86"/>
-      <c r="R22" s="87">
+      <c r="R22" s="87" t="e">
         <f>+SUM(R20-L20)</f>
-        <v>1.9534143518518555E-5</v>
-      </c>
-      <c r="U22" s="127"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U22" s="103"/>
     </row>
     <row r="23" spans="1:24" s="1" customFormat="1">
       <c r="A23" s="129">
@@ -12304,7 +11714,7 @@
     <row r="26" spans="1:24" s="1" customFormat="1"/>
     <row r="27" spans="1:24" s="1" customFormat="1">
       <c r="A27" s="1" t="s">
-        <v>93</v>
+        <v>67</v>
       </c>
       <c r="B27" s="54">
         <f>+AVERAGE(B5:B13,B20:B24)</f>
@@ -12393,7 +11803,7 @@
     </row>
     <row r="31" spans="1:24">
       <c r="A31" s="86" t="s">
-        <v>94</v>
+        <v>68</v>
       </c>
       <c r="B31" s="54">
         <v>1.0291782407407407E-3</v>
@@ -12457,9 +11867,7 @@
     </row>
     <row r="33" spans="1:24" s="1" customFormat="1"/>
     <row r="34" spans="1:24">
-      <c r="A34" s="1" t="s">
-        <v>68</v>
-      </c>
+      <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
@@ -12469,9 +11877,7 @@
       <c r="H34" s="1"/>
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
-      <c r="K34" s="1" t="s">
-        <v>68</v>
-      </c>
+      <c r="K34" s="1"/>
       <c r="L34" s="1"/>
       <c r="M34" s="1"/>
       <c r="N34" s="1"/>
@@ -12487,28 +11893,24 @@
       <c r="X34" s="1"/>
     </row>
     <row r="35" spans="1:24" ht="34.5">
-      <c r="A35" s="120" t="s">
-        <v>69</v>
-      </c>
-      <c r="B35" s="120"/>
-      <c r="C35" s="120"/>
-      <c r="D35" s="120"/>
-      <c r="E35" s="120"/>
-      <c r="F35" s="120"/>
-      <c r="G35" s="120"/>
-      <c r="H35" s="120"/>
+      <c r="A35" s="108"/>
+      <c r="B35" s="108"/>
+      <c r="C35" s="108"/>
+      <c r="D35" s="108"/>
+      <c r="E35" s="108"/>
+      <c r="F35" s="108"/>
+      <c r="G35" s="108"/>
+      <c r="H35" s="108"/>
       <c r="I35" s="97"/>
       <c r="J35" s="1"/>
-      <c r="K35" s="120" t="s">
-        <v>95</v>
-      </c>
-      <c r="L35" s="120"/>
-      <c r="M35" s="120"/>
-      <c r="N35" s="120"/>
-      <c r="O35" s="120"/>
-      <c r="P35" s="120"/>
-      <c r="Q35" s="120"/>
-      <c r="R35" s="120"/>
+      <c r="K35" s="108"/>
+      <c r="L35" s="108"/>
+      <c r="M35" s="108"/>
+      <c r="N35" s="108"/>
+      <c r="O35" s="108"/>
+      <c r="P35" s="108"/>
+      <c r="Q35" s="108"/>
+      <c r="R35" s="108"/>
       <c r="S35" s="1"/>
       <c r="T35" s="1"/>
       <c r="U35" s="1"/>
@@ -12517,74 +11919,42 @@
       <c r="X35" s="1"/>
     </row>
     <row r="36" spans="1:24" s="1" customFormat="1">
-      <c r="A36" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="B36" s="126"/>
-      <c r="C36" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="D36" s="126"/>
-      <c r="E36" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="F36" s="126"/>
-      <c r="G36" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="H36" s="126"/>
-      <c r="K36" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="L36" s="126"/>
-      <c r="M36" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="N36" s="126"/>
-      <c r="O36" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="P36" s="126"/>
-      <c r="Q36" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="R36" s="126"/>
+      <c r="A36" s="109"/>
+      <c r="B36" s="110"/>
+      <c r="C36" s="109"/>
+      <c r="D36" s="110"/>
+      <c r="E36" s="109"/>
+      <c r="F36" s="110"/>
+      <c r="G36" s="109"/>
+      <c r="H36" s="110"/>
+      <c r="K36" s="109"/>
+      <c r="L36" s="110"/>
+      <c r="M36" s="109"/>
+      <c r="N36" s="110"/>
+      <c r="O36" s="109"/>
+      <c r="P36" s="110"/>
+      <c r="Q36" s="109"/>
+      <c r="R36" s="110"/>
     </row>
     <row r="37" spans="1:24">
-      <c r="A37" s="121" t="s">
-        <v>96</v>
-      </c>
-      <c r="B37" s="122"/>
-      <c r="C37" s="121" t="s">
-        <v>75</v>
-      </c>
-      <c r="D37" s="122"/>
-      <c r="E37" s="123" t="s">
-        <v>97</v>
-      </c>
-      <c r="F37" s="124"/>
-      <c r="G37" s="121" t="s">
-        <v>98</v>
-      </c>
-      <c r="H37" s="122"/>
+      <c r="A37" s="104"/>
+      <c r="B37" s="105"/>
+      <c r="C37" s="104"/>
+      <c r="D37" s="105"/>
+      <c r="E37" s="106"/>
+      <c r="F37" s="107"/>
+      <c r="G37" s="104"/>
+      <c r="H37" s="105"/>
       <c r="I37" s="1"/>
       <c r="J37" s="1"/>
-      <c r="K37" s="121" t="s">
-        <v>70</v>
-      </c>
-      <c r="L37" s="122"/>
-      <c r="M37" s="121" t="s">
-        <v>71</v>
-      </c>
-      <c r="N37" s="122"/>
-      <c r="O37" s="123" t="s">
-        <v>72</v>
-      </c>
-      <c r="P37" s="124"/>
-      <c r="Q37" s="121" t="s">
-        <v>73</v>
-      </c>
-      <c r="R37" s="122"/>
+      <c r="K37" s="104"/>
+      <c r="L37" s="105"/>
+      <c r="M37" s="104"/>
+      <c r="N37" s="105"/>
+      <c r="O37" s="106"/>
+      <c r="P37" s="107"/>
+      <c r="Q37" s="104"/>
+      <c r="R37" s="105"/>
       <c r="S37" s="1"/>
       <c r="T37" s="1"/>
       <c r="U37" s="1"/>
@@ -12593,56 +11963,24 @@
       <c r="X37" s="1"/>
     </row>
     <row r="38" spans="1:24">
-      <c r="A38" s="129">
-        <v>1</v>
-      </c>
-      <c r="B38" s="128">
-        <v>1.1538888888888888E-3</v>
-      </c>
-      <c r="C38" s="129">
-        <v>1</v>
-      </c>
-      <c r="D38" s="128">
-        <v>1.1476041666666666E-3</v>
-      </c>
-      <c r="E38" s="129">
-        <v>1</v>
-      </c>
-      <c r="F38" s="128">
-        <v>1.1644560185185187E-3</v>
-      </c>
-      <c r="G38" s="93">
-        <v>1</v>
-      </c>
-      <c r="H38" s="94">
-        <v>1.1644560185185187E-3</v>
-      </c>
+      <c r="A38" s="129"/>
+      <c r="B38" s="128"/>
+      <c r="C38" s="129"/>
+      <c r="D38" s="128"/>
+      <c r="E38" s="129"/>
+      <c r="F38" s="128"/>
+      <c r="G38" s="93"/>
+      <c r="H38" s="94"/>
       <c r="I38" s="1"/>
       <c r="J38" s="1"/>
-      <c r="K38" s="130">
-        <v>1</v>
-      </c>
-      <c r="L38" s="131">
-        <v>1.4355671296296297E-3</v>
-      </c>
-      <c r="M38" s="130">
-        <v>1</v>
-      </c>
-      <c r="N38" s="131">
-        <v>1.4123148148148148E-3</v>
-      </c>
-      <c r="O38" s="89">
-        <v>1</v>
-      </c>
-      <c r="P38" s="90">
-        <v>1.4081597222222223E-3</v>
-      </c>
-      <c r="Q38" s="130">
-        <v>1</v>
-      </c>
-      <c r="R38" s="131">
-        <v>1.4081597222222223E-3</v>
-      </c>
+      <c r="K38" s="130"/>
+      <c r="L38" s="131"/>
+      <c r="M38" s="130"/>
+      <c r="N38" s="131"/>
+      <c r="O38" s="89"/>
+      <c r="P38" s="90"/>
+      <c r="Q38" s="130"/>
+      <c r="R38" s="131"/>
       <c r="S38" s="88"/>
       <c r="T38" s="1"/>
       <c r="U38" s="1"/>
@@ -12651,56 +11989,24 @@
       <c r="X38" s="1"/>
     </row>
     <row r="39" spans="1:24">
-      <c r="A39" s="129">
-        <v>2</v>
-      </c>
-      <c r="B39" s="128">
-        <v>1.1098379629629629E-3</v>
-      </c>
-      <c r="C39" s="129">
-        <v>2</v>
-      </c>
-      <c r="D39" s="128">
-        <v>1.1111458333333333E-3</v>
-      </c>
-      <c r="E39" s="129">
-        <v>2</v>
-      </c>
-      <c r="F39" s="128">
-        <v>1.1378703703703703E-3</v>
-      </c>
-      <c r="G39" s="93">
-        <v>2</v>
-      </c>
-      <c r="H39" s="94">
-        <v>1.1378703703703703E-3</v>
-      </c>
+      <c r="A39" s="129"/>
+      <c r="B39" s="128"/>
+      <c r="C39" s="129"/>
+      <c r="D39" s="128"/>
+      <c r="E39" s="129"/>
+      <c r="F39" s="128"/>
+      <c r="G39" s="93"/>
+      <c r="H39" s="94"/>
       <c r="I39" s="1"/>
       <c r="J39" s="1"/>
-      <c r="K39" s="130">
-        <v>2</v>
-      </c>
-      <c r="L39" s="131">
-        <v>1.1143287037037035E-3</v>
-      </c>
-      <c r="M39" s="130">
-        <v>2</v>
-      </c>
-      <c r="N39" s="131">
-        <v>1.1365393518518519E-3</v>
-      </c>
-      <c r="O39" s="89">
-        <v>2</v>
-      </c>
-      <c r="P39" s="90">
-        <v>1.1394212962962964E-3</v>
-      </c>
-      <c r="Q39" s="130">
-        <v>2</v>
-      </c>
-      <c r="R39" s="131">
-        <v>1.1394212962962964E-3</v>
-      </c>
+      <c r="K39" s="130"/>
+      <c r="L39" s="131"/>
+      <c r="M39" s="130"/>
+      <c r="N39" s="131"/>
+      <c r="O39" s="89"/>
+      <c r="P39" s="90"/>
+      <c r="Q39" s="130"/>
+      <c r="R39" s="131"/>
       <c r="S39" s="1"/>
       <c r="T39" s="1"/>
       <c r="U39" s="1"/>
@@ -12709,56 +12015,24 @@
       <c r="X39" s="1"/>
     </row>
     <row r="40" spans="1:24">
-      <c r="A40" s="129">
-        <v>3</v>
-      </c>
-      <c r="B40" s="128">
-        <v>1.110173611111111E-3</v>
-      </c>
-      <c r="C40" s="129">
-        <v>3</v>
-      </c>
-      <c r="D40" s="128">
-        <v>1.0993171296296296E-3</v>
-      </c>
-      <c r="E40" s="129">
-        <v>3</v>
-      </c>
-      <c r="F40" s="128">
-        <v>1.1312268518518518E-3</v>
-      </c>
-      <c r="G40" s="93">
-        <v>3</v>
-      </c>
-      <c r="H40" s="94">
-        <v>1.1312268518518518E-3</v>
-      </c>
+      <c r="A40" s="129"/>
+      <c r="B40" s="128"/>
+      <c r="C40" s="129"/>
+      <c r="D40" s="128"/>
+      <c r="E40" s="129"/>
+      <c r="F40" s="128"/>
+      <c r="G40" s="93"/>
+      <c r="H40" s="94"/>
       <c r="I40" s="1"/>
       <c r="J40" s="1"/>
-      <c r="K40" s="130">
-        <v>3</v>
-      </c>
-      <c r="L40" s="131">
-        <v>1.1773726851851852E-3</v>
-      </c>
-      <c r="M40" s="130">
-        <v>3</v>
-      </c>
-      <c r="N40" s="131">
-        <v>1.1328703703703702E-3</v>
-      </c>
-      <c r="O40" s="89">
-        <v>3</v>
-      </c>
-      <c r="P40" s="90">
-        <v>1.1317361111111111E-3</v>
-      </c>
-      <c r="Q40" s="130">
-        <v>3</v>
-      </c>
-      <c r="R40" s="131">
-        <v>1.1317361111111111E-3</v>
-      </c>
+      <c r="K40" s="130"/>
+      <c r="L40" s="131"/>
+      <c r="M40" s="130"/>
+      <c r="N40" s="131"/>
+      <c r="O40" s="89"/>
+      <c r="P40" s="90"/>
+      <c r="Q40" s="130"/>
+      <c r="R40" s="131"/>
       <c r="S40" s="1"/>
       <c r="T40" s="1"/>
       <c r="U40" s="1"/>
@@ -12767,56 +12041,24 @@
       <c r="X40" s="1"/>
     </row>
     <row r="41" spans="1:24">
-      <c r="A41" s="129">
-        <v>4</v>
-      </c>
-      <c r="B41" s="128">
-        <v>1.1127083333333334E-3</v>
-      </c>
-      <c r="C41" s="129">
-        <v>4</v>
-      </c>
-      <c r="D41" s="128">
-        <v>1.0976736111111111E-3</v>
-      </c>
-      <c r="E41" s="129">
-        <v>4</v>
-      </c>
-      <c r="F41" s="128">
-        <v>1.1532986111111112E-3</v>
-      </c>
-      <c r="G41" s="93">
-        <v>4</v>
-      </c>
-      <c r="H41" s="94">
-        <v>1.1532986111111112E-3</v>
-      </c>
+      <c r="A41" s="129"/>
+      <c r="B41" s="128"/>
+      <c r="C41" s="129"/>
+      <c r="D41" s="128"/>
+      <c r="E41" s="129"/>
+      <c r="F41" s="128"/>
+      <c r="G41" s="93"/>
+      <c r="H41" s="94"/>
       <c r="I41" s="1"/>
       <c r="J41" s="1"/>
-      <c r="K41" s="130">
-        <v>4</v>
-      </c>
-      <c r="L41" s="131">
-        <v>1.1155787037037037E-3</v>
-      </c>
-      <c r="M41" s="130">
-        <v>4</v>
-      </c>
-      <c r="N41" s="131">
-        <v>1.1118055555555556E-3</v>
-      </c>
-      <c r="O41" s="89">
-        <v>4</v>
-      </c>
-      <c r="P41" s="90">
-        <v>2.0264583333333337E-3</v>
-      </c>
-      <c r="Q41" s="130">
-        <v>4</v>
-      </c>
-      <c r="R41" s="131">
-        <v>2.0264583333333337E-3</v>
-      </c>
+      <c r="K41" s="130"/>
+      <c r="L41" s="131"/>
+      <c r="M41" s="130"/>
+      <c r="N41" s="131"/>
+      <c r="O41" s="89"/>
+      <c r="P41" s="90"/>
+      <c r="Q41" s="130"/>
+      <c r="R41" s="131"/>
       <c r="S41" s="1"/>
       <c r="T41" s="1"/>
       <c r="U41" s="1"/>
@@ -12825,117 +12067,53 @@
       <c r="X41" s="1"/>
     </row>
     <row r="42" spans="1:24">
-      <c r="A42" s="129">
-        <v>5</v>
-      </c>
-      <c r="B42" s="128">
-        <v>1.1121296296296296E-3</v>
-      </c>
-      <c r="C42" s="129">
-        <v>5</v>
-      </c>
-      <c r="D42" s="128">
-        <v>1.1186458333333335E-3</v>
-      </c>
-      <c r="E42" s="129">
-        <v>5</v>
-      </c>
-      <c r="F42" s="128">
-        <v>1.1660416666666668E-3</v>
-      </c>
-      <c r="G42" s="93">
-        <v>5</v>
-      </c>
-      <c r="H42" s="94">
-        <v>1.1660416666666668E-3</v>
-      </c>
+      <c r="A42" s="129"/>
+      <c r="B42" s="128"/>
+      <c r="C42" s="129"/>
+      <c r="D42" s="128"/>
+      <c r="E42" s="129"/>
+      <c r="F42" s="128"/>
+      <c r="G42" s="93"/>
+      <c r="H42" s="94"/>
       <c r="I42" s="1"/>
       <c r="J42" s="1"/>
-      <c r="K42" s="130">
-        <v>5</v>
-      </c>
-      <c r="L42" s="131">
-        <v>1.1346180555555556E-3</v>
-      </c>
-      <c r="M42" s="130">
-        <v>5</v>
-      </c>
-      <c r="N42" s="131">
-        <v>1.0958333333333334E-3</v>
-      </c>
-      <c r="O42" s="89">
-        <v>5</v>
-      </c>
-      <c r="P42" s="90">
-        <v>1.198900462962963E-3</v>
-      </c>
-      <c r="Q42" s="130">
-        <v>5</v>
-      </c>
-      <c r="R42" s="131">
-        <v>1.198900462962963E-3</v>
-      </c>
+      <c r="K42" s="130"/>
+      <c r="L42" s="131"/>
+      <c r="M42" s="130"/>
+      <c r="N42" s="131"/>
+      <c r="O42" s="89"/>
+      <c r="P42" s="90"/>
+      <c r="Q42" s="130"/>
+      <c r="R42" s="131"/>
       <c r="S42" s="1"/>
       <c r="T42" s="1"/>
       <c r="U42" s="1"/>
       <c r="V42" s="1"/>
       <c r="W42" s="54">
         <f>+SUM(D62*1.15)</f>
-        <v>1.2835391865079365E-3</v>
+        <v>0</v>
       </c>
       <c r="X42" s="1"/>
     </row>
     <row r="43" spans="1:24">
-      <c r="A43" s="129">
-        <v>6</v>
-      </c>
-      <c r="B43" s="128">
-        <v>1.1231828703703705E-3</v>
-      </c>
-      <c r="C43" s="129">
-        <v>6</v>
-      </c>
-      <c r="D43" s="128">
-        <v>1.1192708333333332E-3</v>
-      </c>
-      <c r="E43" s="129">
-        <v>6</v>
-      </c>
-      <c r="F43" s="128">
-        <v>1.1783333333333333E-3</v>
-      </c>
-      <c r="G43" s="93">
-        <v>6</v>
-      </c>
-      <c r="H43" s="94">
-        <v>1.1783333333333333E-3</v>
-      </c>
+      <c r="A43" s="129"/>
+      <c r="B43" s="128"/>
+      <c r="C43" s="129"/>
+      <c r="D43" s="128"/>
+      <c r="E43" s="129"/>
+      <c r="F43" s="128"/>
+      <c r="G43" s="93"/>
+      <c r="H43" s="94"/>
       <c r="I43" s="1"/>
       <c r="J43" s="1"/>
-      <c r="K43" s="130">
-        <v>6</v>
-      </c>
-      <c r="L43" s="131">
-        <v>1.1811458333333333E-3</v>
-      </c>
-      <c r="M43" s="130">
-        <v>6</v>
-      </c>
-      <c r="N43" s="131">
-        <v>1.1103587962962964E-3</v>
-      </c>
-      <c r="O43" s="89">
-        <v>6</v>
-      </c>
-      <c r="P43" s="90">
-        <v>1.3676157407407409E-3</v>
-      </c>
-      <c r="Q43" s="130">
-        <v>6</v>
-      </c>
-      <c r="R43" s="131">
-        <v>1.3676157407407409E-3</v>
-      </c>
+      <c r="K43" s="130"/>
+      <c r="L43" s="131"/>
+      <c r="M43" s="130"/>
+      <c r="N43" s="131"/>
+      <c r="O43" s="89"/>
+      <c r="P43" s="90"/>
+      <c r="Q43" s="130"/>
+      <c r="R43" s="131"/>
       <c r="S43" s="1"/>
       <c r="T43" s="1"/>
       <c r="U43" s="1"/>
@@ -12944,56 +12122,24 @@
       <c r="X43" s="1"/>
     </row>
     <row r="44" spans="1:24">
-      <c r="A44" s="129">
-        <v>7</v>
-      </c>
-      <c r="B44" s="128">
-        <v>1.1183564814814815E-3</v>
-      </c>
-      <c r="C44" s="129">
-        <v>7</v>
-      </c>
-      <c r="D44" s="128">
-        <v>1.1119675925925926E-3</v>
-      </c>
-      <c r="E44" s="129">
-        <v>7</v>
-      </c>
-      <c r="F44" s="128">
-        <v>1.1461342592592593E-3</v>
-      </c>
-      <c r="G44" s="93">
-        <v>7</v>
-      </c>
-      <c r="H44" s="94">
-        <v>1.1461342592592593E-3</v>
-      </c>
+      <c r="A44" s="129"/>
+      <c r="B44" s="128"/>
+      <c r="C44" s="129"/>
+      <c r="D44" s="128"/>
+      <c r="E44" s="129"/>
+      <c r="F44" s="128"/>
+      <c r="G44" s="93"/>
+      <c r="H44" s="94"/>
       <c r="I44" s="1"/>
       <c r="J44" s="1"/>
-      <c r="K44" s="130">
-        <v>7</v>
-      </c>
-      <c r="L44" s="131">
-        <v>1.1964467592592591E-3</v>
-      </c>
-      <c r="M44" s="130">
-        <v>7</v>
-      </c>
-      <c r="N44" s="131">
-        <v>1.1330787037037036E-3</v>
-      </c>
-      <c r="O44" s="89">
-        <v>7</v>
-      </c>
-      <c r="P44" s="90">
-        <v>1.2607407407407407E-3</v>
-      </c>
-      <c r="Q44" s="130">
-        <v>7</v>
-      </c>
-      <c r="R44" s="131">
-        <v>1.2607407407407407E-3</v>
-      </c>
+      <c r="K44" s="130"/>
+      <c r="L44" s="131"/>
+      <c r="M44" s="130"/>
+      <c r="N44" s="131"/>
+      <c r="O44" s="89"/>
+      <c r="P44" s="90"/>
+      <c r="Q44" s="130"/>
+      <c r="R44" s="131"/>
       <c r="S44" s="1"/>
       <c r="T44" s="1"/>
       <c r="U44" s="1"/>
@@ -13002,117 +12148,53 @@
       <c r="X44" s="1"/>
     </row>
     <row r="45" spans="1:24">
-      <c r="A45" s="129">
-        <v>8</v>
-      </c>
-      <c r="B45" s="128">
-        <v>1.124398148148148E-3</v>
-      </c>
-      <c r="C45" s="129">
-        <v>8</v>
-      </c>
-      <c r="D45" s="128">
-        <v>1.1048148148148148E-3</v>
-      </c>
-      <c r="E45" s="129">
-        <v>8</v>
-      </c>
-      <c r="F45" s="128">
-        <v>1.2261226851851851E-3</v>
-      </c>
-      <c r="G45" s="93">
-        <v>8</v>
-      </c>
-      <c r="H45" s="94">
-        <v>1.2261226851851851E-3</v>
-      </c>
+      <c r="A45" s="129"/>
+      <c r="B45" s="128"/>
+      <c r="C45" s="129"/>
+      <c r="D45" s="128"/>
+      <c r="E45" s="129"/>
+      <c r="F45" s="128"/>
+      <c r="G45" s="93"/>
+      <c r="H45" s="94"/>
       <c r="I45" s="1"/>
       <c r="J45" s="1"/>
-      <c r="K45" s="130">
-        <v>8</v>
-      </c>
-      <c r="L45" s="131">
-        <v>1.1544097222222223E-3</v>
-      </c>
-      <c r="M45" s="130">
-        <v>8</v>
-      </c>
-      <c r="N45" s="131">
-        <v>1.1489930555555554E-3</v>
-      </c>
-      <c r="O45" s="89">
-        <v>8</v>
-      </c>
-      <c r="P45" s="90">
-        <v>1.1238657407407408E-3</v>
-      </c>
-      <c r="Q45" s="130">
-        <v>8</v>
-      </c>
-      <c r="R45" s="131">
-        <v>1.1238657407407408E-3</v>
-      </c>
+      <c r="K45" s="130"/>
+      <c r="L45" s="131"/>
+      <c r="M45" s="130"/>
+      <c r="N45" s="131"/>
+      <c r="O45" s="89"/>
+      <c r="P45" s="90"/>
+      <c r="Q45" s="130"/>
+      <c r="R45" s="131"/>
       <c r="S45" s="1"/>
       <c r="T45" s="1"/>
       <c r="U45" s="1"/>
       <c r="V45" s="1"/>
       <c r="W45" s="54">
         <f>+SUM(F60*1.05)</f>
-        <v>1.2315920138888891E-3</v>
+        <v>0</v>
       </c>
       <c r="X45" s="1"/>
     </row>
     <row r="46" spans="1:24">
-      <c r="A46" s="129">
-        <v>9</v>
-      </c>
-      <c r="B46" s="128">
-        <v>1.2592476851851853E-3</v>
-      </c>
-      <c r="C46" s="129">
-        <v>9</v>
-      </c>
-      <c r="D46" s="128">
-        <v>1.0967939814814816E-3</v>
-      </c>
-      <c r="E46" s="129">
-        <v>9</v>
-      </c>
-      <c r="F46" s="128">
-        <v>1.1561111111111112E-3</v>
-      </c>
-      <c r="G46" s="93">
-        <v>9</v>
-      </c>
-      <c r="H46" s="94">
-        <v>1.1561111111111112E-3</v>
-      </c>
+      <c r="A46" s="129"/>
+      <c r="B46" s="128"/>
+      <c r="C46" s="129"/>
+      <c r="D46" s="128"/>
+      <c r="E46" s="129"/>
+      <c r="F46" s="128"/>
+      <c r="G46" s="93"/>
+      <c r="H46" s="94"/>
       <c r="I46" s="1"/>
       <c r="J46" s="1"/>
-      <c r="K46" s="130">
-        <v>9</v>
-      </c>
-      <c r="L46" s="131">
-        <v>1.2505092592592592E-3</v>
-      </c>
-      <c r="M46" s="130">
-        <v>9</v>
-      </c>
-      <c r="N46" s="131">
-        <v>1.1331134259259261E-3</v>
-      </c>
-      <c r="O46" s="89">
-        <v>9</v>
-      </c>
-      <c r="P46" s="90">
-        <v>1.2741203703703703E-3</v>
-      </c>
-      <c r="Q46" s="130">
-        <v>9</v>
-      </c>
-      <c r="R46" s="131">
-        <v>1.2741203703703703E-3</v>
-      </c>
+      <c r="K46" s="130"/>
+      <c r="L46" s="131"/>
+      <c r="M46" s="130"/>
+      <c r="N46" s="131"/>
+      <c r="O46" s="89"/>
+      <c r="P46" s="90"/>
+      <c r="Q46" s="130"/>
+      <c r="R46" s="131"/>
       <c r="S46" s="1"/>
       <c r="T46" s="1"/>
       <c r="U46" s="1"/>
@@ -13121,56 +12203,24 @@
       <c r="X46" s="1"/>
     </row>
     <row r="47" spans="1:24">
-      <c r="A47" s="129">
-        <v>10</v>
-      </c>
-      <c r="B47" s="128">
-        <v>1.1363194444444444E-3</v>
-      </c>
-      <c r="C47" s="129">
-        <v>10</v>
-      </c>
-      <c r="D47" s="128">
-        <v>1.1534143518518519E-3</v>
-      </c>
-      <c r="E47" s="129">
-        <v>10</v>
-      </c>
-      <c r="F47" s="128">
-        <v>1.1621296296296297E-3</v>
-      </c>
-      <c r="G47" s="93">
-        <v>10</v>
-      </c>
-      <c r="H47" s="94">
-        <v>1.1621296296296297E-3</v>
-      </c>
+      <c r="A47" s="129"/>
+      <c r="B47" s="128"/>
+      <c r="C47" s="129"/>
+      <c r="D47" s="128"/>
+      <c r="E47" s="129"/>
+      <c r="F47" s="128"/>
+      <c r="G47" s="93"/>
+      <c r="H47" s="94"/>
       <c r="I47" s="1"/>
       <c r="J47" s="1"/>
-      <c r="K47" s="130">
-        <v>10</v>
-      </c>
-      <c r="L47" s="131">
-        <v>1.1465856481481481E-3</v>
-      </c>
-      <c r="M47" s="130">
-        <v>10</v>
-      </c>
-      <c r="N47" s="131">
-        <v>1.1556481481481481E-3</v>
-      </c>
-      <c r="O47" s="89">
-        <v>10</v>
-      </c>
-      <c r="P47" s="90">
-        <v>1.1596180555555557E-3</v>
-      </c>
-      <c r="Q47" s="130">
-        <v>10</v>
-      </c>
-      <c r="R47" s="131">
-        <v>1.1596180555555557E-3</v>
-      </c>
+      <c r="K47" s="130"/>
+      <c r="L47" s="131"/>
+      <c r="M47" s="130"/>
+      <c r="N47" s="131"/>
+      <c r="O47" s="89"/>
+      <c r="P47" s="90"/>
+      <c r="Q47" s="130"/>
+      <c r="R47" s="131"/>
       <c r="S47" s="1"/>
       <c r="T47" s="1"/>
       <c r="U47" s="1"/>
@@ -13179,56 +12229,24 @@
       <c r="X47" s="1"/>
     </row>
     <row r="48" spans="1:24">
-      <c r="A48" s="129">
-        <v>11</v>
-      </c>
-      <c r="B48" s="128">
-        <v>1.3982291666666668E-3</v>
-      </c>
-      <c r="C48" s="129">
-        <v>11</v>
-      </c>
-      <c r="D48" s="128">
-        <v>1.2330902777777778E-3</v>
-      </c>
-      <c r="E48" s="129">
-        <v>11</v>
-      </c>
-      <c r="F48" s="128">
-        <v>1.2419907407407406E-3</v>
-      </c>
-      <c r="G48" s="93">
-        <v>11</v>
-      </c>
-      <c r="H48" s="94">
-        <v>1.2419907407407406E-3</v>
-      </c>
+      <c r="A48" s="129"/>
+      <c r="B48" s="128"/>
+      <c r="C48" s="129"/>
+      <c r="D48" s="128"/>
+      <c r="E48" s="129"/>
+      <c r="F48" s="128"/>
+      <c r="G48" s="93"/>
+      <c r="H48" s="94"/>
       <c r="I48" s="1"/>
       <c r="J48" s="1"/>
-      <c r="K48" s="130">
-        <v>11</v>
-      </c>
-      <c r="L48" s="131">
-        <v>1.1611226851851852E-3</v>
-      </c>
-      <c r="M48" s="130">
-        <v>11</v>
-      </c>
-      <c r="N48" s="131">
-        <v>1.2279976851851851E-3</v>
-      </c>
-      <c r="O48" s="89">
-        <v>11</v>
-      </c>
-      <c r="P48" s="90">
-        <v>2.1243171296296296E-3</v>
-      </c>
-      <c r="Q48" s="130">
-        <v>11</v>
-      </c>
-      <c r="R48" s="131">
-        <v>2.1243171296296296E-3</v>
-      </c>
+      <c r="K48" s="130"/>
+      <c r="L48" s="131"/>
+      <c r="M48" s="130"/>
+      <c r="N48" s="131"/>
+      <c r="O48" s="89"/>
+      <c r="P48" s="90"/>
+      <c r="Q48" s="130"/>
+      <c r="R48" s="131"/>
       <c r="S48" s="1"/>
       <c r="T48" s="1"/>
       <c r="U48" s="1"/>
@@ -13237,117 +12255,53 @@
       <c r="X48" s="1"/>
     </row>
     <row r="49" spans="1:24">
-      <c r="A49" s="129">
-        <v>12</v>
-      </c>
-      <c r="B49" s="128">
-        <v>1.5461458333333332E-3</v>
-      </c>
-      <c r="C49" s="129">
-        <v>12</v>
-      </c>
-      <c r="D49" s="128">
-        <v>1.9078009259259261E-3</v>
-      </c>
-      <c r="E49" s="129">
-        <v>12</v>
-      </c>
-      <c r="F49" s="128">
-        <v>1.4453819444444444E-3</v>
-      </c>
-      <c r="G49" s="93">
-        <v>12</v>
-      </c>
-      <c r="H49" s="94">
-        <v>1.4453819444444444E-3</v>
-      </c>
+      <c r="A49" s="129"/>
+      <c r="B49" s="128"/>
+      <c r="C49" s="129"/>
+      <c r="D49" s="128"/>
+      <c r="E49" s="129"/>
+      <c r="F49" s="128"/>
+      <c r="G49" s="93"/>
+      <c r="H49" s="94"/>
       <c r="I49" s="1"/>
       <c r="J49" s="1"/>
-      <c r="K49" s="130">
-        <v>12</v>
-      </c>
-      <c r="L49" s="131">
-        <v>1.3398611111111113E-3</v>
-      </c>
-      <c r="M49" s="130">
-        <v>12</v>
-      </c>
-      <c r="N49" s="131">
-        <v>1.310949074074074E-3</v>
-      </c>
-      <c r="O49" s="89">
-        <v>12</v>
-      </c>
-      <c r="P49" s="90">
-        <v>1.4692245370370371E-3</v>
-      </c>
-      <c r="Q49" s="130">
-        <v>12</v>
-      </c>
-      <c r="R49" s="131">
-        <v>1.4692245370370371E-3</v>
-      </c>
+      <c r="K49" s="130"/>
+      <c r="L49" s="131"/>
+      <c r="M49" s="130"/>
+      <c r="N49" s="131"/>
+      <c r="O49" s="89"/>
+      <c r="P49" s="90"/>
+      <c r="Q49" s="130"/>
+      <c r="R49" s="131"/>
       <c r="S49" s="1"/>
       <c r="T49" s="1"/>
       <c r="U49" s="1"/>
       <c r="V49" s="1"/>
-      <c r="W49" s="54" t="e">
+      <c r="W49" s="54">
         <f>+SUM(F64*1.1)</f>
-        <v>#VALUE!</v>
+        <v>0</v>
       </c>
       <c r="X49" s="1"/>
     </row>
     <row r="50" spans="1:24">
-      <c r="A50" s="129">
-        <v>13</v>
-      </c>
-      <c r="B50" s="128">
-        <v>1.2216550925925925E-3</v>
-      </c>
-      <c r="C50" s="129">
-        <v>13</v>
-      </c>
-      <c r="D50" s="128">
-        <v>1.2544560185185185E-3</v>
-      </c>
-      <c r="E50" s="129">
-        <v>13</v>
-      </c>
-      <c r="F50" s="128">
-        <v>1.2557175925925926E-3</v>
-      </c>
-      <c r="G50" s="93">
-        <v>13</v>
-      </c>
-      <c r="H50" s="94">
-        <v>1.2557175925925926E-3</v>
-      </c>
+      <c r="A50" s="129"/>
+      <c r="B50" s="128"/>
+      <c r="C50" s="129"/>
+      <c r="D50" s="128"/>
+      <c r="E50" s="129"/>
+      <c r="F50" s="128"/>
+      <c r="G50" s="93"/>
+      <c r="H50" s="94"/>
       <c r="I50" s="1"/>
       <c r="J50" s="1"/>
-      <c r="K50" s="130">
-        <v>13</v>
-      </c>
-      <c r="L50" s="131">
-        <v>3.8921759259259257E-3</v>
-      </c>
-      <c r="M50" s="130">
-        <v>13</v>
-      </c>
-      <c r="N50" s="131">
-        <v>4.1754282407407408E-3</v>
-      </c>
-      <c r="O50" s="89">
-        <v>13</v>
-      </c>
-      <c r="P50" s="90">
-        <v>1.6091435185185184E-3</v>
-      </c>
-      <c r="Q50" s="130">
-        <v>13</v>
-      </c>
-      <c r="R50" s="131">
-        <v>1.6091435185185184E-3</v>
-      </c>
+      <c r="K50" s="130"/>
+      <c r="L50" s="131"/>
+      <c r="M50" s="130"/>
+      <c r="N50" s="131"/>
+      <c r="O50" s="89"/>
+      <c r="P50" s="90"/>
+      <c r="Q50" s="130"/>
+      <c r="R50" s="131"/>
       <c r="S50" s="1"/>
       <c r="T50" s="1"/>
       <c r="U50" s="1"/>
@@ -13356,56 +12310,24 @@
       <c r="X50" s="1"/>
     </row>
     <row r="51" spans="1:24">
-      <c r="A51" s="129">
-        <v>14</v>
-      </c>
-      <c r="B51" s="128">
-        <v>1.1457523148148147E-3</v>
-      </c>
-      <c r="C51" s="129">
-        <v>14</v>
-      </c>
-      <c r="D51" s="128">
-        <v>1.1745949074074074E-3</v>
-      </c>
-      <c r="E51" s="129">
-        <v>14</v>
-      </c>
-      <c r="F51" s="128">
-        <v>1.1743055555555556E-3</v>
-      </c>
-      <c r="G51" s="93">
-        <v>14</v>
-      </c>
-      <c r="H51" s="94">
-        <v>1.1743055555555556E-3</v>
-      </c>
+      <c r="A51" s="129"/>
+      <c r="B51" s="128"/>
+      <c r="C51" s="129"/>
+      <c r="D51" s="128"/>
+      <c r="E51" s="129"/>
+      <c r="F51" s="128"/>
+      <c r="G51" s="93"/>
+      <c r="H51" s="94"/>
       <c r="I51" s="1"/>
       <c r="J51" s="1"/>
-      <c r="K51" s="130">
-        <v>14</v>
-      </c>
-      <c r="L51" s="131">
-        <v>1.1608564814814815E-3</v>
-      </c>
-      <c r="M51" s="130">
-        <v>14</v>
-      </c>
-      <c r="N51" s="131">
-        <v>1.1806365740740742E-3</v>
-      </c>
-      <c r="O51" s="89">
-        <v>14</v>
-      </c>
-      <c r="P51" s="90">
-        <v>1.1635069444444444E-3</v>
-      </c>
-      <c r="Q51" s="130">
-        <v>14</v>
-      </c>
-      <c r="R51" s="131">
-        <v>1.1635069444444444E-3</v>
-      </c>
+      <c r="K51" s="130"/>
+      <c r="L51" s="131"/>
+      <c r="M51" s="130"/>
+      <c r="N51" s="131"/>
+      <c r="O51" s="89"/>
+      <c r="P51" s="90"/>
+      <c r="Q51" s="130"/>
+      <c r="R51" s="131"/>
       <c r="S51" s="1"/>
       <c r="T51" s="1"/>
       <c r="U51" s="1"/>
@@ -13414,56 +12336,24 @@
       <c r="X51" s="1"/>
     </row>
     <row r="52" spans="1:24">
-      <c r="A52" s="129">
-        <v>15</v>
-      </c>
-      <c r="B52" s="128">
-        <v>1.5789930555555557E-3</v>
-      </c>
-      <c r="C52" s="129">
-        <v>15</v>
-      </c>
-      <c r="D52" s="128">
-        <v>1.544236111111111E-3</v>
-      </c>
-      <c r="E52" s="129">
-        <v>15</v>
-      </c>
-      <c r="F52" s="128">
-        <v>1.5701967592592592E-3</v>
-      </c>
-      <c r="G52" s="93">
-        <v>15</v>
-      </c>
-      <c r="H52" s="94">
-        <v>1.5701967592592592E-3</v>
-      </c>
+      <c r="A52" s="129"/>
+      <c r="B52" s="128"/>
+      <c r="C52" s="129"/>
+      <c r="D52" s="128"/>
+      <c r="E52" s="129"/>
+      <c r="F52" s="128"/>
+      <c r="G52" s="93"/>
+      <c r="H52" s="94"/>
       <c r="I52" s="1"/>
       <c r="J52" s="1"/>
-      <c r="K52" s="130">
-        <v>15</v>
-      </c>
-      <c r="L52" s="131">
-        <v>1.1989930555555556E-3</v>
-      </c>
-      <c r="M52" s="130">
-        <v>15</v>
-      </c>
-      <c r="N52" s="131">
-        <v>1.1869444444444445E-3</v>
-      </c>
-      <c r="O52" s="89">
-        <v>15</v>
-      </c>
-      <c r="P52" s="90">
-        <v>1.1449421296296297E-3</v>
-      </c>
-      <c r="Q52" s="130">
-        <v>15</v>
-      </c>
-      <c r="R52" s="131">
-        <v>1.1449421296296297E-3</v>
-      </c>
+      <c r="K52" s="130"/>
+      <c r="L52" s="131"/>
+      <c r="M52" s="130"/>
+      <c r="N52" s="131"/>
+      <c r="O52" s="89"/>
+      <c r="P52" s="90"/>
+      <c r="Q52" s="130"/>
+      <c r="R52" s="131"/>
       <c r="S52" s="1"/>
       <c r="T52" s="1"/>
       <c r="U52" s="1"/>
@@ -13472,56 +12362,24 @@
       <c r="X52" s="1"/>
     </row>
     <row r="53" spans="1:24">
-      <c r="A53" s="129">
-        <v>16</v>
-      </c>
-      <c r="B53" s="128">
-        <v>1.1158217592592591E-3</v>
-      </c>
-      <c r="C53" s="129">
-        <v>16</v>
-      </c>
-      <c r="D53" s="128">
-        <v>1.1127083333333334E-3</v>
-      </c>
-      <c r="E53" s="129">
-        <v>16</v>
-      </c>
-      <c r="F53" s="128">
-        <v>1.2513888888888889E-3</v>
-      </c>
-      <c r="G53" s="93">
-        <v>16</v>
-      </c>
-      <c r="H53" s="94">
-        <v>1.2513888888888889E-3</v>
-      </c>
+      <c r="A53" s="129"/>
+      <c r="B53" s="128"/>
+      <c r="C53" s="129"/>
+      <c r="D53" s="128"/>
+      <c r="E53" s="129"/>
+      <c r="F53" s="128"/>
+      <c r="G53" s="93"/>
+      <c r="H53" s="94"/>
       <c r="I53" s="1"/>
       <c r="J53" s="1"/>
-      <c r="K53" s="130">
-        <v>16</v>
-      </c>
-      <c r="L53" s="131">
-        <v>1.1175E-3</v>
-      </c>
-      <c r="M53" s="130">
-        <v>16</v>
-      </c>
-      <c r="N53" s="131">
-        <v>1.1115046296296296E-3</v>
-      </c>
-      <c r="O53" s="89">
-        <v>16</v>
-      </c>
-      <c r="P53" s="90">
-        <v>1.140324074074074E-3</v>
-      </c>
-      <c r="Q53" s="130">
-        <v>16</v>
-      </c>
-      <c r="R53" s="131">
-        <v>1.140324074074074E-3</v>
-      </c>
+      <c r="K53" s="130"/>
+      <c r="L53" s="131"/>
+      <c r="M53" s="130"/>
+      <c r="N53" s="131"/>
+      <c r="O53" s="89"/>
+      <c r="P53" s="90"/>
+      <c r="Q53" s="130"/>
+      <c r="R53" s="131"/>
       <c r="S53" s="1"/>
       <c r="T53" s="1"/>
       <c r="U53" s="1"/>
@@ -13530,56 +12388,24 @@
       <c r="X53" s="1"/>
     </row>
     <row r="54" spans="1:24">
-      <c r="A54" s="129">
-        <v>17</v>
-      </c>
-      <c r="B54" s="128">
-        <v>1.1162731481481481E-3</v>
-      </c>
-      <c r="C54" s="129">
-        <v>17</v>
-      </c>
-      <c r="D54" s="128">
-        <v>1.1204629629629629E-3</v>
-      </c>
-      <c r="E54" s="129">
-        <v>17</v>
-      </c>
-      <c r="F54" s="128">
-        <v>1.1524421296296296E-3</v>
-      </c>
-      <c r="G54" s="93">
-        <v>17</v>
-      </c>
-      <c r="H54" s="94">
-        <v>1.1524421296296296E-3</v>
-      </c>
+      <c r="A54" s="129"/>
+      <c r="B54" s="128"/>
+      <c r="C54" s="129"/>
+      <c r="D54" s="128"/>
+      <c r="E54" s="129"/>
+      <c r="F54" s="128"/>
+      <c r="G54" s="93"/>
+      <c r="H54" s="94"/>
       <c r="I54" s="1"/>
       <c r="J54" s="1"/>
-      <c r="K54" s="130">
-        <v>17</v>
-      </c>
-      <c r="L54" s="131">
-        <v>1.133587962962963E-3</v>
-      </c>
-      <c r="M54" s="130">
-        <v>17</v>
-      </c>
-      <c r="N54" s="131">
-        <v>1.1427777777777777E-3</v>
-      </c>
-      <c r="O54" s="89">
-        <v>17</v>
-      </c>
-      <c r="P54" s="90">
-        <v>1.1632407407407407E-3</v>
-      </c>
-      <c r="Q54" s="130">
-        <v>17</v>
-      </c>
-      <c r="R54" s="131">
-        <v>1.1632407407407407E-3</v>
-      </c>
+      <c r="K54" s="130"/>
+      <c r="L54" s="131"/>
+      <c r="M54" s="130"/>
+      <c r="N54" s="131"/>
+      <c r="O54" s="89"/>
+      <c r="P54" s="90"/>
+      <c r="Q54" s="130"/>
+      <c r="R54" s="131"/>
       <c r="S54" s="54"/>
       <c r="T54" s="1"/>
       <c r="U54" s="1"/>
@@ -13588,56 +12414,24 @@
       <c r="X54" s="1"/>
     </row>
     <row r="55" spans="1:24">
-      <c r="A55" s="129">
-        <v>18</v>
-      </c>
-      <c r="B55" s="128">
-        <v>1.114398148148148E-3</v>
-      </c>
-      <c r="C55" s="129">
-        <v>18</v>
-      </c>
-      <c r="D55" s="128">
-        <v>1.1069444444444445E-3</v>
-      </c>
-      <c r="E55" s="129">
-        <v>18</v>
-      </c>
-      <c r="F55" s="128">
-        <v>1.1676157407407408E-3</v>
-      </c>
-      <c r="G55" s="93">
-        <v>18</v>
-      </c>
-      <c r="H55" s="94">
-        <v>1.1676157407407408E-3</v>
-      </c>
+      <c r="A55" s="129"/>
+      <c r="B55" s="128"/>
+      <c r="C55" s="129"/>
+      <c r="D55" s="128"/>
+      <c r="E55" s="129"/>
+      <c r="F55" s="128"/>
+      <c r="G55" s="93"/>
+      <c r="H55" s="94"/>
       <c r="I55" s="1"/>
       <c r="J55" s="1"/>
-      <c r="K55" s="130">
-        <v>18</v>
-      </c>
-      <c r="L55" s="131">
-        <v>1.1378240740740741E-3</v>
-      </c>
-      <c r="M55" s="130">
-        <v>18</v>
-      </c>
-      <c r="N55" s="131">
-        <v>1.1362962962962963E-3</v>
-      </c>
-      <c r="O55" s="89">
-        <v>18</v>
-      </c>
-      <c r="P55" s="90">
-        <v>1.1319444444444443E-3</v>
-      </c>
-      <c r="Q55" s="130">
-        <v>18</v>
-      </c>
-      <c r="R55" s="131">
-        <v>1.1319444444444443E-3</v>
-      </c>
+      <c r="K55" s="130"/>
+      <c r="L55" s="131"/>
+      <c r="M55" s="130"/>
+      <c r="N55" s="131"/>
+      <c r="O55" s="89"/>
+      <c r="P55" s="90"/>
+      <c r="Q55" s="130"/>
+      <c r="R55" s="131"/>
       <c r="S55" s="54"/>
       <c r="T55" s="1"/>
       <c r="U55" s="1"/>
@@ -13646,56 +12440,24 @@
       <c r="X55" s="1"/>
     </row>
     <row r="56" spans="1:24">
-      <c r="A56" s="129">
-        <v>19</v>
-      </c>
-      <c r="B56" s="128">
-        <v>1.1236805555555555E-3</v>
-      </c>
-      <c r="C56" s="129">
-        <v>19</v>
-      </c>
-      <c r="D56" s="128">
-        <v>1.1092129629629629E-3</v>
-      </c>
-      <c r="E56" s="129">
-        <v>19</v>
-      </c>
-      <c r="F56" s="128">
-        <v>1.1594328703703703E-3</v>
-      </c>
-      <c r="G56" s="93">
-        <v>19</v>
-      </c>
-      <c r="H56" s="94">
-        <v>1.1594328703703703E-3</v>
-      </c>
+      <c r="A56" s="129"/>
+      <c r="B56" s="128"/>
+      <c r="C56" s="129"/>
+      <c r="D56" s="128"/>
+      <c r="E56" s="129"/>
+      <c r="F56" s="128"/>
+      <c r="G56" s="93"/>
+      <c r="H56" s="94"/>
       <c r="I56" s="1"/>
       <c r="J56" s="1"/>
-      <c r="K56" s="130">
-        <v>19</v>
-      </c>
-      <c r="L56" s="131">
-        <v>1.1439699074074073E-3</v>
-      </c>
-      <c r="M56" s="130">
-        <v>19</v>
-      </c>
-      <c r="N56" s="131">
-        <v>1.1471990740740739E-3</v>
-      </c>
-      <c r="O56" s="89">
-        <v>19</v>
-      </c>
-      <c r="P56" s="90">
-        <v>1.149375E-3</v>
-      </c>
-      <c r="Q56" s="130">
-        <v>19</v>
-      </c>
-      <c r="R56" s="131">
-        <v>1.149375E-3</v>
-      </c>
+      <c r="K56" s="130"/>
+      <c r="L56" s="131"/>
+      <c r="M56" s="130"/>
+      <c r="N56" s="131"/>
+      <c r="O56" s="89"/>
+      <c r="P56" s="90"/>
+      <c r="Q56" s="130"/>
+      <c r="R56" s="131"/>
       <c r="S56" s="54"/>
       <c r="T56" s="1"/>
       <c r="U56" s="1"/>
@@ -13709,56 +12471,24 @@
       </c>
     </row>
     <row r="57" spans="1:24">
-      <c r="A57" s="129">
-        <v>20</v>
-      </c>
-      <c r="B57" s="128">
-        <v>1.1430092592592592E-3</v>
-      </c>
-      <c r="C57" s="129">
-        <v>20</v>
-      </c>
-      <c r="D57" s="128">
-        <v>1.1691319444444444E-3</v>
-      </c>
-      <c r="E57" s="129">
-        <v>20</v>
-      </c>
-      <c r="F57" s="128">
-        <v>1.2307523148148149E-3</v>
-      </c>
-      <c r="G57" s="93">
-        <v>20</v>
-      </c>
-      <c r="H57" s="94">
-        <v>1.2307523148148149E-3</v>
-      </c>
+      <c r="A57" s="129"/>
+      <c r="B57" s="128"/>
+      <c r="C57" s="129"/>
+      <c r="D57" s="128"/>
+      <c r="E57" s="129"/>
+      <c r="F57" s="128"/>
+      <c r="G57" s="93"/>
+      <c r="H57" s="94"/>
       <c r="I57" s="1"/>
       <c r="J57" s="1"/>
-      <c r="K57" s="132">
-        <v>20</v>
-      </c>
-      <c r="L57" s="133">
-        <v>1.1290277777777778E-3</v>
-      </c>
-      <c r="M57" s="132">
-        <v>20</v>
-      </c>
-      <c r="N57" s="133">
-        <v>1.1019907407407408E-3</v>
-      </c>
-      <c r="O57" s="91">
-        <v>20</v>
-      </c>
-      <c r="P57" s="92">
-        <v>1.1516666666666665E-3</v>
-      </c>
-      <c r="Q57" s="132">
-        <v>20</v>
-      </c>
-      <c r="R57" s="133">
-        <v>1.1516666666666665E-3</v>
-      </c>
+      <c r="K57" s="132"/>
+      <c r="L57" s="133"/>
+      <c r="M57" s="132"/>
+      <c r="N57" s="133"/>
+      <c r="O57" s="91"/>
+      <c r="P57" s="92"/>
+      <c r="Q57" s="132"/>
+      <c r="R57" s="133"/>
       <c r="S57" s="1"/>
       <c r="T57" s="1"/>
       <c r="U57" s="1"/>
@@ -13822,52 +12552,24 @@
       <c r="X59" s="1"/>
     </row>
     <row r="60" spans="1:24">
-      <c r="A60" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="B60" s="54">
-        <f>+AVERAGE(B38:B46,B53:B57)</f>
-        <v>1.1312218915343914E-3</v>
-      </c>
+      <c r="A60" s="1"/>
+      <c r="B60" s="54"/>
       <c r="C60" s="1"/>
-      <c r="D60" s="54">
-        <f>+AVERAGE(D38:D46,D53:D57)</f>
-        <v>1.1161210317460319E-3</v>
-      </c>
+      <c r="D60" s="54"/>
       <c r="E60" s="1"/>
-      <c r="F60" s="54">
-        <f>+AVERAGE(F38:F46,F53:F57)</f>
-        <v>1.1729447751322752E-3</v>
-      </c>
+      <c r="F60" s="54"/>
       <c r="G60" s="1"/>
-      <c r="H60" s="54">
-        <f>+AVERAGE(H38:H46,H53:H57)</f>
-        <v>1.1729447751322752E-3</v>
-      </c>
+      <c r="H60" s="54"/>
       <c r="I60" s="1"/>
       <c r="J60" s="1"/>
-      <c r="K60" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="L60" s="54">
-        <f>+AVERAGE(L38:L48,L51:L57)</f>
-        <v>1.1716358024691359E-3</v>
-      </c>
+      <c r="K60" s="1"/>
+      <c r="L60" s="54"/>
       <c r="M60" s="1"/>
-      <c r="N60" s="54">
-        <f>+AVERAGE(N38:N48,N51:N57)</f>
-        <v>1.1558834876543207E-3</v>
-      </c>
+      <c r="N60" s="54"/>
       <c r="O60" s="1"/>
-      <c r="P60" s="54">
-        <f>+AVERAGE(P38:P48,P51:P57)</f>
-        <v>1.2922196502057615E-3</v>
-      </c>
+      <c r="P60" s="54"/>
       <c r="Q60" s="1"/>
-      <c r="R60" s="54">
-        <f>+AVERAGE(R38:R48,R51:R57)</f>
-        <v>1.2922196502057615E-3</v>
-      </c>
+      <c r="R60" s="54"/>
       <c r="S60" s="1"/>
       <c r="T60" s="1"/>
       <c r="U60" s="1"/>
@@ -13903,45 +12605,23 @@
     </row>
     <row r="62" spans="1:24">
       <c r="A62" s="1"/>
-      <c r="B62" s="87">
-        <f>+SUM(B60-D60)</f>
-        <v>1.5100859788359528E-5</v>
-      </c>
+      <c r="B62" s="87"/>
       <c r="C62" s="86"/>
-      <c r="D62" s="54">
-        <v>1.1161210317460319E-3</v>
-      </c>
+      <c r="D62" s="54"/>
       <c r="E62" s="86"/>
-      <c r="F62" s="87">
-        <f>+SUM(F60-D60)</f>
-        <v>5.6823743386243304E-5</v>
-      </c>
+      <c r="F62" s="87"/>
       <c r="G62" s="1"/>
-      <c r="H62" s="87">
-        <f>+SUM(H60-D60)</f>
-        <v>5.6823743386243304E-5</v>
-      </c>
+      <c r="H62" s="87"/>
       <c r="I62" s="1"/>
       <c r="J62" s="1"/>
       <c r="K62" s="1"/>
-      <c r="L62" s="87">
-        <f>+SUM(L60-N60)</f>
-        <v>1.5752314814815229E-5</v>
-      </c>
+      <c r="L62" s="87"/>
       <c r="M62" s="86"/>
-      <c r="N62" s="54">
-        <v>1.1558834876543207E-3</v>
-      </c>
+      <c r="N62" s="54"/>
       <c r="O62" s="86"/>
-      <c r="P62" s="87">
-        <f>+SUM(P60-N60)</f>
-        <v>1.3633616255144076E-4</v>
-      </c>
+      <c r="P62" s="87"/>
       <c r="Q62" s="1"/>
-      <c r="R62" s="87">
-        <f>+SUM(R60-N60)</f>
-        <v>1.3633616255144076E-4</v>
-      </c>
+      <c r="R62" s="87"/>
       <c r="S62" s="1"/>
       <c r="T62" s="1"/>
       <c r="U62" s="1"/>
@@ -13976,44 +12656,24 @@
       <c r="X63" s="1"/>
     </row>
     <row r="64" spans="1:24">
-      <c r="A64" s="86" t="s">
-        <v>94</v>
-      </c>
-      <c r="B64" s="54" t="s">
-        <v>99</v>
-      </c>
+      <c r="A64" s="86"/>
+      <c r="B64" s="54"/>
       <c r="C64" s="1"/>
-      <c r="D64" s="54" t="s">
-        <v>100</v>
-      </c>
+      <c r="D64" s="54"/>
       <c r="E64" s="1"/>
-      <c r="F64" s="54" t="s">
-        <v>101</v>
-      </c>
+      <c r="F64" s="54"/>
       <c r="G64" s="1"/>
-      <c r="H64" s="54" t="s">
-        <v>102</v>
-      </c>
+      <c r="H64" s="54"/>
       <c r="I64" s="1"/>
       <c r="J64" s="1"/>
-      <c r="K64" s="86" t="s">
-        <v>94</v>
-      </c>
-      <c r="L64" s="54" t="s">
-        <v>103</v>
-      </c>
+      <c r="K64" s="86"/>
+      <c r="L64" s="54"/>
       <c r="M64" s="1"/>
-      <c r="N64" s="54" t="s">
-        <v>104</v>
-      </c>
+      <c r="N64" s="54"/>
       <c r="O64" s="1"/>
-      <c r="P64" s="54" t="s">
-        <v>105</v>
-      </c>
+      <c r="P64" s="54"/>
       <c r="Q64" s="1"/>
-      <c r="R64" s="54" t="s">
-        <v>106</v>
-      </c>
+      <c r="R64" s="54"/>
       <c r="S64" s="1"/>
       <c r="T64" s="1"/>
       <c r="U64" s="1"/>
@@ -14074,28 +12734,24 @@
       <c r="X66" s="1"/>
     </row>
     <row r="67" spans="1:24" ht="34.5">
-      <c r="A67" s="120" t="s">
-        <v>107</v>
-      </c>
-      <c r="B67" s="120"/>
-      <c r="C67" s="120"/>
-      <c r="D67" s="120"/>
-      <c r="E67" s="120"/>
-      <c r="F67" s="120"/>
-      <c r="G67" s="120"/>
-      <c r="H67" s="120"/>
+      <c r="A67" s="108"/>
+      <c r="B67" s="108"/>
+      <c r="C67" s="108"/>
+      <c r="D67" s="108"/>
+      <c r="E67" s="108"/>
+      <c r="F67" s="108"/>
+      <c r="G67" s="108"/>
+      <c r="H67" s="108"/>
       <c r="I67" s="1"/>
       <c r="J67" s="1"/>
-      <c r="K67" s="120" t="s">
-        <v>108</v>
-      </c>
-      <c r="L67" s="120"/>
-      <c r="M67" s="120"/>
-      <c r="N67" s="120"/>
-      <c r="O67" s="120"/>
-      <c r="P67" s="120"/>
-      <c r="Q67" s="120"/>
-      <c r="R67" s="120"/>
+      <c r="K67" s="108"/>
+      <c r="L67" s="108"/>
+      <c r="M67" s="108"/>
+      <c r="N67" s="108"/>
+      <c r="O67" s="108"/>
+      <c r="P67" s="108"/>
+      <c r="Q67" s="108"/>
+      <c r="R67" s="108"/>
       <c r="S67" s="1"/>
       <c r="T67" s="1"/>
       <c r="U67" s="1"/>
@@ -14104,36 +12760,24 @@
       <c r="X67" s="1"/>
     </row>
     <row r="68" spans="1:24">
-      <c r="A68" s="121" t="s">
-        <v>96</v>
-      </c>
-      <c r="B68" s="122"/>
-      <c r="C68" s="121" t="s">
-        <v>75</v>
-      </c>
-      <c r="D68" s="122"/>
-      <c r="E68" s="123" t="s">
-        <v>97</v>
-      </c>
-      <c r="F68" s="124"/>
-      <c r="G68" s="121" t="s">
-        <v>98</v>
-      </c>
-      <c r="H68" s="122"/>
+      <c r="A68" s="104"/>
+      <c r="B68" s="105"/>
+      <c r="C68" s="104"/>
+      <c r="D68" s="105"/>
+      <c r="E68" s="106"/>
+      <c r="F68" s="107"/>
+      <c r="G68" s="104"/>
+      <c r="H68" s="105"/>
       <c r="I68" s="1"/>
       <c r="J68" s="1"/>
-      <c r="K68" s="121"/>
-      <c r="L68" s="122"/>
-      <c r="M68" s="121" t="s">
-        <v>4</v>
-      </c>
-      <c r="N68" s="122"/>
-      <c r="O68" s="123"/>
-      <c r="P68" s="124"/>
-      <c r="Q68" s="121" t="s">
-        <v>109</v>
-      </c>
-      <c r="R68" s="122"/>
+      <c r="K68" s="104"/>
+      <c r="L68" s="105"/>
+      <c r="M68" s="104"/>
+      <c r="N68" s="105"/>
+      <c r="O68" s="106"/>
+      <c r="P68" s="107"/>
+      <c r="Q68" s="104"/>
+      <c r="R68" s="105"/>
       <c r="S68" s="1"/>
       <c r="T68" s="1"/>
       <c r="U68" s="1"/>
@@ -14144,38 +12788,22 @@
     <row r="69" spans="1:24">
       <c r="A69" s="1"/>
       <c r="B69" s="1"/>
-      <c r="C69" s="129">
-        <v>1</v>
-      </c>
-      <c r="D69" s="54">
-        <v>1.9520833333333332E-3</v>
-      </c>
+      <c r="C69" s="129"/>
+      <c r="D69" s="54"/>
       <c r="E69" s="1"/>
       <c r="F69" s="1"/>
-      <c r="G69" s="129">
-        <v>1</v>
-      </c>
-      <c r="H69" s="128">
-        <v>1.9796875000000001E-3</v>
-      </c>
+      <c r="G69" s="129"/>
+      <c r="H69" s="128"/>
       <c r="I69" s="1"/>
       <c r="J69" s="1"/>
       <c r="K69" s="1"/>
       <c r="L69" s="1"/>
-      <c r="M69" s="1">
-        <v>1</v>
-      </c>
-      <c r="N69" s="54">
-        <v>1.4361342592592592E-3</v>
-      </c>
+      <c r="M69" s="1"/>
+      <c r="N69" s="54"/>
       <c r="O69" s="1"/>
       <c r="P69" s="1"/>
-      <c r="Q69" s="1">
-        <v>1</v>
-      </c>
-      <c r="R69" s="54">
-        <v>1.4263888888888889E-3</v>
-      </c>
+      <c r="Q69" s="1"/>
+      <c r="R69" s="54"/>
       <c r="S69" s="1"/>
       <c r="T69" s="1"/>
       <c r="U69" s="1"/>
@@ -14186,38 +12814,22 @@
     <row r="70" spans="1:24">
       <c r="A70" s="1"/>
       <c r="B70" s="1"/>
-      <c r="C70" s="129">
-        <v>2</v>
-      </c>
-      <c r="D70" s="54">
-        <v>1.1939004629629628E-3</v>
-      </c>
+      <c r="C70" s="129"/>
+      <c r="D70" s="54"/>
       <c r="E70" s="1"/>
       <c r="F70" s="1"/>
-      <c r="G70" s="129">
-        <v>2</v>
-      </c>
-      <c r="H70" s="128">
-        <v>1.2236342592592594E-3</v>
-      </c>
+      <c r="G70" s="129"/>
+      <c r="H70" s="128"/>
       <c r="I70" s="1"/>
       <c r="J70" s="1"/>
       <c r="K70" s="1"/>
       <c r="L70" s="1"/>
-      <c r="M70" s="1">
-        <v>2</v>
-      </c>
-      <c r="N70" s="54">
-        <v>9.4768518518518509E-4</v>
-      </c>
+      <c r="M70" s="1"/>
+      <c r="N70" s="54"/>
       <c r="O70" s="1"/>
       <c r="P70" s="1"/>
-      <c r="Q70" s="1">
-        <v>2</v>
-      </c>
-      <c r="R70" s="54">
-        <v>9.1004629629629628E-4</v>
-      </c>
+      <c r="Q70" s="1"/>
+      <c r="R70" s="54"/>
       <c r="S70" s="1"/>
       <c r="T70" s="1"/>
       <c r="U70" s="1"/>
@@ -14228,38 +12840,22 @@
     <row r="71" spans="1:24">
       <c r="A71" s="1"/>
       <c r="B71" s="1"/>
-      <c r="C71" s="129">
-        <v>3</v>
-      </c>
-      <c r="D71" s="54">
-        <v>1.1949652777777779E-3</v>
-      </c>
+      <c r="C71" s="129"/>
+      <c r="D71" s="54"/>
       <c r="E71" s="1"/>
       <c r="F71" s="1"/>
-      <c r="G71" s="129">
-        <v>3</v>
-      </c>
-      <c r="H71" s="128">
-        <v>1.2050810185185185E-3</v>
-      </c>
+      <c r="G71" s="129"/>
+      <c r="H71" s="128"/>
       <c r="I71" s="1"/>
       <c r="J71" s="1"/>
       <c r="K71" s="1"/>
       <c r="L71" s="1"/>
-      <c r="M71" s="1">
-        <v>3</v>
-      </c>
-      <c r="N71" s="54">
-        <v>8.3365740740740752E-4</v>
-      </c>
+      <c r="M71" s="1"/>
+      <c r="N71" s="54"/>
       <c r="O71" s="1"/>
       <c r="P71" s="1"/>
-      <c r="Q71" s="1">
-        <v>3</v>
-      </c>
-      <c r="R71" s="54">
-        <v>8.2151620370370364E-4</v>
-      </c>
+      <c r="Q71" s="1"/>
+      <c r="R71" s="54"/>
       <c r="S71" s="1"/>
       <c r="T71" s="1"/>
       <c r="U71" s="1"/>
@@ -14270,38 +12866,22 @@
     <row r="72" spans="1:24">
       <c r="A72" s="1"/>
       <c r="B72" s="1"/>
-      <c r="C72" s="129">
-        <v>4</v>
-      </c>
-      <c r="D72" s="54">
-        <v>1.1942129629629631E-3</v>
-      </c>
+      <c r="C72" s="129"/>
+      <c r="D72" s="54"/>
       <c r="E72" s="1"/>
       <c r="F72" s="1"/>
-      <c r="G72" s="129">
-        <v>4</v>
-      </c>
-      <c r="H72" s="128">
-        <v>1.2027199074074073E-3</v>
-      </c>
+      <c r="G72" s="129"/>
+      <c r="H72" s="128"/>
       <c r="I72" s="1"/>
       <c r="J72" s="1"/>
       <c r="K72" s="1"/>
       <c r="L72" s="1"/>
-      <c r="M72" s="1">
-        <v>4</v>
-      </c>
-      <c r="N72" s="54">
-        <v>8.2813657407407413E-4</v>
-      </c>
+      <c r="M72" s="1"/>
+      <c r="N72" s="54"/>
       <c r="O72" s="1"/>
       <c r="P72" s="1"/>
-      <c r="Q72" s="1">
-        <v>4</v>
-      </c>
-      <c r="R72" s="54">
-        <v>8.2106481481481483E-4</v>
-      </c>
+      <c r="Q72" s="1"/>
+      <c r="R72" s="54"/>
       <c r="S72" s="1"/>
       <c r="T72" s="1"/>
       <c r="U72" s="1"/>
@@ -14312,38 +12892,22 @@
     <row r="73" spans="1:24">
       <c r="A73" s="1"/>
       <c r="B73" s="1"/>
-      <c r="C73" s="129">
-        <v>5</v>
-      </c>
-      <c r="D73" s="54">
-        <v>1.1978819444444443E-3</v>
-      </c>
+      <c r="C73" s="129"/>
+      <c r="D73" s="54"/>
       <c r="E73" s="1"/>
       <c r="F73" s="1"/>
-      <c r="G73" s="129">
-        <v>5</v>
-      </c>
-      <c r="H73" s="128">
-        <v>1.1896412037037036E-3</v>
-      </c>
+      <c r="G73" s="129"/>
+      <c r="H73" s="128"/>
       <c r="I73" s="1"/>
       <c r="J73" s="1"/>
       <c r="K73" s="1"/>
       <c r="L73" s="1"/>
-      <c r="M73" s="1">
-        <v>5</v>
-      </c>
-      <c r="N73" s="54">
-        <v>8.2803240740740743E-4</v>
-      </c>
+      <c r="M73" s="1"/>
+      <c r="N73" s="54"/>
       <c r="O73" s="1"/>
       <c r="P73" s="1"/>
-      <c r="Q73" s="1">
-        <v>5</v>
-      </c>
-      <c r="R73" s="54">
-        <v>8.2216435185185181E-4</v>
-      </c>
+      <c r="Q73" s="1"/>
+      <c r="R73" s="54"/>
       <c r="S73" s="1"/>
       <c r="T73" s="1"/>
       <c r="U73" s="1"/>
@@ -14354,38 +12918,22 @@
     <row r="74" spans="1:24">
       <c r="A74" s="1"/>
       <c r="B74" s="1"/>
-      <c r="C74" s="129">
-        <v>6</v>
-      </c>
-      <c r="D74" s="54">
-        <v>1.1956712962962962E-3</v>
-      </c>
+      <c r="C74" s="129"/>
+      <c r="D74" s="54"/>
       <c r="E74" s="1"/>
       <c r="F74" s="1"/>
-      <c r="G74" s="129">
-        <v>6</v>
-      </c>
-      <c r="H74" s="128">
-        <v>1.2009606481481483E-3</v>
-      </c>
+      <c r="G74" s="129"/>
+      <c r="H74" s="128"/>
       <c r="I74" s="1"/>
       <c r="J74" s="1"/>
       <c r="K74" s="1"/>
       <c r="L74" s="1"/>
-      <c r="M74" s="1">
-        <v>6</v>
-      </c>
-      <c r="N74" s="54">
-        <v>8.3063657407407402E-4</v>
-      </c>
+      <c r="M74" s="1"/>
+      <c r="N74" s="54"/>
       <c r="O74" s="1"/>
       <c r="P74" s="1"/>
-      <c r="Q74" s="1">
-        <v>6</v>
-      </c>
-      <c r="R74" s="54">
-        <v>8.4766203703703707E-4</v>
-      </c>
+      <c r="Q74" s="1"/>
+      <c r="R74" s="54"/>
       <c r="S74" s="1"/>
       <c r="T74" s="1"/>
       <c r="U74" s="1"/>
@@ -14396,38 +12944,22 @@
     <row r="75" spans="1:24">
       <c r="A75" s="1"/>
       <c r="B75" s="1"/>
-      <c r="C75" s="129">
-        <v>7</v>
-      </c>
-      <c r="D75" s="54">
-        <v>1.1767824074074074E-3</v>
-      </c>
+      <c r="C75" s="129"/>
+      <c r="D75" s="54"/>
       <c r="E75" s="1"/>
       <c r="F75" s="1"/>
-      <c r="G75" s="129">
-        <v>7</v>
-      </c>
-      <c r="H75" s="128">
-        <v>1.1911805555555556E-3</v>
-      </c>
+      <c r="G75" s="129"/>
+      <c r="H75" s="128"/>
       <c r="I75" s="1"/>
       <c r="J75" s="1"/>
       <c r="K75" s="1"/>
       <c r="L75" s="1"/>
-      <c r="M75" s="1">
-        <v>7</v>
-      </c>
-      <c r="N75" s="54">
-        <v>8.3038194444444446E-4</v>
-      </c>
+      <c r="M75" s="1"/>
+      <c r="N75" s="54"/>
       <c r="O75" s="1"/>
       <c r="P75" s="1"/>
-      <c r="Q75" s="1">
-        <v>7</v>
-      </c>
-      <c r="R75" s="54">
-        <v>8.2127314814814812E-4</v>
-      </c>
+      <c r="Q75" s="1"/>
+      <c r="R75" s="54"/>
       <c r="S75" s="1"/>
       <c r="T75" s="1"/>
       <c r="U75" s="1"/>
@@ -14438,38 +12970,22 @@
     <row r="76" spans="1:24">
       <c r="A76" s="1"/>
       <c r="B76" s="1"/>
-      <c r="C76" s="129">
-        <v>8</v>
-      </c>
-      <c r="D76" s="54">
-        <v>1.204861111111111E-3</v>
-      </c>
+      <c r="C76" s="129"/>
+      <c r="D76" s="54"/>
       <c r="E76" s="1"/>
       <c r="F76" s="1"/>
-      <c r="G76" s="129">
-        <v>8</v>
-      </c>
-      <c r="H76" s="128">
-        <v>1.1953125E-3</v>
-      </c>
+      <c r="G76" s="129"/>
+      <c r="H76" s="128"/>
       <c r="I76" s="1"/>
       <c r="J76" s="1"/>
       <c r="K76" s="1"/>
       <c r="L76" s="1"/>
-      <c r="M76" s="1">
-        <v>8</v>
-      </c>
-      <c r="N76" s="54">
-        <v>8.2754629629629628E-4</v>
-      </c>
+      <c r="M76" s="1"/>
+      <c r="N76" s="54"/>
       <c r="O76" s="1"/>
       <c r="P76" s="1"/>
-      <c r="Q76" s="1">
-        <v>8</v>
-      </c>
-      <c r="R76" s="54">
-        <v>8.2086805555555559E-4</v>
-      </c>
+      <c r="Q76" s="1"/>
+      <c r="R76" s="54"/>
       <c r="S76" s="1"/>
       <c r="T76" s="1"/>
       <c r="U76" s="1"/>
@@ -14480,38 +12996,22 @@
     <row r="77" spans="1:24">
       <c r="A77" s="1"/>
       <c r="B77" s="1"/>
-      <c r="C77" s="129">
-        <v>9</v>
-      </c>
-      <c r="D77" s="54">
-        <v>1.2104166666666667E-3</v>
-      </c>
+      <c r="C77" s="129"/>
+      <c r="D77" s="54"/>
       <c r="E77" s="1"/>
       <c r="F77" s="1"/>
-      <c r="G77" s="129">
-        <v>9</v>
-      </c>
-      <c r="H77" s="128">
-        <v>1.2066550925925925E-3</v>
-      </c>
+      <c r="G77" s="129"/>
+      <c r="H77" s="128"/>
       <c r="I77" s="1"/>
       <c r="J77" s="1"/>
       <c r="K77" s="1"/>
       <c r="L77" s="1"/>
-      <c r="M77" s="1">
-        <v>9</v>
-      </c>
-      <c r="N77" s="54">
-        <v>8.3032407407407404E-4</v>
-      </c>
+      <c r="M77" s="1"/>
+      <c r="N77" s="54"/>
       <c r="O77" s="1"/>
       <c r="P77" s="1"/>
-      <c r="Q77" s="1">
-        <v>9</v>
-      </c>
-      <c r="R77" s="54">
-        <v>8.1811342592592591E-4</v>
-      </c>
+      <c r="Q77" s="1"/>
+      <c r="R77" s="54"/>
       <c r="S77" s="1"/>
       <c r="T77" s="1"/>
       <c r="U77" s="1"/>
@@ -14522,38 +13022,22 @@
     <row r="78" spans="1:24">
       <c r="A78" s="1"/>
       <c r="B78" s="1"/>
-      <c r="C78" s="129">
-        <v>10</v>
-      </c>
-      <c r="D78" s="54">
-        <v>1.5151504629629629E-3</v>
-      </c>
+      <c r="C78" s="129"/>
+      <c r="D78" s="54"/>
       <c r="E78" s="1"/>
       <c r="F78" s="1"/>
-      <c r="G78" s="129">
-        <v>10</v>
-      </c>
-      <c r="H78" s="128">
-        <v>1.4534606481481482E-3</v>
-      </c>
+      <c r="G78" s="129"/>
+      <c r="H78" s="128"/>
       <c r="I78" s="1"/>
       <c r="J78" s="1"/>
       <c r="K78" s="1"/>
       <c r="L78" s="1"/>
-      <c r="M78" s="1">
-        <v>10</v>
-      </c>
-      <c r="N78" s="54">
-        <v>8.3142361111111123E-4</v>
-      </c>
+      <c r="M78" s="1"/>
+      <c r="N78" s="54"/>
       <c r="O78" s="1"/>
       <c r="P78" s="1"/>
-      <c r="Q78" s="1">
-        <v>10</v>
-      </c>
-      <c r="R78" s="54">
-        <v>8.1762731481481487E-4</v>
-      </c>
+      <c r="Q78" s="1"/>
+      <c r="R78" s="54"/>
       <c r="S78" s="1"/>
       <c r="T78" s="1"/>
       <c r="U78" s="1"/>
@@ -14564,38 +13048,22 @@
     <row r="79" spans="1:24">
       <c r="A79" s="1"/>
       <c r="B79" s="1"/>
-      <c r="C79" s="129">
-        <v>11</v>
-      </c>
-      <c r="D79" s="54">
-        <v>1.9391203703703703E-3</v>
-      </c>
+      <c r="C79" s="129"/>
+      <c r="D79" s="54"/>
       <c r="E79" s="1"/>
       <c r="F79" s="1"/>
-      <c r="G79" s="129">
-        <v>11</v>
-      </c>
-      <c r="H79" s="128">
-        <v>1.9292013888888887E-3</v>
-      </c>
+      <c r="G79" s="129"/>
+      <c r="H79" s="128"/>
       <c r="I79" s="1"/>
       <c r="J79" s="1"/>
       <c r="K79" s="1"/>
       <c r="L79" s="1"/>
-      <c r="M79" s="1">
-        <v>11</v>
-      </c>
-      <c r="N79" s="54">
-        <v>8.480671296296296E-4</v>
-      </c>
+      <c r="M79" s="1"/>
+      <c r="N79" s="54"/>
       <c r="O79" s="1"/>
       <c r="P79" s="1"/>
-      <c r="Q79" s="1">
-        <v>11</v>
-      </c>
-      <c r="R79" s="54">
-        <v>8.2513888888888893E-4</v>
-      </c>
+      <c r="Q79" s="1"/>
+      <c r="R79" s="54"/>
       <c r="S79" s="1"/>
       <c r="T79" s="1"/>
       <c r="U79" s="1"/>
@@ -14606,38 +13074,22 @@
     <row r="80" spans="1:24">
       <c r="A80" s="1"/>
       <c r="B80" s="1"/>
-      <c r="C80" s="129">
-        <v>12</v>
-      </c>
-      <c r="D80" s="54">
-        <v>1.1987847222222222E-3</v>
-      </c>
+      <c r="C80" s="129"/>
+      <c r="D80" s="54"/>
       <c r="E80" s="1"/>
       <c r="F80" s="1"/>
-      <c r="G80" s="129">
-        <v>12</v>
-      </c>
-      <c r="H80" s="128">
-        <v>1.2021874999999999E-3</v>
-      </c>
+      <c r="G80" s="129"/>
+      <c r="H80" s="128"/>
       <c r="I80" s="1"/>
       <c r="J80" s="1"/>
       <c r="K80" s="1"/>
       <c r="L80" s="1"/>
-      <c r="M80" s="1">
-        <v>12</v>
-      </c>
-      <c r="N80" s="54">
-        <v>8.3438657407407398E-4</v>
-      </c>
+      <c r="M80" s="1"/>
+      <c r="N80" s="54"/>
       <c r="O80" s="1"/>
       <c r="P80" s="1"/>
-      <c r="Q80" s="1">
-        <v>12</v>
-      </c>
-      <c r="R80" s="54">
-        <v>9.9265046296296297E-4</v>
-      </c>
+      <c r="Q80" s="1"/>
+      <c r="R80" s="54"/>
       <c r="S80" s="1"/>
       <c r="T80" s="1"/>
       <c r="U80" s="1"/>
@@ -14648,38 +13100,22 @@
     <row r="81" spans="1:24">
       <c r="A81" s="1"/>
       <c r="B81" s="1"/>
-      <c r="C81" s="129">
-        <v>13</v>
-      </c>
-      <c r="D81" s="54">
-        <v>1.2125462962962964E-3</v>
-      </c>
+      <c r="C81" s="129"/>
+      <c r="D81" s="54"/>
       <c r="E81" s="1"/>
       <c r="F81" s="1"/>
-      <c r="G81" s="129">
-        <v>13</v>
-      </c>
-      <c r="H81" s="128">
-        <v>1.2077546296296296E-3</v>
-      </c>
+      <c r="G81" s="129"/>
+      <c r="H81" s="128"/>
       <c r="I81" s="1"/>
       <c r="J81" s="1"/>
       <c r="K81" s="1"/>
       <c r="L81" s="1"/>
-      <c r="M81" s="1">
-        <v>13</v>
-      </c>
-      <c r="N81" s="54">
-        <v>8.3318287037037031E-4</v>
-      </c>
+      <c r="M81" s="1"/>
+      <c r="N81" s="54"/>
       <c r="O81" s="1"/>
       <c r="P81" s="1"/>
-      <c r="Q81" s="1">
-        <v>13</v>
-      </c>
-      <c r="R81" s="54">
-        <v>8.3115740740740741E-4</v>
-      </c>
+      <c r="Q81" s="1"/>
+      <c r="R81" s="54"/>
       <c r="S81" s="1"/>
       <c r="T81" s="1"/>
       <c r="U81" s="1"/>
@@ -14690,38 +13126,22 @@
     <row r="82" spans="1:24">
       <c r="A82" s="1"/>
       <c r="B82" s="1"/>
-      <c r="C82" s="129">
-        <v>14</v>
-      </c>
-      <c r="D82" s="54">
-        <v>1.2050694444444444E-3</v>
-      </c>
+      <c r="C82" s="129"/>
+      <c r="D82" s="54"/>
       <c r="E82" s="1"/>
       <c r="F82" s="1"/>
-      <c r="G82" s="129">
-        <v>14</v>
-      </c>
-      <c r="H82" s="128">
-        <v>1.2092245370370371E-3</v>
-      </c>
+      <c r="G82" s="129"/>
+      <c r="H82" s="128"/>
       <c r="I82" s="1"/>
       <c r="J82" s="1"/>
       <c r="K82" s="1"/>
       <c r="L82" s="1"/>
-      <c r="M82" s="1">
-        <v>14</v>
-      </c>
-      <c r="N82" s="54">
-        <v>8.3377314814814816E-4</v>
-      </c>
+      <c r="M82" s="1"/>
+      <c r="N82" s="54"/>
       <c r="O82" s="1"/>
       <c r="P82" s="1"/>
-      <c r="Q82" s="1">
-        <v>14</v>
-      </c>
-      <c r="R82" s="54">
-        <v>8.1944444444444437E-4</v>
-      </c>
+      <c r="Q82" s="1"/>
+      <c r="R82" s="54"/>
       <c r="S82" s="1"/>
       <c r="T82" s="1"/>
       <c r="U82" s="1"/>
@@ -14732,38 +13152,22 @@
     <row r="83" spans="1:24">
       <c r="A83" s="1"/>
       <c r="B83" s="1"/>
-      <c r="C83" s="129">
-        <v>15</v>
-      </c>
-      <c r="D83" s="54">
-        <v>1.1976967592592592E-3</v>
-      </c>
+      <c r="C83" s="129"/>
+      <c r="D83" s="54"/>
       <c r="E83" s="1"/>
       <c r="F83" s="1"/>
-      <c r="G83" s="129">
-        <v>15</v>
-      </c>
-      <c r="H83" s="128">
-        <v>1.2027314814814815E-3</v>
-      </c>
+      <c r="G83" s="129"/>
+      <c r="H83" s="128"/>
       <c r="I83" s="1"/>
       <c r="J83" s="1"/>
       <c r="K83" s="1"/>
       <c r="L83" s="1"/>
-      <c r="M83" s="1">
-        <v>15</v>
-      </c>
-      <c r="N83" s="54">
-        <v>8.3221064814814822E-4</v>
-      </c>
+      <c r="M83" s="1"/>
+      <c r="N83" s="54"/>
       <c r="O83" s="1"/>
       <c r="P83" s="1"/>
-      <c r="Q83" s="1">
-        <v>15</v>
-      </c>
-      <c r="R83" s="54">
-        <v>8.2342592592592602E-4</v>
-      </c>
+      <c r="Q83" s="1"/>
+      <c r="R83" s="54"/>
       <c r="S83" s="1"/>
       <c r="T83" s="1"/>
       <c r="U83" s="1"/>
@@ -14774,38 +13178,22 @@
     <row r="84" spans="1:24">
       <c r="A84" s="1"/>
       <c r="B84" s="1"/>
-      <c r="C84" s="129">
-        <v>16</v>
-      </c>
-      <c r="D84" s="54">
-        <v>1.2089351851851851E-3</v>
-      </c>
+      <c r="C84" s="129"/>
+      <c r="D84" s="54"/>
       <c r="E84" s="1"/>
       <c r="F84" s="1"/>
-      <c r="G84" s="129">
-        <v>16</v>
-      </c>
-      <c r="H84" s="128">
-        <v>1.2106712962962963E-3</v>
-      </c>
+      <c r="G84" s="129"/>
+      <c r="H84" s="128"/>
       <c r="I84" s="1"/>
       <c r="J84" s="1"/>
       <c r="K84" s="1"/>
       <c r="L84" s="1"/>
-      <c r="M84" s="1">
-        <v>16</v>
-      </c>
-      <c r="N84" s="54">
-        <v>8.2762731481481489E-4</v>
-      </c>
+      <c r="M84" s="1"/>
+      <c r="N84" s="54"/>
       <c r="O84" s="1"/>
       <c r="P84" s="1"/>
-      <c r="Q84" s="1">
-        <v>16</v>
-      </c>
-      <c r="R84" s="54">
-        <v>8.1971064814814819E-4</v>
-      </c>
+      <c r="Q84" s="1"/>
+      <c r="R84" s="54"/>
       <c r="S84" s="1"/>
       <c r="T84" s="1"/>
       <c r="U84" s="1"/>
@@ -14826,20 +13214,12 @@
       <c r="J85" s="1"/>
       <c r="K85" s="1"/>
       <c r="L85" s="1"/>
-      <c r="M85" s="1">
-        <v>17</v>
-      </c>
-      <c r="N85" s="54">
-        <v>8.4262731481481482E-4</v>
-      </c>
+      <c r="M85" s="1"/>
+      <c r="N85" s="54"/>
       <c r="O85" s="1"/>
       <c r="P85" s="1"/>
-      <c r="Q85" s="1">
-        <v>17</v>
-      </c>
-      <c r="R85" s="54">
-        <v>8.3310185185185191E-4</v>
-      </c>
+      <c r="Q85" s="1"/>
+      <c r="R85" s="54"/>
       <c r="S85" s="1"/>
       <c r="T85" s="1"/>
       <c r="U85" s="1"/>
@@ -14860,20 +13240,12 @@
       <c r="J86" s="1"/>
       <c r="K86" s="1"/>
       <c r="L86" s="1"/>
-      <c r="M86" s="1">
-        <v>18</v>
-      </c>
-      <c r="N86" s="54">
-        <v>8.3070601851851849E-4</v>
-      </c>
+      <c r="M86" s="1"/>
+      <c r="N86" s="54"/>
       <c r="O86" s="1"/>
       <c r="P86" s="1"/>
-      <c r="Q86" s="1">
-        <v>18</v>
-      </c>
-      <c r="R86" s="54">
-        <v>8.2271990740740743E-4</v>
-      </c>
+      <c r="Q86" s="1"/>
+      <c r="R86" s="54"/>
       <c r="S86" s="1"/>
       <c r="T86" s="1"/>
       <c r="U86" s="1"/>
@@ -14882,46 +13254,24 @@
       <c r="X86" s="1"/>
     </row>
     <row r="87" spans="1:24">
-      <c r="A87" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="B87" s="54" t="e">
-        <f>+AVERAGE(B65:B74,B78:B84)</f>
-        <v>#DIV/0!</v>
-      </c>
+      <c r="A87" s="1"/>
+      <c r="B87" s="54"/>
       <c r="C87" s="1"/>
-      <c r="D87" s="54">
-        <f>+AVERAGE(D65:D77,D80:D84)</f>
-        <v>1.2531291335978834E-3</v>
-      </c>
+      <c r="D87" s="54"/>
       <c r="E87" s="1"/>
-      <c r="F87" s="54" t="e">
-        <f>+AVERAGE(F65:F74,F78:F84)</f>
-        <v>#DIV/0!</v>
-      </c>
+      <c r="F87" s="54"/>
       <c r="G87" s="129"/>
-      <c r="H87" s="54">
-        <f>+AVERAGE(H69:H77,H80:H84)</f>
-        <v>1.2591030092592593E-3</v>
-      </c>
+      <c r="H87" s="54"/>
       <c r="I87" s="1"/>
       <c r="J87" s="1"/>
       <c r="K87" s="1"/>
       <c r="L87" s="54"/>
-      <c r="M87" s="1">
-        <v>19</v>
-      </c>
-      <c r="N87" s="54">
-        <v>8.292361111111111E-4</v>
-      </c>
+      <c r="M87" s="1"/>
+      <c r="N87" s="54"/>
       <c r="O87" s="1"/>
       <c r="P87" s="54"/>
-      <c r="Q87" s="1">
-        <v>19</v>
-      </c>
-      <c r="R87" s="54">
-        <v>8.2199074074074065E-4</v>
-      </c>
+      <c r="Q87" s="1"/>
+      <c r="R87" s="54"/>
       <c r="S87" s="1"/>
       <c r="T87" s="1"/>
       <c r="U87" s="1"/>
@@ -14942,20 +13292,12 @@
       <c r="J88" s="1"/>
       <c r="K88" s="1"/>
       <c r="L88" s="1"/>
-      <c r="M88" s="1">
-        <v>20</v>
-      </c>
-      <c r="N88" s="54">
-        <v>8.3160879629629633E-4</v>
-      </c>
+      <c r="M88" s="1"/>
+      <c r="N88" s="54"/>
       <c r="O88" s="1"/>
       <c r="P88" s="1"/>
-      <c r="Q88" s="1">
-        <v>20</v>
-      </c>
-      <c r="R88" s="54">
-        <v>8.2870370370370368E-4</v>
-      </c>
+      <c r="Q88" s="1"/>
+      <c r="R88" s="54"/>
       <c r="S88" s="1"/>
       <c r="T88" s="1"/>
       <c r="U88" s="1"/>
@@ -14967,34 +13309,21 @@
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
-      <c r="D89" s="54">
-        <v>1.2531291335978834E-3</v>
-      </c>
+      <c r="D89" s="54"/>
       <c r="E89" s="1"/>
       <c r="F89" s="1"/>
       <c r="G89" s="1"/>
-      <c r="H89" s="96">
-        <f>+SUM(H87-D87)</f>
-        <v>5.9738756613759211E-6</v>
-      </c>
+      <c r="H89" s="96"/>
       <c r="I89" s="1"/>
       <c r="J89" s="1"/>
       <c r="K89" s="1"/>
       <c r="L89" s="1"/>
-      <c r="M89" s="1">
-        <v>21</v>
-      </c>
-      <c r="N89" s="54">
-        <v>8.294444444444445E-4</v>
-      </c>
+      <c r="M89" s="1"/>
+      <c r="N89" s="54"/>
       <c r="O89" s="1"/>
       <c r="P89" s="1"/>
-      <c r="Q89" s="1">
-        <v>21</v>
-      </c>
-      <c r="R89" s="54">
-        <v>8.2164351851851843E-4</v>
-      </c>
+      <c r="Q89" s="1"/>
+      <c r="R89" s="54"/>
       <c r="S89" s="1"/>
       <c r="T89" s="1"/>
       <c r="U89" s="1"/>
@@ -15015,20 +13344,12 @@
       <c r="J90" s="1"/>
       <c r="K90" s="1"/>
       <c r="L90" s="1"/>
-      <c r="M90" s="1">
-        <v>22</v>
-      </c>
-      <c r="N90" s="54">
-        <v>8.3431712962962973E-4</v>
-      </c>
+      <c r="M90" s="1"/>
+      <c r="N90" s="54"/>
       <c r="O90" s="1"/>
       <c r="P90" s="1"/>
-      <c r="Q90" s="1">
-        <v>22</v>
-      </c>
-      <c r="R90" s="54">
-        <v>8.227662037037037E-4</v>
-      </c>
+      <c r="Q90" s="1"/>
+      <c r="R90" s="54"/>
       <c r="S90" s="1"/>
       <c r="T90" s="1"/>
       <c r="U90" s="1"/>
@@ -15037,38 +13358,24 @@
       <c r="X90" s="1"/>
     </row>
     <row r="91" spans="1:24">
-      <c r="A91" s="86" t="s">
-        <v>94</v>
-      </c>
+      <c r="A91" s="86"/>
       <c r="B91" s="1"/>
       <c r="C91" s="1"/>
-      <c r="D91" s="54" t="s">
-        <v>110</v>
-      </c>
+      <c r="D91" s="54"/>
       <c r="E91" s="1"/>
       <c r="F91" s="1"/>
       <c r="G91" s="1"/>
-      <c r="H91" s="54" t="s">
-        <v>111</v>
-      </c>
+      <c r="H91" s="54"/>
       <c r="I91" s="1"/>
       <c r="J91" s="1"/>
       <c r="K91" s="86"/>
       <c r="L91" s="1"/>
-      <c r="M91" s="1">
-        <v>23</v>
-      </c>
-      <c r="N91" s="54">
-        <v>8.2590277777777783E-4</v>
-      </c>
+      <c r="M91" s="1"/>
+      <c r="N91" s="54"/>
       <c r="O91" s="1"/>
       <c r="P91" s="1"/>
-      <c r="Q91" s="1">
-        <v>23</v>
-      </c>
-      <c r="R91" s="54">
-        <v>8.2003472222222222E-4</v>
-      </c>
+      <c r="Q91" s="1"/>
+      <c r="R91" s="54"/>
       <c r="S91" s="1"/>
       <c r="T91" s="1"/>
       <c r="U91" s="1"/>
@@ -15089,20 +13396,12 @@
       <c r="J92" s="1"/>
       <c r="K92" s="1"/>
       <c r="L92" s="1"/>
-      <c r="M92" s="1">
-        <v>24</v>
-      </c>
-      <c r="N92" s="54">
-        <v>8.2978009259259257E-4</v>
-      </c>
+      <c r="M92" s="1"/>
+      <c r="N92" s="54"/>
       <c r="O92" s="1"/>
       <c r="P92" s="1"/>
-      <c r="Q92" s="1">
-        <v>24</v>
-      </c>
-      <c r="R92" s="54">
-        <v>8.2083333333333335E-4</v>
-      </c>
+      <c r="Q92" s="1"/>
+      <c r="R92" s="54"/>
       <c r="S92" s="1"/>
       <c r="T92" s="1"/>
       <c r="U92" s="1"/>
@@ -15123,20 +13422,12 @@
       <c r="J93" s="1"/>
       <c r="K93" s="1"/>
       <c r="L93" s="1"/>
-      <c r="M93" s="1">
-        <v>25</v>
-      </c>
-      <c r="N93" s="54">
-        <v>8.2966435185185172E-4</v>
-      </c>
+      <c r="M93" s="1"/>
+      <c r="N93" s="54"/>
       <c r="O93" s="1"/>
       <c r="P93" s="1"/>
-      <c r="Q93" s="1">
-        <v>25</v>
-      </c>
-      <c r="R93" s="54">
-        <v>8.3520833333333342E-4</v>
-      </c>
+      <c r="Q93" s="1"/>
+      <c r="R93" s="54"/>
       <c r="S93" s="1"/>
       <c r="T93" s="1"/>
       <c r="U93" s="1"/>
@@ -15183,20 +13474,12 @@
       <c r="J95" s="1"/>
       <c r="K95" s="1"/>
       <c r="L95" s="1"/>
-      <c r="M95" s="86" t="s">
-        <v>112</v>
-      </c>
-      <c r="N95" s="54">
-        <f>+AVERAGE(N69:N93)</f>
-        <v>8.6065972222222208E-4</v>
-      </c>
+      <c r="M95" s="86"/>
+      <c r="N95" s="54"/>
       <c r="O95" s="1"/>
       <c r="P95" s="1"/>
       <c r="Q95" s="1"/>
-      <c r="R95" s="54">
-        <f>+AVERAGE(R69:R93)</f>
-        <v>8.58610185185185E-4</v>
-      </c>
+      <c r="R95" s="54"/>
       <c r="S95" s="1"/>
       <c r="T95" s="1"/>
       <c r="U95" s="1"/>
@@ -15243,20 +13526,12 @@
       <c r="J97" s="1"/>
       <c r="K97" s="1"/>
       <c r="L97" s="1"/>
-      <c r="M97" s="86" t="s">
-        <v>113</v>
-      </c>
-      <c r="N97" s="98">
-        <f>+SUM(N95-R95)</f>
-        <v>2.0495370370370806E-6</v>
-      </c>
+      <c r="M97" s="86"/>
+      <c r="N97" s="98"/>
       <c r="O97" s="1"/>
       <c r="P97" s="1"/>
       <c r="Q97" s="1"/>
-      <c r="R97" s="54">
-        <f>+AVERAGE(R71:R95)</f>
-        <v>8.328095679012345E-4</v>
-      </c>
+      <c r="R97" s="54"/>
       <c r="S97" s="1"/>
       <c r="T97" s="1"/>
       <c r="U97" s="1"/>
@@ -15303,18 +13578,12 @@
       <c r="J99" s="1"/>
       <c r="K99" s="1"/>
       <c r="L99" s="1"/>
-      <c r="M99" s="86" t="s">
-        <v>114</v>
-      </c>
-      <c r="N99" s="54" t="s">
-        <v>115</v>
-      </c>
+      <c r="M99" s="86"/>
+      <c r="N99" s="54"/>
       <c r="O99" s="1"/>
       <c r="P99" s="1"/>
       <c r="Q99" s="1"/>
-      <c r="R99" s="54" t="s">
-        <v>116</v>
-      </c>
+      <c r="R99" s="54"/>
       <c r="S99" s="1"/>
       <c r="T99" s="1"/>
       <c r="U99" s="1"/>
@@ -15361,19 +13630,12 @@
       <c r="J101" s="1"/>
       <c r="K101" s="1"/>
       <c r="L101" s="1"/>
-      <c r="M101" s="86" t="s">
-        <v>117</v>
-      </c>
-      <c r="N101" s="99" t="e">
-        <f>+SUM(N99-R99)</f>
-        <v>#VALUE!</v>
-      </c>
+      <c r="M101" s="86"/>
+      <c r="N101" s="99"/>
       <c r="O101" s="1"/>
       <c r="P101" s="1"/>
       <c r="Q101" s="1"/>
-      <c r="R101" s="54" t="s">
-        <v>118</v>
-      </c>
+      <c r="R101" s="54"/>
       <c r="S101" s="1"/>
       <c r="T101" s="1"/>
       <c r="U101" s="1"/>
@@ -15408,9 +13670,7 @@
       <c r="X102" s="1"/>
     </row>
     <row r="103" spans="1:24">
-      <c r="A103" s="111" t="s">
-        <v>65</v>
-      </c>
+      <c r="A103" s="111"/>
       <c r="B103" s="111"/>
       <c r="C103" s="111"/>
       <c r="D103" s="111"/>
@@ -15463,22 +13723,22 @@
     </row>
     <row r="105" spans="1:24">
       <c r="A105" s="1" t="s">
-        <v>119</v>
+        <v>69</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>120</v>
+        <v>70</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>121</v>
+        <v>71</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>122</v>
+        <v>72</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>123</v>
+        <v>73</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>124</v>
+        <v>74</v>
       </c>
       <c r="G105" s="1"/>
       <c r="H105" s="1"/>
@@ -16033,6 +14293,40 @@
     </row>
   </sheetData>
   <mergeCells count="43">
+    <mergeCell ref="A103:H104"/>
+    <mergeCell ref="A67:H67"/>
+    <mergeCell ref="A68:B68"/>
+    <mergeCell ref="C68:D68"/>
+    <mergeCell ref="E68:F68"/>
+    <mergeCell ref="G68:H68"/>
+    <mergeCell ref="K35:R35"/>
+    <mergeCell ref="K37:L37"/>
+    <mergeCell ref="Q37:R37"/>
+    <mergeCell ref="O37:P37"/>
+    <mergeCell ref="M37:N37"/>
+    <mergeCell ref="K36:L36"/>
+    <mergeCell ref="M36:N36"/>
+    <mergeCell ref="O36:P36"/>
+    <mergeCell ref="Q36:R36"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="Q2:R2"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="O2:P2"/>
+    <mergeCell ref="K1:R1"/>
+    <mergeCell ref="A35:H35"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="G37:H37"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="E37:F37"/>
+    <mergeCell ref="G36:H36"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="E36:F36"/>
+    <mergeCell ref="K68:L68"/>
+    <mergeCell ref="M68:N68"/>
+    <mergeCell ref="O68:P68"/>
+    <mergeCell ref="Q68:R68"/>
+    <mergeCell ref="K67:R67"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="C4:D4"/>
     <mergeCell ref="E4:F4"/>
@@ -16042,40 +14336,6 @@
     <mergeCell ref="C3:D3"/>
     <mergeCell ref="E3:F3"/>
     <mergeCell ref="G3:H3"/>
-    <mergeCell ref="K68:L68"/>
-    <mergeCell ref="M68:N68"/>
-    <mergeCell ref="O68:P68"/>
-    <mergeCell ref="Q68:R68"/>
-    <mergeCell ref="K67:R67"/>
-    <mergeCell ref="A35:H35"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="G37:H37"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="E37:F37"/>
-    <mergeCell ref="G36:H36"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="E36:F36"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="Q2:R2"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="O2:P2"/>
-    <mergeCell ref="K1:R1"/>
-    <mergeCell ref="K35:R35"/>
-    <mergeCell ref="K37:L37"/>
-    <mergeCell ref="Q37:R37"/>
-    <mergeCell ref="O37:P37"/>
-    <mergeCell ref="M37:N37"/>
-    <mergeCell ref="K36:L36"/>
-    <mergeCell ref="M36:N36"/>
-    <mergeCell ref="O36:P36"/>
-    <mergeCell ref="Q36:R36"/>
-    <mergeCell ref="A103:H104"/>
-    <mergeCell ref="A67:H67"/>
-    <mergeCell ref="A68:B68"/>
-    <mergeCell ref="C68:D68"/>
-    <mergeCell ref="E68:F68"/>
-    <mergeCell ref="G68:H68"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
